--- a/sample_data/acoes_brasileiras.xlsx
+++ b/sample_data/acoes_brasileiras.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Python\portfolio_optimizer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Python\portfolio_optimizer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6D546B9-9CA6-4CB4-85C6-04C0792EAFD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75FB77F5-085D-4183-A6D0-02AFFF2D0C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,14 @@
     <sheet name="Estatísticas" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Preços de Fechamento'!$A$1:$BH$251</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Preços de Fechamento'!$A$1:$BG$251</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="69">
   <si>
     <t>Data</t>
   </si>
@@ -230,7 +230,7 @@
     <t>Desvio Padrão</t>
   </si>
   <si>
-    <t>REF_BOVA11</t>
+    <t>REF</t>
   </si>
 </sst>
 </file>
@@ -238,8 +238,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="166" formatCode="\R\$\ #,##0.00"/>
-    <numFmt numFmtId="167" formatCode="0.00&quot;%&quot;"/>
+    <numFmt numFmtId="164" formatCode="\R\$\ #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;%&quot;"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -312,11 +312,11 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -621,14 +621,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BH251"/>
+  <dimension ref="A1:BG251"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="60" width="15" customWidth="1"/>
+    <col min="2" max="59" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -789,28 +789,25 @@
         <v>52</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="BH1" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>45293</v>
       </c>
@@ -971,28 +968,25 @@
         <v>13.967512130737299</v>
       </c>
       <c r="BB2" s="3">
-        <v>3.1550769805908199</v>
+        <v>8.8256044387817383</v>
       </c>
       <c r="BC2" s="3">
-        <v>8.8256044387817383</v>
+        <v>67.873283386230469</v>
       </c>
       <c r="BD2" s="3">
-        <v>67.873283386230469</v>
+        <v>20.417461395263668</v>
       </c>
       <c r="BE2" s="3">
-        <v>20.417461395263668</v>
+        <v>23.884775161743161</v>
       </c>
       <c r="BF2" s="3">
-        <v>23.884775161743161</v>
+        <v>17.623029708862301</v>
       </c>
       <c r="BG2" s="3">
-        <v>17.623029708862301</v>
-      </c>
-      <c r="BH2" s="3">
         <v>35.562427520751953</v>
       </c>
     </row>
-    <row r="3" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>45294</v>
       </c>
@@ -1153,28 +1147,25 @@
         <v>12.93105411529541</v>
       </c>
       <c r="BB3" s="3">
-        <v>3.158636093139648</v>
+        <v>8.7772712707519531</v>
       </c>
       <c r="BC3" s="3">
-        <v>8.7772712707519531</v>
+        <v>67.520919799804688</v>
       </c>
       <c r="BD3" s="3">
-        <v>67.520919799804688</v>
+        <v>20.61301231384277</v>
       </c>
       <c r="BE3" s="3">
-        <v>20.61301231384277</v>
+        <v>23.571573257446289</v>
       </c>
       <c r="BF3" s="3">
-        <v>23.571573257446289</v>
+        <v>18.102102279663089</v>
       </c>
       <c r="BG3" s="3">
-        <v>18.102102279663089</v>
-      </c>
-      <c r="BH3" s="3">
         <v>35.834712982177727</v>
       </c>
     </row>
-    <row r="4" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>45295</v>
       </c>
@@ -1335,28 +1326,25 @@
         <v>11.519495964050289</v>
       </c>
       <c r="BB4" s="3">
-        <v>3.1052508354187012</v>
+        <v>8.6419382095336914</v>
       </c>
       <c r="BC4" s="3">
-        <v>8.6419382095336914</v>
+        <v>66.613594055175781</v>
       </c>
       <c r="BD4" s="3">
-        <v>66.613594055175781</v>
+        <v>19.928579330444339</v>
       </c>
       <c r="BE4" s="3">
-        <v>19.928579330444339</v>
+        <v>23.335540771484379</v>
       </c>
       <c r="BF4" s="3">
-        <v>23.335540771484379</v>
+        <v>17.854013442993161</v>
       </c>
       <c r="BG4" s="3">
-        <v>17.854013442993161</v>
-      </c>
-      <c r="BH4" s="3">
         <v>35.358219146728523</v>
       </c>
     </row>
-    <row r="5" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>45296</v>
       </c>
@@ -1517,28 +1505,25 @@
         <v>11.48001194000244</v>
       </c>
       <c r="BB5" s="3">
-        <v>3.0607631206512451</v>
+        <v>8.6226062774658203</v>
       </c>
       <c r="BC5" s="3">
-        <v>8.6226062774658203</v>
+        <v>65.759124755859375</v>
       </c>
       <c r="BD5" s="3">
-        <v>65.759124755859375</v>
+        <v>20.29301834106445</v>
       </c>
       <c r="BE5" s="3">
-        <v>20.29301834106445</v>
+        <v>22.91340255737305</v>
       </c>
       <c r="BF5" s="3">
-        <v>22.91340255737305</v>
+        <v>17.751352310180661</v>
       </c>
       <c r="BG5" s="3">
-        <v>17.751352310180661</v>
-      </c>
-      <c r="BH5" s="3">
         <v>34.978965759277337</v>
       </c>
     </row>
-    <row r="6" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>45299</v>
       </c>
@@ -1699,28 +1684,25 @@
         <v>11.83536911010742</v>
       </c>
       <c r="BB6" s="3">
-        <v>3.0874559879302979</v>
+        <v>8.564605712890625</v>
       </c>
       <c r="BC6" s="3">
-        <v>8.564605712890625</v>
+        <v>65.42437744140625</v>
       </c>
       <c r="BD6" s="3">
-        <v>65.42437744140625</v>
+        <v>20.29301834106445</v>
       </c>
       <c r="BE6" s="3">
-        <v>20.29301834106445</v>
+        <v>22.69553184509277</v>
       </c>
       <c r="BF6" s="3">
-        <v>22.69553184509277</v>
+        <v>17.777017593383789</v>
       </c>
       <c r="BG6" s="3">
-        <v>17.777017593383789</v>
-      </c>
-      <c r="BH6" s="3">
         <v>35.066482543945313</v>
       </c>
     </row>
-    <row r="7" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>45300</v>
       </c>
@@ -1881,28 +1863,25 @@
         <v>10.868007659912109</v>
       </c>
       <c r="BB7" s="3">
-        <v>3.0874559879302979</v>
+        <v>8.3422746658325195</v>
       </c>
       <c r="BC7" s="3">
-        <v>8.3422746658325195</v>
+        <v>64.596343994140625</v>
       </c>
       <c r="BD7" s="3">
-        <v>64.596343994140625</v>
+        <v>19.999689102172852</v>
       </c>
       <c r="BE7" s="3">
-        <v>19.999689102172852</v>
+        <v>22.799924850463871</v>
       </c>
       <c r="BF7" s="3">
-        <v>22.799924850463871</v>
+        <v>17.546035766601559</v>
       </c>
       <c r="BG7" s="3">
-        <v>17.546035766601559</v>
-      </c>
-      <c r="BH7" s="3">
         <v>34.201011657714837</v>
       </c>
     </row>
-    <row r="8" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>45301</v>
       </c>
@@ -2063,28 +2042,25 @@
         <v>10.99633121490479</v>
       </c>
       <c r="BB8" s="3">
-        <v>3.076778650283813</v>
+        <v>8.1199426651000977</v>
       </c>
       <c r="BC8" s="3">
-        <v>8.1199426651000977</v>
+        <v>63.627349853515618</v>
       </c>
       <c r="BD8" s="3">
-        <v>63.627349853515618</v>
+        <v>20.159685134887699</v>
       </c>
       <c r="BE8" s="3">
-        <v>20.159685134887699</v>
+        <v>22.97695350646973</v>
       </c>
       <c r="BF8" s="3">
-        <v>22.97695350646973</v>
+        <v>17.60592079162598</v>
       </c>
       <c r="BG8" s="3">
-        <v>17.60592079162598</v>
-      </c>
-      <c r="BH8" s="3">
         <v>34.346870422363281</v>
       </c>
     </row>
-    <row r="9" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>45302</v>
       </c>
@@ -2245,28 +2221,25 @@
         <v>10.177036285400391</v>
       </c>
       <c r="BB9" s="3">
-        <v>3.0287315845489502</v>
+        <v>8.2359418869018555</v>
       </c>
       <c r="BC9" s="3">
-        <v>8.2359418869018555</v>
+        <v>63.962085723876953</v>
       </c>
       <c r="BD9" s="3">
-        <v>63.962085723876953</v>
+        <v>19.9730224609375</v>
       </c>
       <c r="BE9" s="3">
-        <v>19.9730224609375</v>
+        <v>22.849855422973629</v>
       </c>
       <c r="BF9" s="3">
-        <v>22.849855422973629</v>
+        <v>17.366386413574219</v>
       </c>
       <c r="BG9" s="3">
-        <v>17.366386413574219</v>
-      </c>
-      <c r="BH9" s="3">
         <v>33.860652923583977</v>
       </c>
     </row>
-    <row r="10" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>45303</v>
       </c>
@@ -2427,28 +2400,25 @@
         <v>9.9894857406616211</v>
       </c>
       <c r="BB10" s="3">
-        <v>3.0643212795257568</v>
+        <v>8.1876087188720703</v>
       </c>
       <c r="BC10" s="3">
-        <v>8.1876087188720703</v>
+        <v>63.151664733886719</v>
       </c>
       <c r="BD10" s="3">
-        <v>63.151664733886719</v>
+        <v>20.515237808227539</v>
       </c>
       <c r="BE10" s="3">
-        <v>20.515237808227539</v>
+        <v>23.045038223266602</v>
       </c>
       <c r="BF10" s="3">
-        <v>23.045038223266602</v>
+        <v>17.409160614013668</v>
       </c>
       <c r="BG10" s="3">
-        <v>17.409160614013668</v>
-      </c>
-      <c r="BH10" s="3">
         <v>33.71478271484375</v>
       </c>
     </row>
-    <row r="11" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>45306</v>
       </c>
@@ -2609,28 +2579,25 @@
         <v>10.00922870635986</v>
       </c>
       <c r="BB11" s="3">
-        <v>3.1070306301116939</v>
+        <v>8.255274772644043</v>
       </c>
       <c r="BC11" s="3">
-        <v>8.255274772644043</v>
+        <v>63.028335571289063</v>
       </c>
       <c r="BD11" s="3">
-        <v>63.028335571289063</v>
+        <v>20.45301628112793</v>
       </c>
       <c r="BE11" s="3">
-        <v>20.45301628112793</v>
+        <v>23.008726119995121</v>
       </c>
       <c r="BF11" s="3">
-        <v>23.008726119995121</v>
+        <v>17.614475250244141</v>
       </c>
       <c r="BG11" s="3">
-        <v>17.614475250244141</v>
-      </c>
-      <c r="BH11" s="3">
         <v>33.374427795410163</v>
       </c>
     </row>
-    <row r="12" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>45307</v>
       </c>
@@ -2791,28 +2758,25 @@
         <v>9.9993572235107422</v>
       </c>
       <c r="BB12" s="3">
-        <v>3.0518653392791748</v>
+        <v>8.0909423828125</v>
       </c>
       <c r="BC12" s="3">
-        <v>8.0909423828125</v>
+        <v>62.209102630615227</v>
       </c>
       <c r="BD12" s="3">
-        <v>62.209102630615227</v>
+        <v>19.741912841796879</v>
       </c>
       <c r="BE12" s="3">
-        <v>19.741912841796879</v>
+        <v>22.999650955200199</v>
       </c>
       <c r="BF12" s="3">
-        <v>22.999650955200199</v>
+        <v>17.37493896484375</v>
       </c>
       <c r="BG12" s="3">
-        <v>17.37493896484375</v>
-      </c>
-      <c r="BH12" s="3">
         <v>32.683986663818359</v>
       </c>
     </row>
-    <row r="13" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>45308</v>
       </c>
@@ -2973,28 +2937,25 @@
         <v>9.9006462097167969</v>
       </c>
       <c r="BB13" s="3">
-        <v>3.09635329246521</v>
+        <v>8.0136098861694336</v>
       </c>
       <c r="BC13" s="3">
-        <v>8.0136098861694336</v>
+        <v>61.090358734130859</v>
       </c>
       <c r="BD13" s="3">
-        <v>61.090358734130859</v>
+        <v>19.86635780334473</v>
       </c>
       <c r="BE13" s="3">
-        <v>19.86635780334473</v>
+        <v>23.131280899047852</v>
       </c>
       <c r="BF13" s="3">
-        <v>23.131280899047852</v>
+        <v>17.323610305786129</v>
       </c>
       <c r="BG13" s="3">
-        <v>17.323610305786129</v>
-      </c>
-      <c r="BH13" s="3">
         <v>32.479774475097663</v>
       </c>
     </row>
-    <row r="14" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>45309</v>
       </c>
@@ -3155,28 +3116,25 @@
         <v>9.4268369674682617</v>
       </c>
       <c r="BB14" s="3">
-        <v>3.09635329246521</v>
+        <v>8.2359418869018555</v>
       </c>
       <c r="BC14" s="3">
-        <v>8.2359418869018555</v>
+        <v>60.782047271728523</v>
       </c>
       <c r="BD14" s="3">
-        <v>60.782047271728523</v>
+        <v>19.733026504516602</v>
       </c>
       <c r="BE14" s="3">
-        <v>19.733026504516602</v>
+        <v>22.97695350646973</v>
       </c>
       <c r="BF14" s="3">
-        <v>22.97695350646973</v>
+        <v>17.494707107543949</v>
       </c>
       <c r="BG14" s="3">
-        <v>17.494707107543949</v>
-      </c>
-      <c r="BH14" s="3">
         <v>32.226932525634773</v>
       </c>
     </row>
-    <row r="15" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>45310</v>
       </c>
@@ -3337,28 +3295,25 @@
         <v>9.693354606628418</v>
       </c>
       <c r="BB15" s="3">
-        <v>3.1355025768280029</v>
+        <v>8.216609001159668</v>
       </c>
       <c r="BC15" s="3">
-        <v>8.216609001159668</v>
+        <v>59.989231109619141</v>
       </c>
       <c r="BD15" s="3">
-        <v>59.989231109619141</v>
+        <v>20.159685134887699</v>
       </c>
       <c r="BE15" s="3">
-        <v>20.159685134887699</v>
+        <v>22.990571975708011</v>
       </c>
       <c r="BF15" s="3">
-        <v>22.990571975708011</v>
+        <v>17.88823127746582</v>
       </c>
       <c r="BG15" s="3">
-        <v>17.88823127746582</v>
-      </c>
-      <c r="BH15" s="3">
         <v>32.557571411132813</v>
       </c>
     </row>
-    <row r="16" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>45313</v>
       </c>
@@ -3519,28 +3474,25 @@
         <v>9.6341285705566406</v>
       </c>
       <c r="BB16" s="3">
-        <v>3.1141481399536128</v>
+        <v>8.3132753372192383</v>
       </c>
       <c r="BC16" s="3">
-        <v>8.3132753372192383</v>
+        <v>59.724964141845703</v>
       </c>
       <c r="BD16" s="3">
-        <v>59.724964141845703</v>
+        <v>20.275239944458011</v>
       </c>
       <c r="BE16" s="3">
-        <v>20.275239944458011</v>
+        <v>23.076812744140621</v>
       </c>
       <c r="BF16" s="3">
-        <v>23.076812744140621</v>
+        <v>17.717134475708011</v>
       </c>
       <c r="BG16" s="3">
-        <v>17.717134475708011</v>
-      </c>
-      <c r="BH16" s="3">
         <v>32.460330963134773</v>
       </c>
     </row>
-    <row r="17" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>45314</v>
       </c>
@@ -3701,28 +3653,25 @@
         <v>9.7130966186523438</v>
       </c>
       <c r="BB17" s="3">
-        <v>3.1052508354187012</v>
+        <v>8.3519411087036133</v>
       </c>
       <c r="BC17" s="3">
-        <v>8.3519411087036133</v>
+        <v>60.958221435546882</v>
       </c>
       <c r="BD17" s="3">
-        <v>60.958221435546882</v>
+        <v>20.45301628112793</v>
       </c>
       <c r="BE17" s="3">
-        <v>20.45301628112793</v>
+        <v>23.104045867919918</v>
       </c>
       <c r="BF17" s="3">
-        <v>23.104045867919918</v>
+        <v>18.324531555175781</v>
       </c>
       <c r="BG17" s="3">
-        <v>18.324531555175781</v>
-      </c>
-      <c r="BH17" s="3">
         <v>32.839576721191413</v>
       </c>
     </row>
-    <row r="18" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>45315</v>
       </c>
@@ -3883,28 +3832,25 @@
         <v>9.7525815963745117</v>
       </c>
       <c r="BB18" s="3">
-        <v>3.101691722869873</v>
+        <v>8.6709394454956055</v>
       </c>
       <c r="BC18" s="3">
-        <v>8.6709394454956055</v>
+        <v>61.574851989746087</v>
       </c>
       <c r="BD18" s="3">
-        <v>61.574851989746087</v>
+        <v>20.76412200927734</v>
       </c>
       <c r="BE18" s="3">
-        <v>20.76412200927734</v>
+        <v>23.022340774536129</v>
       </c>
       <c r="BF18" s="3">
-        <v>23.022340774536129</v>
+        <v>18.538400650024411</v>
       </c>
       <c r="BG18" s="3">
-        <v>18.538400650024411</v>
-      </c>
-      <c r="BH18" s="3">
         <v>32.547847747802727</v>
       </c>
     </row>
-    <row r="19" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>45316</v>
       </c>
@@ -4065,28 +4011,25 @@
         <v>10.52252101898193</v>
       </c>
       <c r="BB19" s="3">
-        <v>3.0945734977722168</v>
+        <v>8.728938102722168</v>
       </c>
       <c r="BC19" s="3">
-        <v>8.728938102722168</v>
+        <v>60.059700012207031</v>
       </c>
       <c r="BD19" s="3">
-        <v>60.059700012207031</v>
+        <v>20.746345520019531</v>
       </c>
       <c r="BE19" s="3">
-        <v>20.746345520019531</v>
+        <v>23.03596115112305</v>
       </c>
       <c r="BF19" s="3">
-        <v>23.03596115112305</v>
+        <v>19.111577987670898</v>
       </c>
       <c r="BG19" s="3">
-        <v>19.111577987670898</v>
-      </c>
-      <c r="BH19" s="3">
         <v>32.333904266357422</v>
       </c>
     </row>
-    <row r="20" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>45317</v>
       </c>
@@ -4247,28 +4190,25 @@
         <v>10.23626136779785</v>
       </c>
       <c r="BB20" s="3">
-        <v>3.117707252502441</v>
+        <v>9.1832685470581055</v>
       </c>
       <c r="BC20" s="3">
-        <v>9.1832685470581055</v>
+        <v>61.222496032714837</v>
       </c>
       <c r="BD20" s="3">
-        <v>61.222496032714837</v>
+        <v>20.648569107055661</v>
       </c>
       <c r="BE20" s="3">
-        <v>20.648569107055661</v>
+        <v>23.2402229309082</v>
       </c>
       <c r="BF20" s="3">
-        <v>23.2402229309082</v>
+        <v>18.48707389831543</v>
       </c>
       <c r="BG20" s="3">
-        <v>18.48707389831543</v>
-      </c>
-      <c r="BH20" s="3">
         <v>32.256099700927727</v>
       </c>
     </row>
-    <row r="21" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>45320</v>
       </c>
@@ -4429,28 +4369,25 @@
         <v>9.9993572235107422</v>
       </c>
       <c r="BB21" s="3">
-        <v>3.1070306301116939</v>
+        <v>8.9899368286132813</v>
       </c>
       <c r="BC21" s="3">
-        <v>8.9899368286132813</v>
+        <v>60.931793212890618</v>
       </c>
       <c r="BD21" s="3">
-        <v>60.931793212890618</v>
+        <v>20.45301628112793</v>
       </c>
       <c r="BE21" s="3">
-        <v>20.45301628112793</v>
+        <v>23.140363693237301</v>
       </c>
       <c r="BF21" s="3">
-        <v>23.140363693237301</v>
+        <v>17.99089241027832</v>
       </c>
       <c r="BG21" s="3">
-        <v>17.99089241027832</v>
-      </c>
-      <c r="BH21" s="3">
         <v>32.333904266357422</v>
       </c>
     </row>
-    <row r="22" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>45321</v>
       </c>
@@ -4611,28 +4548,25 @@
         <v>9.584773063659668</v>
       </c>
       <c r="BB22" s="3">
-        <v>3.0536448955535889</v>
+        <v>8.7869377136230469</v>
       </c>
       <c r="BC22" s="3">
-        <v>8.7869377136230469</v>
+        <v>60.588241577148438</v>
       </c>
       <c r="BD22" s="3">
-        <v>60.588241577148438</v>
+        <v>20.746345520019531</v>
       </c>
       <c r="BE22" s="3">
-        <v>20.746345520019531</v>
+        <v>23.094970703125</v>
       </c>
       <c r="BF22" s="3">
-        <v>23.094970703125</v>
+        <v>17.392049789428711</v>
       </c>
       <c r="BG22" s="3">
-        <v>17.392049789428711</v>
-      </c>
-      <c r="BH22" s="3">
         <v>32.081066131591797</v>
       </c>
     </row>
-    <row r="23" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>45322</v>
       </c>
@@ -4793,28 +4727,25 @@
         <v>9.8315496444702148</v>
       </c>
       <c r="BB23" s="3">
-        <v>3.085675716400146</v>
+        <v>8.8836030960083008</v>
       </c>
       <c r="BC23" s="3">
-        <v>8.8836030960083008</v>
+        <v>59.689727783203118</v>
       </c>
       <c r="BD23" s="3">
-        <v>59.689727783203118</v>
+        <v>21.110782623291019</v>
       </c>
       <c r="BE23" s="3">
-        <v>21.110782623291019</v>
+        <v>23.312845230102539</v>
       </c>
       <c r="BF23" s="3">
-        <v>23.312845230102539</v>
+        <v>17.56314659118652</v>
       </c>
       <c r="BG23" s="3">
-        <v>17.56314659118652</v>
-      </c>
-      <c r="BH23" s="3">
         <v>31.448974609375</v>
       </c>
     </row>
-    <row r="24" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>45323</v>
       </c>
@@ -4975,28 +4906,25 @@
         <v>9.801936149597168</v>
       </c>
       <c r="BB24" s="3">
-        <v>3.1444001197814941</v>
+        <v>8.9222698211669922</v>
       </c>
       <c r="BC24" s="3">
-        <v>8.9222698211669922</v>
+        <v>59.416645050048828</v>
       </c>
       <c r="BD24" s="3">
-        <v>59.416645050048828</v>
+        <v>20.870784759521481</v>
       </c>
       <c r="BE24" s="3">
-        <v>20.870784759521481</v>
+        <v>23.793991088867191</v>
       </c>
       <c r="BF24" s="3">
-        <v>23.793991088867191</v>
+        <v>18.418632507324219</v>
       </c>
       <c r="BG24" s="3">
-        <v>18.418632507324219</v>
-      </c>
-      <c r="BH24" s="3">
         <v>31.730985641479489</v>
       </c>
     </row>
-    <row r="25" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>45324</v>
       </c>
@@ -5157,28 +5085,25 @@
         <v>9.4465789794921875</v>
       </c>
       <c r="BB25" s="3">
-        <v>3.149739027023315</v>
+        <v>8.7869377136230469</v>
       </c>
       <c r="BC25" s="3">
-        <v>8.7869377136230469</v>
+        <v>58.209815979003913</v>
       </c>
       <c r="BD25" s="3">
-        <v>58.209815979003913</v>
+        <v>20.737455368041989</v>
       </c>
       <c r="BE25" s="3">
-        <v>20.737455368041989</v>
+        <v>23.78945159912109</v>
       </c>
       <c r="BF25" s="3">
-        <v>23.78945159912109</v>
+        <v>18.410079956054691</v>
       </c>
       <c r="BG25" s="3">
-        <v>18.410079956054691</v>
-      </c>
-      <c r="BH25" s="3">
         <v>31.692087173461911</v>
       </c>
     </row>
-    <row r="26" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>45327</v>
       </c>
@@ -5339,28 +5264,25 @@
         <v>9.2985134124755859</v>
       </c>
       <c r="BB26" s="3">
-        <v>3.183549165725708</v>
+        <v>8.7869377136230469</v>
       </c>
       <c r="BC26" s="3">
-        <v>8.7869377136230469</v>
+        <v>57.70770263671875</v>
       </c>
       <c r="BD26" s="3">
-        <v>57.70770263671875</v>
+        <v>21.03078460693359</v>
       </c>
       <c r="BE26" s="3">
-        <v>21.03078460693359</v>
+        <v>24.002790451049801</v>
       </c>
       <c r="BF26" s="3">
-        <v>24.002790451049801</v>
+        <v>17.922452926635739</v>
       </c>
       <c r="BG26" s="3">
-        <v>17.922452926635739</v>
-      </c>
-      <c r="BH26" s="3">
         <v>32.343624114990227</v>
       </c>
     </row>
-    <row r="27" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>45328</v>
       </c>
@@ -5521,28 +5443,25 @@
         <v>9.6242580413818359</v>
       </c>
       <c r="BB27" s="3">
-        <v>3.2280371189117432</v>
+        <v>8.9126043319702148</v>
       </c>
       <c r="BC27" s="3">
-        <v>8.9126043319702148</v>
+        <v>58.729545593261719</v>
       </c>
       <c r="BD27" s="3">
-        <v>58.729545593261719</v>
+        <v>21.288557052612301</v>
       </c>
       <c r="BE27" s="3">
-        <v>21.288557052612301</v>
+        <v>24.45670127868652</v>
       </c>
       <c r="BF27" s="3">
-        <v>24.45670127868652</v>
+        <v>18.427186965942379</v>
       </c>
       <c r="BG27" s="3">
-        <v>18.427186965942379</v>
-      </c>
-      <c r="BH27" s="3">
         <v>32.324180603027337</v>
       </c>
     </row>
-    <row r="28" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>45329</v>
       </c>
@@ -5703,28 +5622,25 @@
         <v>9.8512907028198242</v>
       </c>
       <c r="BB28" s="3">
-        <v>3.242273092269897</v>
+        <v>9.0189361572265625</v>
       </c>
       <c r="BC28" s="3">
-        <v>9.0189361572265625</v>
+        <v>58.844066619873047</v>
       </c>
       <c r="BD28" s="3">
-        <v>58.844066619873047</v>
+        <v>21.297445297241211</v>
       </c>
       <c r="BE28" s="3">
-        <v>21.297445297241211</v>
+        <v>24.461238861083981</v>
       </c>
       <c r="BF28" s="3">
-        <v>24.461238861083981</v>
+        <v>18.050773620605469</v>
       </c>
       <c r="BG28" s="3">
-        <v>18.050773620605469</v>
-      </c>
-      <c r="BH28" s="3">
         <v>32.703437805175781</v>
       </c>
     </row>
-    <row r="29" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>45330</v>
       </c>
@@ -5885,28 +5801,25 @@
         <v>9.584773063659668</v>
       </c>
       <c r="BB29" s="3">
-        <v>3.279643058776855</v>
+        <v>9.0866022109985352</v>
       </c>
       <c r="BC29" s="3">
-        <v>9.0866022109985352</v>
+        <v>58.324329376220703</v>
       </c>
       <c r="BD29" s="3">
-        <v>58.324329376220703</v>
+        <v>21.208560943603519</v>
       </c>
       <c r="BE29" s="3">
-        <v>21.208560943603519</v>
+        <v>24.365921020507809</v>
       </c>
       <c r="BF29" s="3">
-        <v>24.365921020507809</v>
+        <v>17.058408737182621</v>
       </c>
       <c r="BG29" s="3">
-        <v>17.058408737182621</v>
-      </c>
-      <c r="BH29" s="3">
         <v>32.868755340576172</v>
       </c>
     </row>
-    <row r="30" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>45331</v>
       </c>
@@ -6067,28 +5980,25 @@
         <v>10.186905860900881</v>
       </c>
       <c r="BB30" s="3">
-        <v>3.2707452774047852</v>
+        <v>8.9706029891967773</v>
       </c>
       <c r="BC30" s="3">
-        <v>8.9706029891967773</v>
+        <v>58.068874359130859</v>
       </c>
       <c r="BD30" s="3">
-        <v>58.068874359130859</v>
+        <v>21.821882247924801</v>
       </c>
       <c r="BE30" s="3">
-        <v>21.821882247924801</v>
+        <v>24.356838226318359</v>
       </c>
       <c r="BF30" s="3">
-        <v>24.356838226318359</v>
+        <v>16.998525619506839</v>
       </c>
       <c r="BG30" s="3">
-        <v>16.998525619506839</v>
-      </c>
-      <c r="BH30" s="3">
         <v>32.450595855712891</v>
       </c>
     </row>
-    <row r="31" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>45336</v>
       </c>
@@ -6249,28 +6159,25 @@
         <v>9.9598731994628906</v>
       </c>
       <c r="BB31" s="3">
-        <v>3.2707452774047852</v>
+        <v>9.0479354858398438</v>
       </c>
       <c r="BC31" s="3">
-        <v>9.0479354858398438</v>
+        <v>57.892696380615227</v>
       </c>
       <c r="BD31" s="3">
-        <v>57.892696380615227</v>
+        <v>21.208560943603519</v>
       </c>
       <c r="BE31" s="3">
-        <v>21.208560943603519</v>
+        <v>24.733589172363281</v>
       </c>
       <c r="BF31" s="3">
-        <v>24.733589172363281</v>
+        <v>16.78465461730957</v>
       </c>
       <c r="BG31" s="3">
-        <v>16.78465461730957</v>
-      </c>
-      <c r="BH31" s="3">
         <v>32.606193542480469</v>
       </c>
     </row>
-    <row r="32" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>45337</v>
       </c>
@@ -6431,28 +6338,25 @@
         <v>9.910517692565918</v>
       </c>
       <c r="BB32" s="3">
-        <v>3.2191393375396729</v>
+        <v>9.5505990982055664</v>
       </c>
       <c r="BC32" s="3">
-        <v>9.5505990982055664</v>
+        <v>57.70770263671875</v>
       </c>
       <c r="BD32" s="3">
-        <v>57.70770263671875</v>
+        <v>21.15522384643555</v>
       </c>
       <c r="BE32" s="3">
-        <v>21.15522384643555</v>
+        <v>24.524785995483398</v>
       </c>
       <c r="BF32" s="3">
-        <v>24.524785995483398</v>
+        <v>16.374019622802731</v>
       </c>
       <c r="BG32" s="3">
-        <v>16.374019622802731</v>
-      </c>
-      <c r="BH32" s="3">
         <v>32.295009613037109</v>
       </c>
     </row>
-    <row r="33" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>45338</v>
       </c>
@@ -6613,28 +6517,25 @@
         <v>10.404068946838381</v>
       </c>
       <c r="BB33" s="3">
-        <v>3.09635329246521</v>
+        <v>9.7729310989379883</v>
       </c>
       <c r="BC33" s="3">
-        <v>9.7729310989379883</v>
+        <v>59.901145935058587</v>
       </c>
       <c r="BD33" s="3">
-        <v>59.901145935058587</v>
+        <v>21.564107894897461</v>
       </c>
       <c r="BE33" s="3">
-        <v>21.564107894897461</v>
+        <v>23.90293121337891</v>
       </c>
       <c r="BF33" s="3">
-        <v>23.90293121337891</v>
+        <v>16.758991241455082</v>
       </c>
       <c r="BG33" s="3">
-        <v>16.758991241455082</v>
-      </c>
-      <c r="BH33" s="3">
         <v>32.479774475097663</v>
       </c>
     </row>
-    <row r="34" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>45341</v>
       </c>
@@ -6795,28 +6696,25 @@
         <v>10.581748008728029</v>
       </c>
       <c r="BB34" s="3">
-        <v>3.1105887889862061</v>
+        <v>9.8212642669677734</v>
       </c>
       <c r="BC34" s="3">
-        <v>9.8212642669677734</v>
+        <v>59.451881408691413</v>
       </c>
       <c r="BD34" s="3">
-        <v>59.451881408691413</v>
+        <v>21.333000183105469</v>
       </c>
       <c r="BE34" s="3">
-        <v>21.333000183105469</v>
+        <v>23.993717193603519</v>
       </c>
       <c r="BF34" s="3">
-        <v>23.993717193603519</v>
+        <v>16.938640594482418</v>
       </c>
       <c r="BG34" s="3">
-        <v>16.938640594482418</v>
-      </c>
-      <c r="BH34" s="3">
         <v>32.567291259765618</v>
       </c>
     </row>
-    <row r="35" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>45342</v>
       </c>
@@ -6977,28 +6875,25 @@
         <v>10.99633121490479</v>
       </c>
       <c r="BB35" s="3">
-        <v>3.1337227821350102</v>
+        <v>9.985595703125</v>
       </c>
       <c r="BC35" s="3">
-        <v>9.985595703125</v>
+        <v>58.148155212402337</v>
       </c>
       <c r="BD35" s="3">
-        <v>58.148155212402337</v>
+        <v>22.124099731445309</v>
       </c>
       <c r="BE35" s="3">
-        <v>22.124099731445309</v>
+        <v>24.02548980712891</v>
       </c>
       <c r="BF35" s="3">
-        <v>24.02548980712891</v>
+        <v>16.433904647827148</v>
       </c>
       <c r="BG35" s="3">
-        <v>16.433904647827148</v>
-      </c>
-      <c r="BH35" s="3">
         <v>33.3258056640625</v>
       </c>
     </row>
-    <row r="36" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>45343</v>
       </c>
@@ -7159,28 +7054,25 @@
         <v>10.59161853790283</v>
       </c>
       <c r="BB36" s="3">
-        <v>3.1746516227722168</v>
+        <v>10.0049295425415</v>
       </c>
       <c r="BC36" s="3">
-        <v>10.0049295425415</v>
+        <v>58.588603973388672</v>
       </c>
       <c r="BD36" s="3">
-        <v>58.588603973388672</v>
+        <v>22.675201416015621</v>
       </c>
       <c r="BE36" s="3">
-        <v>22.675201416015621</v>
+        <v>24.338685989379879</v>
       </c>
       <c r="BF36" s="3">
-        <v>24.338685989379879</v>
+        <v>16.297025680541989</v>
       </c>
       <c r="BG36" s="3">
-        <v>16.297025680541989</v>
-      </c>
-      <c r="BH36" s="3">
         <v>35.620780944824219</v>
       </c>
     </row>
-    <row r="37" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>45344</v>
       </c>
@@ -7341,28 +7233,25 @@
         <v>11.15426826477051</v>
       </c>
       <c r="BB37" s="3">
-        <v>3.2974379062652588</v>
+        <v>10.29492664337158</v>
       </c>
       <c r="BC37" s="3">
-        <v>10.29492664337158</v>
+        <v>59.214038848876953</v>
       </c>
       <c r="BD37" s="3">
-        <v>59.214038848876953</v>
+        <v>22.986310958862301</v>
       </c>
       <c r="BE37" s="3">
-        <v>22.986310958862301</v>
+        <v>25.500692367553711</v>
       </c>
       <c r="BF37" s="3">
-        <v>25.500692367553711</v>
+        <v>16.545114517211911</v>
       </c>
       <c r="BG37" s="3">
-        <v>16.545114517211911</v>
-      </c>
-      <c r="BH37" s="3">
         <v>34.492740631103523</v>
       </c>
     </row>
-    <row r="38" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>45345</v>
       </c>
@@ -7523,28 +7412,25 @@
         <v>10.91736316680908</v>
       </c>
       <c r="BB38" s="3">
-        <v>3.2707452774047852</v>
+        <v>10.343259811401371</v>
       </c>
       <c r="BC38" s="3">
-        <v>10.343259811401371</v>
+        <v>59.35498046875</v>
       </c>
       <c r="BD38" s="3">
-        <v>59.35498046875</v>
+        <v>22.888532638549801</v>
       </c>
       <c r="BE38" s="3">
-        <v>22.888532638549801</v>
+        <v>25.105794906616211</v>
       </c>
       <c r="BF38" s="3">
-        <v>25.105794906616211</v>
+        <v>16.18581390380859</v>
       </c>
       <c r="BG38" s="3">
-        <v>16.18581390380859</v>
-      </c>
-      <c r="BH38" s="3">
         <v>34.988685607910163</v>
       </c>
     </row>
-    <row r="39" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>45348</v>
       </c>
@@ -7705,28 +7591,25 @@
         <v>10.87787914276123</v>
       </c>
       <c r="BB39" s="3">
-        <v>3.2707452774047852</v>
+        <v>10.314260482788089</v>
       </c>
       <c r="BC39" s="3">
-        <v>10.314260482788089</v>
+        <v>57.919116973876953</v>
       </c>
       <c r="BD39" s="3">
-        <v>57.919116973876953</v>
+        <v>23.0218620300293</v>
       </c>
       <c r="BE39" s="3">
-        <v>23.0218620300293</v>
+        <v>24.828910827636719</v>
       </c>
       <c r="BF39" s="3">
-        <v>24.828910827636719</v>
+        <v>16.288471221923832</v>
       </c>
       <c r="BG39" s="3">
-        <v>16.288471221923832</v>
-      </c>
-      <c r="BH39" s="3">
         <v>35.859371185302727</v>
       </c>
     </row>
-    <row r="40" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>45349</v>
       </c>
@@ -7887,28 +7770,25 @@
         <v>11.44052791595459</v>
       </c>
       <c r="BB40" s="3">
-        <v>3.3365874290466309</v>
+        <v>10.478592872619631</v>
       </c>
       <c r="BC40" s="3">
-        <v>10.478592872619631</v>
+        <v>59.443077087402337</v>
       </c>
       <c r="BD40" s="3">
-        <v>59.443077087402337</v>
+        <v>23.075197219848629</v>
       </c>
       <c r="BE40" s="3">
-        <v>23.075197219848629</v>
+        <v>25.627792358398441</v>
       </c>
       <c r="BF40" s="3">
-        <v>25.627792358398441</v>
+        <v>16.639223098754879</v>
       </c>
       <c r="BG40" s="3">
-        <v>16.639223098754879</v>
-      </c>
-      <c r="BH40" s="3">
         <v>36.241802215576172</v>
       </c>
     </row>
-    <row r="41" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>45350</v>
       </c>
@@ -8069,28 +7949,25 @@
         <v>11.00620174407959</v>
       </c>
       <c r="BB41" s="3">
-        <v>3.354382991790771</v>
+        <v>10.58492469787598</v>
       </c>
       <c r="BC41" s="3">
-        <v>10.58492469787598</v>
+        <v>58.791206359863281</v>
       </c>
       <c r="BD41" s="3">
-        <v>58.791206359863281</v>
+        <v>23.190750122070309</v>
       </c>
       <c r="BE41" s="3">
-        <v>23.190750122070309</v>
+        <v>25.291896820068359</v>
       </c>
       <c r="BF41" s="3">
-        <v>25.291896820068359</v>
+        <v>16.40823936462402</v>
       </c>
       <c r="BG41" s="3">
-        <v>16.40823936462402</v>
-      </c>
-      <c r="BH41" s="3">
         <v>36.192771911621087</v>
       </c>
     </row>
-    <row r="42" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>45351</v>
       </c>
@@ -8251,28 +8128,25 @@
         <v>10.67058753967285</v>
       </c>
       <c r="BB42" s="3">
-        <v>3.2333755493164058</v>
+        <v>10.700923919677731</v>
       </c>
       <c r="BC42" s="3">
-        <v>10.700923919677731</v>
+        <v>59.011440277099609</v>
       </c>
       <c r="BD42" s="3">
-        <v>59.011440277099609</v>
+        <v>22.986310958862301</v>
       </c>
       <c r="BE42" s="3">
-        <v>22.986310958862301</v>
+        <v>24.729045867919918</v>
       </c>
       <c r="BF42" s="3">
-        <v>24.729045867919918</v>
+        <v>15.98905086517334</v>
       </c>
       <c r="BG42" s="3">
-        <v>15.98905086517334</v>
-      </c>
-      <c r="BH42" s="3">
         <v>35.97705078125</v>
       </c>
     </row>
-    <row r="43" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>45352</v>
       </c>
@@ -8433,28 +8307,25 @@
         <v>10.44355297088623</v>
       </c>
       <c r="BB43" s="3">
-        <v>3.2760837078094478</v>
+        <v>10.739590644836429</v>
       </c>
       <c r="BC43" s="3">
-        <v>10.739590644836429</v>
+        <v>58.914531707763672</v>
       </c>
       <c r="BD43" s="3">
-        <v>58.914531707763672</v>
+        <v>23.644077301025391</v>
       </c>
       <c r="BE43" s="3">
-        <v>23.644077301025391</v>
+        <v>24.50662994384766</v>
       </c>
       <c r="BF43" s="3">
-        <v>24.50662994384766</v>
+        <v>16.22858810424805</v>
       </c>
       <c r="BG43" s="3">
-        <v>16.22858810424805</v>
-      </c>
-      <c r="BH43" s="3">
         <v>36.565387725830078</v>
       </c>
     </row>
-    <row r="44" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>45355</v>
       </c>
@@ -8615,28 +8486,25 @@
         <v>9.9401302337646484</v>
       </c>
       <c r="BB44" s="3">
-        <v>3.2298164367675781</v>
+        <v>10.343259811401371</v>
       </c>
       <c r="BC44" s="3">
-        <v>10.343259811401371</v>
+        <v>58.78240966796875</v>
       </c>
       <c r="BD44" s="3">
-        <v>58.78240966796875</v>
+        <v>23.608522415161129</v>
       </c>
       <c r="BE44" s="3">
-        <v>23.608522415161129</v>
+        <v>23.830305099487301</v>
       </c>
       <c r="BF44" s="3">
-        <v>23.830305099487301</v>
+        <v>15.87783718109131</v>
       </c>
       <c r="BG44" s="3">
-        <v>15.87783718109131</v>
-      </c>
-      <c r="BH44" s="3">
         <v>36.418300628662109</v>
       </c>
     </row>
-    <row r="45" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>45356</v>
       </c>
@@ -8797,28 +8665,25 @@
         <v>10.285616874694821</v>
       </c>
       <c r="BB45" s="3">
-        <v>3.1871082782745361</v>
+        <v>10.38192653656006</v>
       </c>
       <c r="BC45" s="3">
-        <v>10.38192653656006</v>
+        <v>58.007209777832031</v>
       </c>
       <c r="BD45" s="3">
-        <v>58.007209777832031</v>
+        <v>22.31076622009277</v>
       </c>
       <c r="BE45" s="3">
-        <v>22.31076622009277</v>
+        <v>23.635124206542969</v>
       </c>
       <c r="BF45" s="3">
-        <v>23.635124206542969</v>
+        <v>15.698184967041019</v>
       </c>
       <c r="BG45" s="3">
-        <v>15.698184967041019</v>
-      </c>
-      <c r="BH45" s="3">
         <v>36.702667236328118</v>
       </c>
     </row>
-    <row r="46" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>45357</v>
       </c>
@@ -8979,28 +8844,25 @@
         <v>10.48303699493408</v>
       </c>
       <c r="BB46" s="3">
-        <v>3.2262578010559082</v>
+        <v>10.391592979431151</v>
       </c>
       <c r="BC46" s="3">
-        <v>10.391592979431151</v>
+        <v>58.800014495849609</v>
       </c>
       <c r="BD46" s="3">
-        <v>58.800014495849609</v>
+        <v>22.088544845581051</v>
       </c>
       <c r="BE46" s="3">
-        <v>22.088544845581051</v>
+        <v>23.60788726806641</v>
       </c>
       <c r="BF46" s="3">
-        <v>23.60788726806641</v>
+        <v>16.091709136962891</v>
       </c>
       <c r="BG46" s="3">
-        <v>16.091709136962891</v>
-      </c>
-      <c r="BH46" s="3">
         <v>36.408500671386719</v>
       </c>
     </row>
-    <row r="47" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>45358</v>
       </c>
@@ -9161,28 +9023,25 @@
         <v>10.99633121490479</v>
       </c>
       <c r="BB47" s="3">
-        <v>3.3027768135070801</v>
+        <v>10.275594711303709</v>
       </c>
       <c r="BC47" s="3">
-        <v>10.275594711303709</v>
+        <v>58.597412109375</v>
       </c>
       <c r="BD47" s="3">
-        <v>58.597412109375</v>
+        <v>21.324111938476559</v>
       </c>
       <c r="BE47" s="3">
-        <v>21.324111938476559</v>
+        <v>23.857540130615231</v>
       </c>
       <c r="BF47" s="3">
-        <v>23.857540130615231</v>
+        <v>16.44245719909668</v>
       </c>
       <c r="BG47" s="3">
-        <v>16.44245719909668</v>
-      </c>
-      <c r="BH47" s="3">
         <v>36.182968139648438</v>
       </c>
     </row>
-    <row r="48" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>45359</v>
       </c>
@@ -9343,28 +9202,25 @@
         <v>11.124654769897459</v>
       </c>
       <c r="BB48" s="3">
-        <v>3.3721776008605961</v>
+        <v>10.49792575836182</v>
       </c>
       <c r="BC48" s="3">
-        <v>10.49792575836182</v>
+        <v>58.148155212402337</v>
       </c>
       <c r="BD48" s="3">
-        <v>58.148155212402337</v>
+        <v>21.270780563354489</v>
       </c>
       <c r="BE48" s="3">
-        <v>21.270780563354489</v>
+        <v>23.744062423706051</v>
       </c>
       <c r="BF48" s="3">
-        <v>23.744062423706051</v>
+        <v>15.85217380523682</v>
       </c>
       <c r="BG48" s="3">
-        <v>15.85217380523682</v>
-      </c>
-      <c r="BH48" s="3">
         <v>36.202579498291023</v>
       </c>
     </row>
-    <row r="49" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>45362</v>
       </c>
@@ -9525,28 +9381,25 @@
         <v>11.134525299072269</v>
       </c>
       <c r="BB49" s="3">
-        <v>3.251171350479126</v>
+        <v>10.0049295425415</v>
       </c>
       <c r="BC49" s="3">
-        <v>10.0049295425415</v>
+        <v>56.342311859130859</v>
       </c>
       <c r="BD49" s="3">
-        <v>56.342311859130859</v>
+        <v>21.564107894897461</v>
       </c>
       <c r="BE49" s="3">
-        <v>21.564107894897461</v>
+        <v>23.721366882324219</v>
       </c>
       <c r="BF49" s="3">
-        <v>23.721366882324219</v>
+        <v>15.732405662536619</v>
       </c>
       <c r="BG49" s="3">
-        <v>15.732405662536619</v>
-      </c>
-      <c r="BH49" s="3">
         <v>36.437911987304688</v>
       </c>
     </row>
-    <row r="50" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>45363</v>
       </c>
@@ -9707,28 +9560,25 @@
         <v>11.164138793945311</v>
       </c>
       <c r="BB50" s="3">
-        <v>3.300997257232666</v>
+        <v>9.8695974349975586</v>
       </c>
       <c r="BC50" s="3">
-        <v>9.8695974349975586</v>
+        <v>55.991260528564453</v>
       </c>
       <c r="BD50" s="3">
-        <v>55.991260528564453</v>
+        <v>21.528554916381839</v>
       </c>
       <c r="BE50" s="3">
-        <v>21.528554916381839</v>
+        <v>23.68051719665527</v>
       </c>
       <c r="BF50" s="3">
-        <v>23.68051719665527</v>
+        <v>16.237140655517582</v>
       </c>
       <c r="BG50" s="3">
-        <v>16.237140655517582</v>
-      </c>
-      <c r="BH50" s="3">
         <v>36.879173278808587</v>
       </c>
     </row>
-    <row r="51" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>45364</v>
       </c>
@@ -9889,28 +9739,25 @@
         <v>11.272720336914061</v>
       </c>
       <c r="BB51" s="3">
-        <v>3.2956585884094238</v>
+        <v>9.7535982131958008</v>
       </c>
       <c r="BC51" s="3">
-        <v>9.7535982131958008</v>
+        <v>56.350173950195313</v>
       </c>
       <c r="BD51" s="3">
-        <v>56.350173950195313</v>
+        <v>21.919658660888668</v>
       </c>
       <c r="BE51" s="3">
-        <v>21.919658660888668</v>
+        <v>23.60788726806641</v>
       </c>
       <c r="BF51" s="3">
-        <v>23.60788726806641</v>
+        <v>15.83506393432617</v>
       </c>
       <c r="BG51" s="3">
-        <v>15.83506393432617</v>
-      </c>
-      <c r="BH51" s="3">
         <v>37.281200408935547</v>
       </c>
     </row>
-    <row r="52" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>45365</v>
       </c>
@@ -10071,28 +9918,25 @@
         <v>10.7100715637207</v>
       </c>
       <c r="BB52" s="3">
-        <v>3.3383669853210449</v>
+        <v>9.5505990982055664</v>
       </c>
       <c r="BC52" s="3">
-        <v>9.5505990982055664</v>
+        <v>55.632339477539063</v>
       </c>
       <c r="BD52" s="3">
-        <v>55.632339477539063</v>
+        <v>22.42631912231445</v>
       </c>
       <c r="BE52" s="3">
-        <v>22.42631912231445</v>
+        <v>24.125349044799801</v>
       </c>
       <c r="BF52" s="3">
-        <v>24.125349044799801</v>
+        <v>15.792287826538089</v>
       </c>
       <c r="BG52" s="3">
-        <v>15.792287826538089</v>
-      </c>
-      <c r="BH52" s="3">
         <v>37.055675506591797</v>
       </c>
     </row>
-    <row r="53" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>45366</v>
       </c>
@@ -10253,28 +10097,25 @@
         <v>11.786013603210449</v>
       </c>
       <c r="BB53" s="3">
-        <v>3.3134536743164058</v>
+        <v>9.4539327621459961</v>
       </c>
       <c r="BC53" s="3">
-        <v>9.4539327621459961</v>
+        <v>54.997329711914063</v>
       </c>
       <c r="BD53" s="3">
-        <v>54.997329711914063</v>
+        <v>22.47965049743652</v>
       </c>
       <c r="BE53" s="3">
-        <v>22.47965049743652</v>
+        <v>23.612424850463871</v>
       </c>
       <c r="BF53" s="3">
-        <v>23.612424850463871</v>
+        <v>15.66396427154541</v>
       </c>
       <c r="BG53" s="3">
-        <v>15.66396427154541</v>
-      </c>
-      <c r="BH53" s="3">
         <v>37.2615966796875</v>
       </c>
     </row>
-    <row r="54" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>45369</v>
       </c>
@@ -10435,28 +10276,25 @@
         <v>11.519495964050289</v>
       </c>
       <c r="BB54" s="3">
-        <v>3.3098945617675781</v>
+        <v>9.5989322662353516</v>
       </c>
       <c r="BC54" s="3">
-        <v>9.5989322662353516</v>
+        <v>56.046478271484382</v>
       </c>
       <c r="BD54" s="3">
-        <v>56.046478271484382</v>
+        <v>22.452985763549801</v>
       </c>
       <c r="BE54" s="3">
-        <v>22.452985763549801</v>
+        <v>23.458097457885739</v>
       </c>
       <c r="BF54" s="3">
-        <v>23.458097457885739</v>
+        <v>15.52708911895752</v>
       </c>
       <c r="BG54" s="3">
-        <v>15.52708911895752</v>
-      </c>
-      <c r="BH54" s="3">
         <v>37.2615966796875</v>
       </c>
     </row>
-    <row r="55" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>45370</v>
       </c>
@@ -10617,28 +10455,25 @@
         <v>11.894595146179199</v>
       </c>
       <c r="BB55" s="3">
-        <v>3.2565093040466309</v>
+        <v>9.8309307098388672</v>
       </c>
       <c r="BC55" s="3">
-        <v>9.8309307098388672</v>
+        <v>56.506629943847663</v>
       </c>
       <c r="BD55" s="3">
-        <v>56.506629943847663</v>
+        <v>22.22187614440918</v>
       </c>
       <c r="BE55" s="3">
-        <v>22.22187614440918</v>
+        <v>23.23567962646484</v>
       </c>
       <c r="BF55" s="3">
-        <v>23.23567962646484</v>
+        <v>15.569863319396971</v>
       </c>
       <c r="BG55" s="3">
-        <v>15.569863319396971</v>
-      </c>
-      <c r="BH55" s="3">
         <v>38.006824493408203</v>
       </c>
     </row>
-    <row r="56" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>45371</v>
       </c>
@@ -10799,28 +10634,25 @@
         <v>12.89157009124756</v>
       </c>
       <c r="BB56" s="3">
-        <v>3.238714456558228</v>
+        <v>10.03392887115479</v>
       </c>
       <c r="BC56" s="3">
-        <v>10.03392887115479</v>
+        <v>56.883956909179688</v>
       </c>
       <c r="BD56" s="3">
-        <v>56.883956909179688</v>
+        <v>22.22187614440918</v>
       </c>
       <c r="BE56" s="3">
-        <v>22.22187614440918</v>
+        <v>23.271993637084961</v>
       </c>
       <c r="BF56" s="3">
-        <v>23.271993637084961</v>
+        <v>16.014715194702148</v>
       </c>
       <c r="BG56" s="3">
-        <v>16.014715194702148</v>
-      </c>
-      <c r="BH56" s="3">
         <v>38.075462341308587</v>
       </c>
     </row>
-    <row r="57" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>45372</v>
       </c>
@@ -10981,28 +10813,25 @@
         <v>12.90144062042236</v>
       </c>
       <c r="BB57" s="3">
-        <v>3.2458324432373051</v>
+        <v>9.985595703125</v>
       </c>
       <c r="BC57" s="3">
-        <v>9.985595703125</v>
+        <v>56.745906829833977</v>
       </c>
       <c r="BD57" s="3">
-        <v>56.745906829833977</v>
+        <v>22.461874008178711</v>
       </c>
       <c r="BE57" s="3">
-        <v>22.461874008178711</v>
+        <v>23.281074523925781</v>
       </c>
       <c r="BF57" s="3">
-        <v>23.281074523925781</v>
+        <v>15.954830169677731</v>
       </c>
       <c r="BG57" s="3">
-        <v>15.954830169677731</v>
-      </c>
-      <c r="BH57" s="3">
         <v>38.663806915283203</v>
       </c>
     </row>
-    <row r="58" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>45373</v>
       </c>
@@ -11163,28 +10992,25 @@
         <v>12.289436340332029</v>
       </c>
       <c r="BB58" s="3">
-        <v>3.2476117610931401</v>
+        <v>9.8115968704223633</v>
       </c>
       <c r="BC58" s="3">
-        <v>9.8115968704223633</v>
+        <v>56.092491149902337</v>
       </c>
       <c r="BD58" s="3">
-        <v>56.092491149902337</v>
+        <v>22.070768356323239</v>
       </c>
       <c r="BE58" s="3">
-        <v>22.070768356323239</v>
+        <v>23.47171592712402</v>
       </c>
       <c r="BF58" s="3">
-        <v>23.47171592712402</v>
+        <v>16.023271560668949</v>
       </c>
       <c r="BG58" s="3">
-        <v>16.023271560668949</v>
-      </c>
-      <c r="BH58" s="3">
         <v>38.967781066894531</v>
       </c>
     </row>
-    <row r="59" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>45376</v>
       </c>
@@ -11345,28 +11171,25 @@
         <v>12.13150024414062</v>
       </c>
       <c r="BB59" s="3">
-        <v>3.2033929824829102</v>
+        <v>9.637598991394043</v>
       </c>
       <c r="BC59" s="3">
-        <v>9.637598991394043</v>
+        <v>55.972850799560547</v>
       </c>
       <c r="BD59" s="3">
-        <v>55.972850799560547</v>
+        <v>22.355207443237301</v>
       </c>
       <c r="BE59" s="3">
-        <v>22.355207443237301</v>
+        <v>22.80446815490723</v>
       </c>
       <c r="BF59" s="3">
-        <v>22.80446815490723</v>
+        <v>15.82650661468506</v>
       </c>
       <c r="BG59" s="3">
-        <v>15.82650661468506</v>
-      </c>
-      <c r="BH59" s="3">
         <v>38.337108612060547</v>
       </c>
     </row>
-    <row r="60" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>45377</v>
       </c>
@@ -11527,28 +11350,25 @@
         <v>12.05253219604492</v>
       </c>
       <c r="BB60" s="3">
-        <v>3.2212691307067871</v>
+        <v>9.5989322662353516</v>
       </c>
       <c r="BC60" s="3">
-        <v>9.5989322662353516</v>
+        <v>55.264217376708977</v>
       </c>
       <c r="BD60" s="3">
-        <v>55.264217376708977</v>
+        <v>22.31076622009277</v>
       </c>
       <c r="BE60" s="3">
-        <v>22.31076622009277</v>
+        <v>22.963333129882809</v>
       </c>
       <c r="BF60" s="3">
-        <v>22.963333129882809</v>
+        <v>15.569863319396971</v>
       </c>
       <c r="BG60" s="3">
-        <v>15.569863319396971</v>
-      </c>
-      <c r="BH60" s="3">
         <v>38.081787109375</v>
       </c>
     </row>
-    <row r="61" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>45378</v>
       </c>
@@ -11709,28 +11529,25 @@
         <v>12.151242256164551</v>
       </c>
       <c r="BB61" s="3">
-        <v>3.2016053199768071</v>
+        <v>9.7052650451660156</v>
       </c>
       <c r="BC61" s="3">
-        <v>9.7052650451660156</v>
+        <v>55.7703857421875</v>
       </c>
       <c r="BD61" s="3">
-        <v>55.7703857421875</v>
+        <v>22.541872024536129</v>
       </c>
       <c r="BE61" s="3">
-        <v>22.541872024536129</v>
+        <v>22.872552871704102</v>
       </c>
       <c r="BF61" s="3">
-        <v>22.872552871704102</v>
+        <v>15.51852989196777</v>
       </c>
       <c r="BG61" s="3">
-        <v>15.51852989196777</v>
-      </c>
-      <c r="BH61" s="3">
         <v>37.855926513671882</v>
       </c>
     </row>
-    <row r="62" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>45379</v>
       </c>
@@ -11891,28 +11708,25 @@
         <v>12.664535522460939</v>
       </c>
       <c r="BB62" s="3">
-        <v>3.1819412708282471</v>
+        <v>9.6762657165527344</v>
       </c>
       <c r="BC62" s="3">
-        <v>9.6762657165527344</v>
+        <v>55.9820556640625</v>
       </c>
       <c r="BD62" s="3">
-        <v>55.9820556640625</v>
+        <v>22.230766296386719</v>
       </c>
       <c r="BE62" s="3">
-        <v>22.230766296386719</v>
+        <v>22.967874526977539</v>
       </c>
       <c r="BF62" s="3">
-        <v>22.967874526977539</v>
+        <v>15.817953109741209</v>
       </c>
       <c r="BG62" s="3">
-        <v>15.817953109741209</v>
-      </c>
-      <c r="BH62" s="3">
         <v>37.512233734130859</v>
       </c>
     </row>
-    <row r="63" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>45383</v>
       </c>
@@ -12073,28 +11887,25 @@
         <v>12.180855751037599</v>
       </c>
       <c r="BB63" s="3">
-        <v>3.183728933334351</v>
+        <v>9.7535982131958008</v>
       </c>
       <c r="BC63" s="3">
-        <v>9.7535982131958008</v>
+        <v>56.340976715087891</v>
       </c>
       <c r="BD63" s="3">
-        <v>56.340976715087891</v>
+        <v>22.399650573730469</v>
       </c>
       <c r="BE63" s="3">
-        <v>22.399650573730469</v>
+        <v>23.146236419677731</v>
       </c>
       <c r="BF63" s="3">
-        <v>23.146236419677731</v>
+        <v>15.71529483795166</v>
       </c>
       <c r="BG63" s="3">
-        <v>15.71529483795166</v>
-      </c>
-      <c r="BH63" s="3">
         <v>37.306011199951172</v>
       </c>
     </row>
-    <row r="64" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>45384</v>
       </c>
@@ -12255,28 +12066,25 @@
         <v>12.664535522460939</v>
       </c>
       <c r="BB64" s="3">
-        <v>3.1819412708282471</v>
+        <v>9.8985967636108398</v>
       </c>
       <c r="BC64" s="3">
-        <v>9.8985967636108398</v>
+        <v>57.003593444824219</v>
       </c>
       <c r="BD64" s="3">
-        <v>57.003593444824219</v>
+        <v>22.568538665771481</v>
       </c>
       <c r="BE64" s="3">
-        <v>22.568538665771481</v>
+        <v>22.991350173950199</v>
       </c>
       <c r="BF64" s="3">
-        <v>22.991350173950199</v>
+        <v>16.194366455078121</v>
       </c>
       <c r="BG64" s="3">
-        <v>16.194366455078121</v>
-      </c>
-      <c r="BH64" s="3">
         <v>37.482769012451172</v>
       </c>
     </row>
-    <row r="65" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>45385</v>
       </c>
@@ -12437,28 +12245,25 @@
         <v>12.24995231628418</v>
       </c>
       <c r="BB65" s="3">
-        <v>3.223056316375732</v>
+        <v>9.8309307098388672</v>
       </c>
       <c r="BC65" s="3">
-        <v>9.8309307098388672</v>
+        <v>56.184520721435547</v>
       </c>
       <c r="BD65" s="3">
-        <v>56.184520721435547</v>
+        <v>21.928546905517582</v>
       </c>
       <c r="BE65" s="3">
-        <v>21.928546905517582</v>
+        <v>23.273788452148441</v>
       </c>
       <c r="BF65" s="3">
-        <v>23.273788452148441</v>
+        <v>16.40823936462402</v>
       </c>
       <c r="BG65" s="3">
-        <v>16.40823936462402</v>
-      </c>
-      <c r="BH65" s="3">
         <v>37.207809448242188</v>
       </c>
     </row>
-    <row r="66" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>45386</v>
       </c>
@@ -12619,28 +12424,25 @@
         <v>12.259823799133301</v>
       </c>
       <c r="BB66" s="3">
-        <v>3.324949979782104</v>
+        <v>9.8405971527099609</v>
       </c>
       <c r="BC66" s="3">
-        <v>9.8405971527099609</v>
+        <v>55.5587158203125</v>
       </c>
       <c r="BD66" s="3">
-        <v>55.5587158203125</v>
+        <v>22.230766296386719</v>
       </c>
       <c r="BE66" s="3">
-        <v>22.230766296386719</v>
+        <v>23.57444953918457</v>
       </c>
       <c r="BF66" s="3">
-        <v>23.57444953918457</v>
+        <v>15.80939769744873</v>
       </c>
       <c r="BG66" s="3">
-        <v>15.80939769744873</v>
-      </c>
-      <c r="BH66" s="3">
         <v>37.414031982421882</v>
       </c>
     </row>
-    <row r="67" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>45387</v>
       </c>
@@ -12801,28 +12603,25 @@
         <v>12.437502861022949</v>
       </c>
       <c r="BB67" s="3">
-        <v>3.3106493949890141</v>
+        <v>9.5892658233642578</v>
       </c>
       <c r="BC67" s="3">
-        <v>9.5892658233642578</v>
+        <v>54.951313018798828</v>
       </c>
       <c r="BD67" s="3">
-        <v>54.951313018798828</v>
+        <v>22.577426910400391</v>
       </c>
       <c r="BE67" s="3">
-        <v>22.577426910400391</v>
+        <v>23.446895599365231</v>
       </c>
       <c r="BF67" s="3">
-        <v>23.446895599365231</v>
+        <v>15.65540885925293</v>
       </c>
       <c r="BG67" s="3">
-        <v>15.65540885925293</v>
-      </c>
-      <c r="BH67" s="3">
         <v>37.306011199951172</v>
       </c>
     </row>
-    <row r="68" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>45390</v>
       </c>
@@ -12983,28 +12782,25 @@
         <v>13.05937671661377</v>
       </c>
       <c r="BB68" s="3">
-        <v>3.3142247200012211</v>
+        <v>10.149928092956539</v>
       </c>
       <c r="BC68" s="3">
-        <v>10.149928092956539</v>
+        <v>57.951503753662109</v>
       </c>
       <c r="BD68" s="3">
-        <v>57.951503753662109</v>
+        <v>22.79964447021484</v>
       </c>
       <c r="BE68" s="3">
-        <v>22.79964447021484</v>
+        <v>23.474224090576168</v>
       </c>
       <c r="BF68" s="3">
-        <v>23.474224090576168</v>
+        <v>15.94627666473389</v>
       </c>
       <c r="BG68" s="3">
-        <v>15.94627666473389</v>
-      </c>
-      <c r="BH68" s="3">
         <v>37.512233734130859</v>
       </c>
     </row>
-    <row r="69" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>45391</v>
       </c>
@@ -13165,28 +12961,25 @@
         <v>13.68125152587891</v>
       </c>
       <c r="BB69" s="3">
-        <v>3.355339527130127</v>
+        <v>10.29492664337158</v>
       </c>
       <c r="BC69" s="3">
-        <v>10.29492664337158</v>
+        <v>57.564975738525391</v>
       </c>
       <c r="BD69" s="3">
-        <v>57.564975738525391</v>
+        <v>23.128532409667969</v>
       </c>
       <c r="BE69" s="3">
-        <v>23.128532409667969</v>
+        <v>23.620002746582031</v>
       </c>
       <c r="BF69" s="3">
-        <v>23.620002746582031</v>
+        <v>16.100265502929691</v>
       </c>
       <c r="BG69" s="3">
-        <v>16.100265502929691</v>
-      </c>
-      <c r="BH69" s="3">
         <v>38.101428985595703</v>
       </c>
     </row>
-    <row r="70" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>45392</v>
       </c>
@@ -13347,28 +13140,25 @@
         <v>13.503574371337891</v>
       </c>
       <c r="BB70" s="3">
-        <v>-1.6882673501968379</v>
+        <v>10.014595985412599</v>
       </c>
       <c r="BC70" s="3">
-        <v>10.014595985412599</v>
+        <v>56.690685272216797</v>
       </c>
       <c r="BD70" s="3">
-        <v>56.690685272216797</v>
+        <v>22.675201416015621</v>
       </c>
       <c r="BE70" s="3">
-        <v>22.675201416015621</v>
+        <v>23.40589714050293</v>
       </c>
       <c r="BF70" s="3">
-        <v>23.40589714050293</v>
+        <v>15.501424789428709</v>
       </c>
       <c r="BG70" s="3">
-        <v>15.501424789428709</v>
-      </c>
-      <c r="BH70" s="3">
         <v>37.708633422851563</v>
       </c>
     </row>
-    <row r="71" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>45393</v>
       </c>
@@ -13529,28 +13319,25 @@
         <v>12.89157009124756</v>
       </c>
       <c r="BB71" s="3">
-        <v>-1.6569504737853999</v>
+        <v>9.9275970458984375</v>
       </c>
       <c r="BC71" s="3">
-        <v>9.9275970458984375</v>
+        <v>56.929969787597663</v>
       </c>
       <c r="BD71" s="3">
-        <v>56.929969787597663</v>
+        <v>22.621870040893551</v>
       </c>
       <c r="BE71" s="3">
-        <v>22.621870040893551</v>
+        <v>22.899345397949219</v>
       </c>
       <c r="BF71" s="3">
-        <v>22.899345397949219</v>
+        <v>15.313217163085939</v>
       </c>
       <c r="BG71" s="3">
-        <v>15.313217163085939</v>
-      </c>
-      <c r="BH71" s="3">
         <v>37.551513671875</v>
       </c>
     </row>
-    <row r="72" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>45394</v>
       </c>
@@ -13711,28 +13498,25 @@
         <v>11.94395065307617</v>
       </c>
       <c r="BB72" s="3">
-        <v>-1.638919591903687</v>
+        <v>9.8309307098388672</v>
       </c>
       <c r="BC72" s="3">
-        <v>9.8309307098388672</v>
+        <v>56.718299865722663</v>
       </c>
       <c r="BD72" s="3">
-        <v>56.718299865722663</v>
+        <v>22.05299186706543</v>
       </c>
       <c r="BE72" s="3">
-        <v>22.05299186706543</v>
+        <v>22.75557899475098</v>
       </c>
       <c r="BF72" s="3">
-        <v>22.75557899475098</v>
+        <v>14.825588226318359</v>
       </c>
       <c r="BG72" s="3">
-        <v>14.825588226318359</v>
-      </c>
-      <c r="BH72" s="3">
         <v>37.296192169189453</v>
       </c>
     </row>
-    <row r="73" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>45397</v>
       </c>
@@ -13893,28 +13677,25 @@
         <v>11.26284885406494</v>
       </c>
       <c r="BB73" s="3">
-        <v>-1.648409485816956</v>
+        <v>9.8792638778686523</v>
       </c>
       <c r="BC73" s="3">
-        <v>9.8792638778686523</v>
+        <v>57.049610137939453</v>
       </c>
       <c r="BD73" s="3">
-        <v>57.049610137939453</v>
+        <v>21.99965858459473</v>
       </c>
       <c r="BE73" s="3">
-        <v>21.99965858459473</v>
+        <v>22.635011672973629</v>
       </c>
       <c r="BF73" s="3">
-        <v>22.635011672973629</v>
+        <v>14.85125255584717</v>
       </c>
       <c r="BG73" s="3">
-        <v>14.85125255584717</v>
-      </c>
-      <c r="BH73" s="3">
         <v>36.962318420410163</v>
       </c>
     </row>
-    <row r="74" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>45398</v>
       </c>
@@ -14075,28 +13856,25 @@
         <v>11.40104389190674</v>
       </c>
       <c r="BB74" s="3">
-        <v>-1.6351232528686519</v>
+        <v>9.7149314880371094</v>
       </c>
       <c r="BC74" s="3">
-        <v>9.7149314880371094</v>
+        <v>56.543437957763672</v>
       </c>
       <c r="BD74" s="3">
-        <v>56.543437957763672</v>
+        <v>21.501888275146481</v>
       </c>
       <c r="BE74" s="3">
-        <v>21.501888275146481</v>
+        <v>22.579362869262699</v>
       </c>
       <c r="BF74" s="3">
-        <v>22.579362869262699</v>
+        <v>14.62882709503174</v>
       </c>
       <c r="BG74" s="3">
-        <v>14.62882709503174</v>
-      </c>
-      <c r="BH74" s="3">
         <v>38.071971893310547</v>
       </c>
     </row>
-    <row r="75" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>45399</v>
       </c>
@@ -14257,28 +14035,25 @@
         <v>11.20362377166748</v>
       </c>
       <c r="BB75" s="3">
-        <v>-1.6398686170578001</v>
+        <v>9.5892658233642578</v>
       </c>
       <c r="BC75" s="3">
-        <v>9.5892658233642578</v>
+        <v>57.160041809082031</v>
       </c>
       <c r="BD75" s="3">
-        <v>57.160041809082031</v>
+        <v>21.635219573974609</v>
       </c>
       <c r="BE75" s="3">
-        <v>21.635219573974609</v>
+        <v>22.68138313293457</v>
       </c>
       <c r="BF75" s="3">
-        <v>22.68138313293457</v>
+        <v>15.082234382629389</v>
       </c>
       <c r="BG75" s="3">
-        <v>15.082234382629389</v>
-      </c>
-      <c r="BH75" s="3">
         <v>37.531871795654297</v>
       </c>
     </row>
-    <row r="76" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>45400</v>
       </c>
@@ -14439,28 +14214,25 @@
         <v>11.460269927978519</v>
       </c>
       <c r="BB76" s="3">
-        <v>-1.6265823841094971</v>
+        <v>9.6085987091064453</v>
       </c>
       <c r="BC76" s="3">
-        <v>9.6085987091064453</v>
+        <v>57.371711730957031</v>
       </c>
       <c r="BD76" s="3">
-        <v>57.371711730957031</v>
+        <v>21.45744514465332</v>
       </c>
       <c r="BE76" s="3">
-        <v>21.45744514465332</v>
+        <v>22.5979118347168</v>
       </c>
       <c r="BF76" s="3">
-        <v>22.5979118347168</v>
+        <v>15.09078884124756</v>
       </c>
       <c r="BG76" s="3">
-        <v>15.09078884124756</v>
-      </c>
-      <c r="BH76" s="3">
         <v>37.905033111572273</v>
       </c>
     </row>
-    <row r="77" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
         <v>45401</v>
       </c>
@@ -14621,28 +14393,25 @@
         <v>11.864982604980471</v>
       </c>
       <c r="BB77" s="3">
-        <v>-1.640817284584045</v>
+        <v>9.985595703125</v>
       </c>
       <c r="BC77" s="3">
-        <v>9.985595703125</v>
+        <v>58.3104248046875</v>
       </c>
       <c r="BD77" s="3">
-        <v>58.3104248046875</v>
+        <v>21.244405746459961</v>
       </c>
       <c r="BE77" s="3">
-        <v>21.244405746459961</v>
+        <v>22.58863639831543</v>
       </c>
       <c r="BF77" s="3">
-        <v>22.58863639831543</v>
+        <v>15.07368087768555</v>
       </c>
       <c r="BG77" s="3">
-        <v>15.07368087768555</v>
-      </c>
-      <c r="BH77" s="3">
         <v>37.855926513671882</v>
       </c>
     </row>
-    <row r="78" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>45404</v>
       </c>
@@ -14803,28 +14572,25 @@
         <v>11.72678756713867</v>
       </c>
       <c r="BB78" s="3">
-        <v>-1.645562410354614</v>
+        <v>10.217594146728519</v>
       </c>
       <c r="BC78" s="3">
-        <v>10.217594146728519</v>
+        <v>58.282817840576172</v>
       </c>
       <c r="BD78" s="3">
-        <v>58.282817840576172</v>
+        <v>21.125875473022461</v>
       </c>
       <c r="BE78" s="3">
-        <v>21.125875473022461</v>
+        <v>22.630373001098629</v>
       </c>
       <c r="BF78" s="3">
-        <v>22.630373001098629</v>
+        <v>15.193447113037109</v>
       </c>
       <c r="BG78" s="3">
-        <v>15.193447113037109</v>
-      </c>
-      <c r="BH78" s="3">
         <v>37.580970764160163</v>
       </c>
     </row>
-    <row r="79" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
         <v>45405</v>
       </c>
@@ -14985,28 +14751,25 @@
         <v>11.58859348297119</v>
       </c>
       <c r="BB79" s="3">
-        <v>-1.6294294595718379</v>
+        <v>8.796605110168457</v>
       </c>
       <c r="BC79" s="3">
-        <v>8.796605110168457</v>
+        <v>57.776641845703118</v>
       </c>
       <c r="BD79" s="3">
-        <v>57.776641845703118</v>
+        <v>20.85234451293945</v>
       </c>
       <c r="BE79" s="3">
-        <v>20.85234451293945</v>
+        <v>22.37067985534668</v>
       </c>
       <c r="BF79" s="3">
-        <v>22.37067985534668</v>
+        <v>15.078028678894039</v>
       </c>
       <c r="BG79" s="3">
-        <v>15.078028678894039</v>
-      </c>
-      <c r="BH79" s="3">
         <v>37.306011199951172</v>
       </c>
     </row>
-    <row r="80" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>45406</v>
       </c>
@@ -15167,28 +14930,25 @@
         <v>11.628077507019039</v>
       </c>
       <c r="BB80" s="3">
-        <v>-1.6398686170578001</v>
+        <v>8.4679403305053711</v>
       </c>
       <c r="BC80" s="3">
-        <v>8.4679403305053711</v>
+        <v>58.494483947753913</v>
       </c>
       <c r="BD80" s="3">
-        <v>58.494483947753913</v>
+        <v>20.505865097045898</v>
       </c>
       <c r="BE80" s="3">
-        <v>20.505865097045898</v>
+        <v>22.213010787963871</v>
       </c>
       <c r="BF80" s="3">
-        <v>22.213010787963871</v>
+        <v>15.347900390625</v>
       </c>
       <c r="BG80" s="3">
-        <v>15.347900390625</v>
-      </c>
-      <c r="BH80" s="3">
         <v>37.541690826416023</v>
       </c>
     </row>
-    <row r="81" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>45407</v>
       </c>
@@ -15349,28 +15109,25 @@
         <v>11.84523963928223</v>
       </c>
       <c r="BB81" s="3">
-        <v>-1.653154253959656</v>
+        <v>8.2069416046142578</v>
       </c>
       <c r="BC81" s="3">
-        <v>8.2069416046142578</v>
+        <v>57.261276245117188</v>
       </c>
       <c r="BD81" s="3">
-        <v>57.261276245117188</v>
+        <v>20.770282745361332</v>
       </c>
       <c r="BE81" s="3">
-        <v>20.770282745361332</v>
+        <v>22.11562347412109</v>
       </c>
       <c r="BF81" s="3">
-        <v>22.11562347412109</v>
+        <v>15.487191200256349</v>
       </c>
       <c r="BG81" s="3">
-        <v>15.487191200256349</v>
-      </c>
-      <c r="BH81" s="3">
         <v>37.973766326904297</v>
       </c>
     </row>
-    <row r="82" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>45408</v>
       </c>
@@ -15531,28 +15288,25 @@
         <v>12.89157009124756</v>
       </c>
       <c r="BB82" s="3">
-        <v>-1.653154253959656</v>
+        <v>8.1999998092651367</v>
       </c>
       <c r="BC82" s="3">
-        <v>8.1999998092651367</v>
+        <v>57.261276245117188</v>
       </c>
       <c r="BD82" s="3">
-        <v>57.261276245117188</v>
+        <v>21.508821487426761</v>
       </c>
       <c r="BE82" s="3">
-        <v>21.508821487426761</v>
+        <v>22.259384155273441</v>
       </c>
       <c r="BF82" s="3">
-        <v>22.259384155273441</v>
+        <v>15.783176422119141</v>
       </c>
       <c r="BG82" s="3">
-        <v>15.783176422119141</v>
-      </c>
-      <c r="BH82" s="3">
         <v>38.513870239257813</v>
       </c>
     </row>
-    <row r="83" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
         <v>45411</v>
       </c>
@@ -15713,28 +15467,25 @@
         <v>13.15808773040771</v>
       </c>
       <c r="BB83" s="3">
-        <v>-1.670236349105835</v>
+        <v>8.2100000381469727</v>
       </c>
       <c r="BC83" s="3">
-        <v>8.2100000381469727</v>
+        <v>58.807392120361328</v>
       </c>
       <c r="BD83" s="3">
-        <v>58.807392120361328</v>
+        <v>21.59999847412109</v>
       </c>
       <c r="BE83" s="3">
-        <v>21.59999847412109</v>
+        <v>22.226922988891602</v>
       </c>
       <c r="BF83" s="3">
-        <v>22.226922988891602</v>
+        <v>15.878941535949711</v>
       </c>
       <c r="BG83" s="3">
-        <v>15.878941535949711</v>
-      </c>
-      <c r="BH83" s="3">
         <v>38.651344299316413</v>
       </c>
     </row>
-    <row r="84" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>45412</v>
       </c>
@@ -15895,28 +15646,25 @@
         <v>12.180855751037599</v>
       </c>
       <c r="BB84" s="3">
-        <v>-1.671185374259949</v>
+        <v>7.9099998474121094</v>
       </c>
       <c r="BC84" s="3">
-        <v>7.9099998474121094</v>
+        <v>58.246002197265618</v>
       </c>
       <c r="BD84" s="3">
-        <v>58.246002197265618</v>
+        <v>21.390289306640621</v>
       </c>
       <c r="BE84" s="3">
-        <v>21.390289306640621</v>
+        <v>22.05921745300293</v>
       </c>
       <c r="BF84" s="3">
-        <v>22.05921745300293</v>
+        <v>15.365310668945311</v>
       </c>
       <c r="BG84" s="3">
-        <v>15.365310668945311</v>
-      </c>
-      <c r="BH84" s="3">
         <v>38.837924957275391</v>
       </c>
     </row>
-    <row r="85" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
         <v>45414</v>
       </c>
@@ -16077,28 +15825,25 @@
         <v>12.42763137817383</v>
       </c>
       <c r="BB85" s="3">
-        <v>-1.7214821577072139</v>
+        <v>7.9800000190734863</v>
       </c>
       <c r="BC85" s="3">
-        <v>7.9800000190734863</v>
+        <v>58.825790405273438</v>
       </c>
       <c r="BD85" s="3">
-        <v>58.825790405273438</v>
+        <v>21.253522872924801</v>
       </c>
       <c r="BE85" s="3">
-        <v>21.253522872924801</v>
+        <v>23.140274047851559</v>
       </c>
       <c r="BF85" s="3">
-        <v>23.140274047851559</v>
+        <v>15.14767265319824</v>
       </c>
       <c r="BG85" s="3">
-        <v>15.14767265319824</v>
-      </c>
-      <c r="BH85" s="3">
         <v>38.150524139404297</v>
       </c>
     </row>
-    <row r="86" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
         <v>45415</v>
       </c>
@@ -16259,28 +16004,25 @@
         <v>13.4443473815918</v>
       </c>
       <c r="BB86" s="3">
-        <v>-1.766085028648376</v>
+        <v>8</v>
       </c>
       <c r="BC86" s="3">
-        <v>8</v>
+        <v>58.890213012695313</v>
       </c>
       <c r="BD86" s="3">
-        <v>58.890213012695313</v>
+        <v>21.9647102355957</v>
       </c>
       <c r="BE86" s="3">
-        <v>21.9647102355957</v>
+        <v>23.461795806884769</v>
       </c>
       <c r="BF86" s="3">
-        <v>23.461795806884769</v>
+        <v>15.4001350402832</v>
       </c>
       <c r="BG86" s="3">
-        <v>15.4001350402832</v>
-      </c>
-      <c r="BH86" s="3">
         <v>38.071971893310547</v>
       </c>
     </row>
-    <row r="87" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
         <v>45418</v>
       </c>
@@ -16441,28 +16183,25 @@
         <v>12.94092464447021</v>
       </c>
       <c r="BB87" s="3">
-        <v>-1.7603908777236941</v>
+        <v>8.0399999618530273</v>
       </c>
       <c r="BC87" s="3">
-        <v>8.0399999618530273</v>
+        <v>59.065071105957031</v>
       </c>
       <c r="BD87" s="3">
-        <v>59.065071105957031</v>
+        <v>21.399408340454102</v>
       </c>
       <c r="BE87" s="3">
-        <v>21.399408340454102</v>
+        <v>23.559652328491211</v>
       </c>
       <c r="BF87" s="3">
-        <v>23.559652328491211</v>
+        <v>15.29566860198975</v>
       </c>
       <c r="BG87" s="3">
-        <v>15.29566860198975</v>
-      </c>
-      <c r="BH87" s="3">
         <v>37.934490203857422</v>
       </c>
     </row>
-    <row r="88" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
         <v>45419</v>
       </c>
@@ -16623,28 +16362,25 @@
         <v>12.24995231628418</v>
       </c>
       <c r="BB88" s="3">
-        <v>-1.651256203651428</v>
+        <v>8.0100002288818359</v>
       </c>
       <c r="BC88" s="3">
-        <v>8.0100002288818359</v>
+        <v>59.433193206787109</v>
       </c>
       <c r="BD88" s="3">
-        <v>59.433193206787109</v>
+        <v>21.289995193481449</v>
       </c>
       <c r="BE88" s="3">
-        <v>21.289995193481449</v>
+        <v>23.177555084228519</v>
       </c>
       <c r="BF88" s="3">
-        <v>23.177555084228519</v>
+        <v>15.47848415374756</v>
       </c>
       <c r="BG88" s="3">
-        <v>15.47848415374756</v>
-      </c>
-      <c r="BH88" s="3">
         <v>38.199630737304688</v>
       </c>
     </row>
-    <row r="89" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
         <v>45420</v>
       </c>
@@ -16805,28 +16541,25 @@
         <v>12.78298854827881</v>
       </c>
       <c r="BB89" s="3">
-        <v>-1.6313275098800659</v>
+        <v>8.0600004196166992</v>
       </c>
       <c r="BC89" s="3">
-        <v>8.0600004196166992</v>
+        <v>58.890213012695313</v>
       </c>
       <c r="BD89" s="3">
-        <v>58.890213012695313</v>
+        <v>21.32646369934082</v>
       </c>
       <c r="BE89" s="3">
-        <v>21.32646369934082</v>
+        <v>21.87282562255859</v>
       </c>
       <c r="BF89" s="3">
-        <v>21.87282562255859</v>
+        <v>15.58295154571533</v>
       </c>
       <c r="BG89" s="3">
-        <v>15.58295154571533</v>
-      </c>
-      <c r="BH89" s="3">
         <v>38.386211395263672</v>
       </c>
     </row>
-    <row r="90" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
         <v>45421</v>
       </c>
@@ -16987,28 +16720,25 @@
         <v>12.437502861022949</v>
       </c>
       <c r="BB90" s="3">
-        <v>-1.601908206939697</v>
+        <v>8</v>
       </c>
       <c r="BC90" s="3">
-        <v>8</v>
+        <v>59.3687744140625</v>
       </c>
       <c r="BD90" s="3">
-        <v>59.3687744140625</v>
+        <v>21.508821487426761</v>
       </c>
       <c r="BE90" s="3">
-        <v>21.508821487426761</v>
+        <v>21.215803146362301</v>
       </c>
       <c r="BF90" s="3">
-        <v>21.215803146362301</v>
+        <v>14.712393760681151</v>
       </c>
       <c r="BG90" s="3">
-        <v>14.712393760681151</v>
-      </c>
-      <c r="BH90" s="3">
         <v>38.199630737304688</v>
       </c>
     </row>
-    <row r="91" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
         <v>45422</v>
       </c>
@@ -17169,28 +16899,25 @@
         <v>12.06240272521973</v>
       </c>
       <c r="BB91" s="3">
-        <v>-1.582928538322449</v>
+        <v>7.9600000381469727</v>
       </c>
       <c r="BC91" s="3">
-        <v>7.9600000381469727</v>
+        <v>59.166305541992188</v>
       </c>
       <c r="BD91" s="3">
-        <v>59.166305541992188</v>
+        <v>21.773239135742191</v>
       </c>
       <c r="BE91" s="3">
-        <v>21.773239135742191</v>
+        <v>21.02009391784668</v>
       </c>
       <c r="BF91" s="3">
-        <v>21.02009391784668</v>
+        <v>14.625338554382321</v>
       </c>
       <c r="BG91" s="3">
-        <v>14.625338554382321</v>
-      </c>
-      <c r="BH91" s="3">
         <v>38.268367767333977</v>
       </c>
     </row>
-    <row r="92" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
         <v>45425</v>
       </c>
@@ -17351,28 +17078,25 @@
         <v>11.825497627258301</v>
       </c>
       <c r="BB92" s="3">
-        <v>-1.591469526290894</v>
+        <v>7.9800000190734863</v>
       </c>
       <c r="BC92" s="3">
-        <v>7.9800000190734863</v>
+        <v>59.516017913818359</v>
       </c>
       <c r="BD92" s="3">
-        <v>59.516017913818359</v>
+        <v>21.545289993286129</v>
       </c>
       <c r="BE92" s="3">
-        <v>21.545289993286129</v>
+        <v>21.15522575378418</v>
       </c>
       <c r="BF92" s="3">
-        <v>21.15522575378418</v>
+        <v>14.93873882293701</v>
       </c>
       <c r="BG92" s="3">
-        <v>14.93873882293701</v>
-      </c>
-      <c r="BH92" s="3">
         <v>38.376388549804688</v>
       </c>
     </row>
-    <row r="93" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
         <v>45426</v>
       </c>
@@ -17533,28 +17257,25 @@
         <v>11.855111122131349</v>
       </c>
       <c r="BB93" s="3">
-        <v>-1.601908206939697</v>
+        <v>7.9000000953674316</v>
       </c>
       <c r="BC93" s="3">
-        <v>7.9000000953674316</v>
+        <v>59.479206085205078</v>
       </c>
       <c r="BD93" s="3">
-        <v>59.479206085205078</v>
+        <v>21.882648468017582</v>
       </c>
       <c r="BE93" s="3">
-        <v>21.882648468017582</v>
+        <v>21.113288879394531</v>
       </c>
       <c r="BF93" s="3">
-        <v>21.113288879394531</v>
+        <v>14.947445869445801</v>
       </c>
       <c r="BG93" s="3">
-        <v>14.947445869445801</v>
-      </c>
-      <c r="BH93" s="3">
         <v>38.8968505859375</v>
       </c>
     </row>
-    <row r="94" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
         <v>45427</v>
       </c>
@@ -17715,28 +17436,25 @@
         <v>12.26969528198242</v>
       </c>
       <c r="BB94" s="3">
-        <v>-1.62468433380127</v>
+        <v>7.929999828338623</v>
       </c>
       <c r="BC94" s="3">
-        <v>7.929999828338623</v>
+        <v>59.304351806640618</v>
       </c>
       <c r="BD94" s="3">
-        <v>59.304351806640618</v>
+        <v>21.691177368164059</v>
       </c>
       <c r="BE94" s="3">
-        <v>21.691177368164059</v>
+        <v>21.364912033081051</v>
       </c>
       <c r="BF94" s="3">
-        <v>21.364912033081051</v>
+        <v>14.91262149810791</v>
       </c>
       <c r="BG94" s="3">
-        <v>14.91262149810791</v>
-      </c>
-      <c r="BH94" s="3">
         <v>38.906665802001953</v>
       </c>
     </row>
-    <row r="95" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
         <v>45428</v>
       </c>
@@ -17897,28 +17615,25 @@
         <v>12.56582546234131</v>
       </c>
       <c r="BB95" s="3">
-        <v>-1.6493581533432009</v>
+        <v>7.9699997901916504</v>
       </c>
       <c r="BC95" s="3">
-        <v>7.9699997901916504</v>
+        <v>59.736900329589837</v>
       </c>
       <c r="BD95" s="3">
-        <v>59.736900329589837</v>
+        <v>21.791469573974609</v>
       </c>
       <c r="BE95" s="3">
-        <v>21.791469573974609</v>
+        <v>21.66779899597168</v>
       </c>
       <c r="BF95" s="3">
-        <v>21.66779899597168</v>
+        <v>15.060616493225099</v>
       </c>
       <c r="BG95" s="3">
-        <v>15.060616493225099</v>
-      </c>
-      <c r="BH95" s="3">
         <v>38.88702392578125</v>
       </c>
     </row>
-    <row r="96" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>45429</v>
       </c>
@@ -18079,28 +17794,25 @@
         <v>12.21046829223633</v>
       </c>
       <c r="BB96" s="3">
-        <v>-1.6398686170578001</v>
+        <v>7.9600000381469727</v>
       </c>
       <c r="BC96" s="3">
-        <v>7.9600000381469727</v>
+        <v>60.905673980712891</v>
       </c>
       <c r="BD96" s="3">
-        <v>60.905673980712891</v>
+        <v>21.59999847412109</v>
       </c>
       <c r="BE96" s="3">
-        <v>21.59999847412109</v>
+        <v>21.644498825073239</v>
       </c>
       <c r="BF96" s="3">
-        <v>21.644498825073239</v>
+        <v>14.87780094146729</v>
       </c>
       <c r="BG96" s="3">
-        <v>14.87780094146729</v>
-      </c>
-      <c r="BH96" s="3">
         <v>38.926303863525391</v>
       </c>
     </row>
-    <row r="97" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
         <v>45432</v>
       </c>
@@ -18261,28 +17973,25 @@
         <v>12.180855751037599</v>
       </c>
       <c r="BB97" s="3">
-        <v>-1.5924185514450071</v>
+        <v>8.1499996185302734</v>
       </c>
       <c r="BC97" s="3">
-        <v>8.1499996185302734</v>
+        <v>60.878074645996087</v>
       </c>
       <c r="BD97" s="3">
-        <v>60.878074645996087</v>
+        <v>21.645587921142582</v>
       </c>
       <c r="BE97" s="3">
-        <v>21.645587921142582</v>
+        <v>21.229782104492191</v>
       </c>
       <c r="BF97" s="3">
-        <v>21.229782104492191</v>
+        <v>14.703688621521</v>
       </c>
       <c r="BG97" s="3">
-        <v>14.703688621521</v>
-      </c>
-      <c r="BH97" s="3">
         <v>39.132522583007813</v>
       </c>
     </row>
-    <row r="98" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
         <v>45433</v>
       </c>
@@ -18443,28 +18152,25 @@
         <v>12.161112785339361</v>
       </c>
       <c r="BB98" s="3">
-        <v>-1.5696425437927251</v>
+        <v>8.2899999618530273</v>
       </c>
       <c r="BC98" s="3">
-        <v>8.2899999618530273</v>
+        <v>60.703212738037109</v>
       </c>
       <c r="BD98" s="3">
-        <v>60.703212738037109</v>
+        <v>21.48146820068359</v>
       </c>
       <c r="BE98" s="3">
-        <v>21.48146820068359</v>
+        <v>21.089986801147461</v>
       </c>
       <c r="BF98" s="3">
-        <v>21.089986801147461</v>
+        <v>14.8255672454834</v>
       </c>
       <c r="BG98" s="3">
-        <v>14.8255672454834</v>
-      </c>
-      <c r="BH98" s="3">
         <v>39.044143676757813</v>
       </c>
     </row>
-    <row r="99" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
         <v>45434</v>
       </c>
@@ -18625,28 +18331,25 @@
         <v>11.864982604980471</v>
       </c>
       <c r="BB99" s="3">
-        <v>-1.5943164825439451</v>
+        <v>8.1700000762939453</v>
       </c>
       <c r="BC99" s="3">
-        <v>8.1700000762939453</v>
+        <v>60.224655151367188</v>
       </c>
       <c r="BD99" s="3">
-        <v>60.224655151367188</v>
+        <v>21.05293083190918</v>
       </c>
       <c r="BE99" s="3">
-        <v>21.05293083190918</v>
+        <v>21.467428207397461</v>
       </c>
       <c r="BF99" s="3">
-        <v>21.467428207397461</v>
+        <v>14.68627834320068</v>
       </c>
       <c r="BG99" s="3">
-        <v>14.68627834320068</v>
-      </c>
-      <c r="BH99" s="3">
         <v>38.572784423828118</v>
       </c>
     </row>
-    <row r="100" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>45435</v>
       </c>
@@ -18807,28 +18510,25 @@
         <v>11.69717502593994</v>
       </c>
       <c r="BB100" s="3">
-        <v>-1.5667955875396731</v>
+        <v>8.0299997329711914</v>
       </c>
       <c r="BC100" s="3">
-        <v>8.0299997329711914</v>
+        <v>59.865737915039063</v>
       </c>
       <c r="BD100" s="3">
-        <v>59.865737915039063</v>
+        <v>20.46939659118652</v>
       </c>
       <c r="BE100" s="3">
-        <v>20.46939659118652</v>
+        <v>21.388214111328121</v>
       </c>
       <c r="BF100" s="3">
-        <v>21.388214111328121</v>
+        <v>14.78203868865967</v>
       </c>
       <c r="BG100" s="3">
-        <v>14.78203868865967</v>
-      </c>
-      <c r="BH100" s="3">
         <v>38.327285766601563</v>
       </c>
     </row>
-    <row r="101" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
         <v>45436</v>
       </c>
@@ -18989,28 +18689,25 @@
         <v>11.519495964050289</v>
       </c>
       <c r="BB101" s="3">
-        <v>-1.558254599571228</v>
+        <v>7.929999828338623</v>
       </c>
       <c r="BC101" s="3">
-        <v>7.929999828338623</v>
+        <v>59.893344879150391</v>
       </c>
       <c r="BD101" s="3">
-        <v>59.893344879150391</v>
+        <v>20.4511604309082</v>
       </c>
       <c r="BE101" s="3">
-        <v>20.4511604309082</v>
+        <v>21.388214111328121</v>
       </c>
       <c r="BF101" s="3">
-        <v>21.388214111328121</v>
+        <v>14.764627456665041</v>
       </c>
       <c r="BG101" s="3">
-        <v>14.764627456665041</v>
-      </c>
-      <c r="BH101" s="3">
         <v>37.649711608886719</v>
       </c>
     </row>
-    <row r="102" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
         <v>45439</v>
       </c>
@@ -19171,28 +18868,25 @@
         <v>11.598464012146</v>
       </c>
       <c r="BB102" s="3">
-        <v>-1.56584644317627</v>
+        <v>8.0100002288818359</v>
       </c>
       <c r="BC102" s="3">
-        <v>8.0100002288818359</v>
+        <v>60.095813751220703</v>
       </c>
       <c r="BD102" s="3">
-        <v>60.095813751220703</v>
+        <v>20.6882209777832</v>
       </c>
       <c r="BE102" s="3">
-        <v>20.6882209777832</v>
+        <v>21.402191162109379</v>
       </c>
       <c r="BF102" s="3">
-        <v>21.402191162109379</v>
+        <v>15.15637874603271</v>
       </c>
       <c r="BG102" s="3">
-        <v>15.15637874603271</v>
-      </c>
-      <c r="BH102" s="3">
         <v>37.659526824951172</v>
       </c>
     </row>
-    <row r="103" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
         <v>45440</v>
       </c>
@@ -19353,28 +19047,25 @@
         <v>11.3813009262085</v>
       </c>
       <c r="BB103" s="3">
-        <v>-1.557305574417114</v>
+        <v>7.9099998474121094</v>
       </c>
       <c r="BC103" s="3">
-        <v>7.9099998474121094</v>
+        <v>58.798183441162109</v>
       </c>
       <c r="BD103" s="3">
-        <v>58.798183441162109</v>
+        <v>20.432926177978519</v>
       </c>
       <c r="BE103" s="3">
-        <v>20.432926177978519</v>
+        <v>21.12260627746582</v>
       </c>
       <c r="BF103" s="3">
-        <v>21.12260627746582</v>
+        <v>14.49933528900146</v>
       </c>
       <c r="BG103" s="3">
-        <v>14.49933528900146</v>
-      </c>
-      <c r="BH103" s="3">
         <v>37.541690826416023</v>
       </c>
     </row>
-    <row r="104" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
         <v>45441</v>
       </c>
@@ -19535,28 +19226,25 @@
         <v>11.26284885406494</v>
       </c>
       <c r="BB104" s="3">
-        <v>-1.5449686050415039</v>
+        <v>7.7699999809265137</v>
       </c>
       <c r="BC104" s="3">
-        <v>7.7699999809265137</v>
+        <v>58.199985504150391</v>
       </c>
       <c r="BD104" s="3">
-        <v>58.199985504150391</v>
+        <v>19.94968223571777</v>
       </c>
       <c r="BE104" s="3">
-        <v>19.94968223571777</v>
+        <v>20.810405731201168</v>
       </c>
       <c r="BF104" s="3">
-        <v>20.810405731201168</v>
+        <v>14.2951192855835</v>
       </c>
       <c r="BG104" s="3">
-        <v>14.2951192855835</v>
-      </c>
-      <c r="BH104" s="3">
         <v>37.050689697265618</v>
       </c>
     </row>
-    <row r="105" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
         <v>45443</v>
       </c>
@@ -19717,28 +19405,25 @@
         <v>11.233236312866209</v>
       </c>
       <c r="BB105" s="3">
-        <v>-1.505110383033752</v>
+        <v>7.570000171661377</v>
       </c>
       <c r="BC105" s="3">
-        <v>7.570000171661377</v>
+        <v>58.163177490234382</v>
       </c>
       <c r="BD105" s="3">
-        <v>58.163177490234382</v>
+        <v>19.639678955078121</v>
       </c>
       <c r="BE105" s="3">
-        <v>19.639678955078121</v>
+        <v>20.176679611206051</v>
       </c>
       <c r="BF105" s="3">
-        <v>20.176679611206051</v>
+        <v>14.090903282165529</v>
       </c>
       <c r="BG105" s="3">
-        <v>14.090903282165529</v>
-      </c>
-      <c r="BH105" s="3">
         <v>36.873931884765618</v>
       </c>
     </row>
-    <row r="106" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
         <v>45446</v>
       </c>
@@ -19899,28 +19584,25 @@
         <v>11.24310779571533</v>
       </c>
       <c r="BB106" s="3">
-        <v>-1.50226366519928</v>
+        <v>7.5799999237060547</v>
       </c>
       <c r="BC106" s="3">
-        <v>7.5799999237060547</v>
+        <v>56.939170837402337</v>
       </c>
       <c r="BD106" s="3">
-        <v>56.939170837402337</v>
+        <v>19.502908706665039</v>
       </c>
       <c r="BE106" s="3">
-        <v>19.502908706665039</v>
+        <v>20.456264495849609</v>
       </c>
       <c r="BF106" s="3">
-        <v>20.456264495849609</v>
+        <v>13.957718849182131</v>
       </c>
       <c r="BG106" s="3">
-        <v>13.957718849182131</v>
-      </c>
-      <c r="BH106" s="3">
         <v>36.667716979980469</v>
       </c>
     </row>
-    <row r="107" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
         <v>45447</v>
       </c>
@@ -20081,28 +19763,25 @@
         <v>11.272720336914061</v>
       </c>
       <c r="BB107" s="3">
-        <v>-1.5411725044250491</v>
+        <v>7.4800000190734863</v>
       </c>
       <c r="BC107" s="3">
-        <v>7.4800000190734863</v>
+        <v>56.359382629394531</v>
       </c>
       <c r="BD107" s="3">
-        <v>56.359382629394531</v>
+        <v>19.101730346679691</v>
       </c>
       <c r="BE107" s="3">
-        <v>19.101730346679691</v>
+        <v>20.982816696166989</v>
       </c>
       <c r="BF107" s="3">
-        <v>20.982816696166989</v>
+        <v>14.188570976257321</v>
       </c>
       <c r="BG107" s="3">
-        <v>14.188570976257321</v>
-      </c>
-      <c r="BH107" s="3">
         <v>37.119434356689453</v>
       </c>
     </row>
-    <row r="108" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
         <v>45448</v>
       </c>
@@ -20263,28 +19942,25 @@
         <v>11.272720336914061</v>
       </c>
       <c r="BB108" s="3">
-        <v>-1.5554074048995969</v>
+        <v>7.2899999618530273</v>
       </c>
       <c r="BC108" s="3">
-        <v>7.2899999618530273</v>
+        <v>55.5587158203125</v>
       </c>
       <c r="BD108" s="3">
-        <v>55.5587158203125</v>
+        <v>19.047023773193359</v>
       </c>
       <c r="BE108" s="3">
-        <v>19.047023773193359</v>
+        <v>21.150564193725589</v>
       </c>
       <c r="BF108" s="3">
-        <v>21.150564193725589</v>
+        <v>14.019871711730961</v>
       </c>
       <c r="BG108" s="3">
-        <v>14.019871711730961</v>
-      </c>
-      <c r="BH108" s="3">
         <v>36.864124298095703</v>
       </c>
     </row>
-    <row r="109" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
         <v>45449</v>
       </c>
@@ -20445,28 +20121,25 @@
         <v>11.50962448120117</v>
       </c>
       <c r="BB109" s="3">
-        <v>-1.559203505516052</v>
+        <v>7.320000171661377</v>
       </c>
       <c r="BC109" s="3">
-        <v>7.320000171661377</v>
+        <v>56.331768035888672</v>
       </c>
       <c r="BD109" s="3">
-        <v>56.331768035888672</v>
+        <v>19.183792114257809</v>
       </c>
       <c r="BE109" s="3">
-        <v>19.183792114257809</v>
+        <v>21.22512054443359</v>
       </c>
       <c r="BF109" s="3">
-        <v>21.22512054443359</v>
+        <v>14.49933528900146</v>
       </c>
       <c r="BG109" s="3">
-        <v>14.49933528900146</v>
-      </c>
-      <c r="BH109" s="3">
         <v>37.129257202148438</v>
       </c>
     </row>
-    <row r="110" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
         <v>45450</v>
       </c>
@@ -20627,28 +20300,25 @@
         <v>11.164138793945311</v>
       </c>
       <c r="BB110" s="3">
-        <v>-1.5250396728515621</v>
+        <v>7.179999828338623</v>
       </c>
       <c r="BC110" s="3">
-        <v>7.179999828338623</v>
+        <v>55.595527648925781</v>
       </c>
       <c r="BD110" s="3">
-        <v>55.595527648925781</v>
+        <v>18.964963912963871</v>
       </c>
       <c r="BE110" s="3">
-        <v>18.964963912963871</v>
+        <v>20.96883583068848</v>
       </c>
       <c r="BF110" s="3">
-        <v>20.96883583068848</v>
+        <v>14.064267158508301</v>
       </c>
       <c r="BG110" s="3">
-        <v>14.064267158508301</v>
-      </c>
-      <c r="BH110" s="3">
         <v>37.168533325195313</v>
       </c>
     </row>
-    <row r="111" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
         <v>45453</v>
       </c>
@@ -20809,28 +20479,25 @@
         <v>10.946976661682131</v>
       </c>
       <c r="BB111" s="3">
-        <v>-1.508906483650208</v>
+        <v>7.0500001907348633</v>
       </c>
       <c r="BC111" s="3">
-        <v>7.0500001907348633</v>
+        <v>56.202930450439453</v>
       </c>
       <c r="BD111" s="3">
-        <v>56.202930450439453</v>
+        <v>19.42085075378418</v>
       </c>
       <c r="BE111" s="3">
-        <v>19.42085075378418</v>
+        <v>20.675271987915039</v>
       </c>
       <c r="BF111" s="3">
-        <v>20.675271987915039</v>
+        <v>13.65583419799805</v>
       </c>
       <c r="BG111" s="3">
-        <v>13.65583419799805</v>
-      </c>
-      <c r="BH111" s="3">
         <v>37.129257202148438</v>
       </c>
     </row>
-    <row r="112" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A112" s="2">
         <v>45454</v>
       </c>
@@ -20991,28 +20658,25 @@
         <v>11.10491275787354</v>
       </c>
       <c r="BB112" s="3">
-        <v>-1.5250396728515621</v>
+        <v>7.130000114440918</v>
       </c>
       <c r="BC112" s="3">
-        <v>7.130000114440918</v>
+        <v>56.120101928710938</v>
       </c>
       <c r="BD112" s="3">
-        <v>56.120101928710938</v>
+        <v>19.69438362121582</v>
       </c>
       <c r="BE112" s="3">
-        <v>19.69438362121582</v>
+        <v>21.15522575378418</v>
       </c>
       <c r="BF112" s="3">
-        <v>21.15522575378418</v>
+        <v>14.2951192855835</v>
       </c>
       <c r="BG112" s="3">
-        <v>14.2951192855835</v>
-      </c>
-      <c r="BH112" s="3">
         <v>37.119434356689453</v>
       </c>
     </row>
-    <row r="113" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
         <v>45455</v>
       </c>
@@ -21173,28 +20837,25 @@
         <v>11.193752288818359</v>
       </c>
       <c r="BB113" s="3">
-        <v>-1.500365614891052</v>
+        <v>7.0500001907348633</v>
       </c>
       <c r="BC113" s="3">
-        <v>7.0500001907348633</v>
+        <v>55.3470458984375</v>
       </c>
       <c r="BD113" s="3">
-        <v>55.3470458984375</v>
+        <v>19.07437705993652</v>
       </c>
       <c r="BE113" s="3">
-        <v>19.07437705993652</v>
+        <v>20.749826431274411</v>
       </c>
       <c r="BF113" s="3">
-        <v>20.749826431274411</v>
+        <v>13.93996047973633</v>
       </c>
       <c r="BG113" s="3">
-        <v>13.93996047973633</v>
-      </c>
-      <c r="BH113" s="3">
         <v>37.384574890136719</v>
       </c>
     </row>
-    <row r="114" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
         <v>45456</v>
       </c>
@@ -21355,28 +21016,25 @@
         <v>11.075300216674799</v>
       </c>
       <c r="BB114" s="3">
-        <v>-1.4785387516021731</v>
+        <v>7.1599998474121094</v>
       </c>
       <c r="BC114" s="3">
-        <v>7.1599998474121094</v>
+        <v>55.9820556640625</v>
       </c>
       <c r="BD114" s="3">
-        <v>55.9820556640625</v>
+        <v>18.8190803527832</v>
       </c>
       <c r="BE114" s="3">
-        <v>18.8190803527832</v>
+        <v>20.516841888427731</v>
       </c>
       <c r="BF114" s="3">
-        <v>20.516841888427731</v>
+        <v>13.735745429992679</v>
       </c>
       <c r="BG114" s="3">
-        <v>13.735745429992679</v>
-      </c>
-      <c r="BH114" s="3">
         <v>37.728267669677727</v>
       </c>
     </row>
-    <row r="115" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
         <v>45457</v>
       </c>
@@ -21537,28 +21195,25 @@
         <v>11.193752288818359</v>
       </c>
       <c r="BB115" s="3">
-        <v>-1.506059527397156</v>
+        <v>7.179999828338623</v>
       </c>
       <c r="BC115" s="3">
-        <v>7.179999828338623</v>
+        <v>55.788791656494141</v>
       </c>
       <c r="BD115" s="3">
-        <v>55.788791656494141</v>
+        <v>18.892021179199219</v>
       </c>
       <c r="BE115" s="3">
-        <v>18.892021179199219</v>
+        <v>20.922239303588871</v>
       </c>
       <c r="BF115" s="3">
-        <v>20.922239303588871</v>
+        <v>13.7446231842041</v>
       </c>
       <c r="BG115" s="3">
-        <v>13.7446231842041</v>
-      </c>
-      <c r="BH115" s="3">
         <v>38.071971893310547</v>
       </c>
     </row>
-    <row r="116" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
         <v>45460</v>
       </c>
@@ -21719,28 +21374,25 @@
         <v>10.946976661682131</v>
       </c>
       <c r="BB116" s="3">
-        <v>-1.473793745040894</v>
+        <v>7.0999999046325684</v>
       </c>
       <c r="BC116" s="3">
-        <v>7.0999999046325684</v>
+        <v>55.567916870117188</v>
       </c>
       <c r="BD116" s="3">
-        <v>55.567916870117188</v>
+        <v>18.408779144287109</v>
       </c>
       <c r="BE116" s="3">
-        <v>18.408779144287109</v>
+        <v>20.642656326293949</v>
       </c>
       <c r="BF116" s="3">
-        <v>20.642656326293949</v>
+        <v>13.602560997009279</v>
       </c>
       <c r="BG116" s="3">
-        <v>13.602560997009279</v>
-      </c>
-      <c r="BH116" s="3">
         <v>38.071971893310547</v>
       </c>
     </row>
-    <row r="117" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A117" s="2">
         <v>45461</v>
       </c>
@@ -21901,28 +21553,25 @@
         <v>10.749555587768549</v>
       </c>
       <c r="BB117" s="3">
-        <v>-1.488977789878845</v>
+        <v>7.2300000190734863</v>
       </c>
       <c r="BC117" s="3">
-        <v>7.2300000190734863</v>
+        <v>55.825603485107422</v>
       </c>
       <c r="BD117" s="3">
-        <v>55.825603485107422</v>
+        <v>18.645839691162109</v>
       </c>
       <c r="BE117" s="3">
-        <v>18.645839691162109</v>
+        <v>20.656633377075199</v>
       </c>
       <c r="BF117" s="3">
-        <v>20.656633377075199</v>
+        <v>13.531528472900391</v>
       </c>
       <c r="BG117" s="3">
-        <v>13.531528472900391</v>
-      </c>
-      <c r="BH117" s="3">
         <v>38.160346984863281</v>
       </c>
     </row>
-    <row r="118" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
         <v>45462</v>
       </c>
@@ -22083,28 +21732,25 @@
         <v>10.66071605682373</v>
       </c>
       <c r="BB118" s="3">
-        <v>-1.488028764724731</v>
+        <v>7.3400001525878906</v>
       </c>
       <c r="BC118" s="3">
-        <v>7.3400001525878906</v>
+        <v>56.000457763671882</v>
       </c>
       <c r="BD118" s="3">
-        <v>56.000457763671882</v>
+        <v>18.673196792602539</v>
       </c>
       <c r="BE118" s="3">
-        <v>18.673196792602539</v>
+        <v>20.64731407165527</v>
       </c>
       <c r="BF118" s="3">
-        <v>20.64731407165527</v>
+        <v>13.504892349243161</v>
       </c>
       <c r="BG118" s="3">
-        <v>13.504892349243161</v>
-      </c>
-      <c r="BH118" s="3">
         <v>39.093246459960938</v>
       </c>
     </row>
-    <row r="119" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
         <v>45463</v>
       </c>
@@ -22265,28 +21911,25 @@
         <v>10.48303699493408</v>
       </c>
       <c r="BB119" s="3">
-        <v>-1.489926695823669</v>
+        <v>7.6100001335144043</v>
       </c>
       <c r="BC119" s="3">
-        <v>7.6100001335144043</v>
+        <v>56.506629943847663</v>
       </c>
       <c r="BD119" s="3">
-        <v>56.506629943847663</v>
+        <v>18.727901458740231</v>
       </c>
       <c r="BE119" s="3">
-        <v>18.727901458740231</v>
+        <v>20.810405731201168</v>
       </c>
       <c r="BF119" s="3">
-        <v>20.810405731201168</v>
+        <v>13.407223701477051</v>
       </c>
       <c r="BG119" s="3">
-        <v>13.407223701477051</v>
-      </c>
-      <c r="BH119" s="3">
         <v>40.045772552490227</v>
       </c>
     </row>
-    <row r="120" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A120" s="2">
         <v>45464</v>
       </c>
@@ -22447,28 +22090,25 @@
         <v>10.48303699493408</v>
       </c>
       <c r="BB120" s="3">
-        <v>-1.49751877784729</v>
+        <v>7.5399999618530273</v>
       </c>
       <c r="BC120" s="3">
-        <v>7.5399999618530273</v>
+        <v>55.9820556640625</v>
       </c>
       <c r="BD120" s="3">
-        <v>55.9820556640625</v>
+        <v>19.083492279052731</v>
       </c>
       <c r="BE120" s="3">
-        <v>19.083492279052731</v>
+        <v>20.7311897277832</v>
       </c>
       <c r="BF120" s="3">
-        <v>20.7311897277832</v>
+        <v>13.478255271911619</v>
       </c>
       <c r="BG120" s="3">
-        <v>13.478255271911619</v>
-      </c>
-      <c r="BH120" s="3">
         <v>40.340385437011719</v>
       </c>
     </row>
-    <row r="121" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
         <v>45467</v>
       </c>
@@ -22629,28 +22269,25 @@
         <v>10.76929759979248</v>
       </c>
       <c r="BB121" s="3">
-        <v>-1.511299133300781</v>
+        <v>7.690000057220459</v>
       </c>
       <c r="BC121" s="3">
-        <v>7.690000057220459</v>
+        <v>56.046478271484382</v>
       </c>
       <c r="BD121" s="3">
-        <v>56.046478271484382</v>
+        <v>19.183792114257809</v>
       </c>
       <c r="BE121" s="3">
-        <v>19.183792114257809</v>
+        <v>21.066692352294918</v>
       </c>
       <c r="BF121" s="3">
-        <v>21.066692352294918</v>
+        <v>13.726865768432621</v>
       </c>
       <c r="BG121" s="3">
-        <v>13.726865768432621</v>
-      </c>
-      <c r="BH121" s="3">
         <v>40.134159088134773</v>
       </c>
     </row>
-    <row r="122" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A122" s="2">
         <v>45468</v>
       </c>
@@ -22811,28 +22448,25 @@
         <v>10.631103515625</v>
       </c>
       <c r="BB122" s="3">
-        <v>-1.5141687393188481</v>
+        <v>7.5399999618530273</v>
       </c>
       <c r="BC122" s="3">
-        <v>7.5399999618530273</v>
+        <v>55.816402435302727</v>
       </c>
       <c r="BD122" s="3">
-        <v>55.816402435302727</v>
+        <v>18.627607345581051</v>
       </c>
       <c r="BE122" s="3">
-        <v>18.627607345581051</v>
+        <v>21.131927490234379</v>
       </c>
       <c r="BF122" s="3">
-        <v>21.131927490234379</v>
+        <v>13.442739486694339</v>
       </c>
       <c r="BG122" s="3">
-        <v>13.442739486694339</v>
-      </c>
-      <c r="BH122" s="3">
         <v>40.821559906005859</v>
       </c>
     </row>
-    <row r="123" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A123" s="2">
         <v>45469</v>
       </c>
@@ -22993,28 +22627,25 @@
         <v>10.463295936584471</v>
       </c>
       <c r="BB123" s="3">
-        <v>-1.5141687393188481</v>
+        <v>7.7899999618530273</v>
       </c>
       <c r="BC123" s="3">
-        <v>7.7899999618530273</v>
+        <v>56.506629943847663</v>
       </c>
       <c r="BD123" s="3">
-        <v>56.506629943847663</v>
+        <v>18.95584678649902</v>
       </c>
       <c r="BE123" s="3">
-        <v>18.95584678649902</v>
+        <v>21.518686294555661</v>
       </c>
       <c r="BF123" s="3">
-        <v>21.518686294555661</v>
+        <v>13.45161724090576</v>
       </c>
       <c r="BG123" s="3">
-        <v>13.45161724090576</v>
-      </c>
-      <c r="BH123" s="3">
         <v>41.194713592529297</v>
       </c>
     </row>
-    <row r="124" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A124" s="2">
         <v>45470</v>
       </c>
@@ -23175,28 +22806,25 @@
         <v>10.87787914276123</v>
       </c>
       <c r="BB124" s="3">
-        <v>-1.528516530990601</v>
+        <v>8</v>
       </c>
       <c r="BC124" s="3">
-        <v>8</v>
+        <v>56.653881072998047</v>
       </c>
       <c r="BD124" s="3">
-        <v>56.653881072998047</v>
+        <v>19.45732307434082</v>
       </c>
       <c r="BE124" s="3">
-        <v>19.45732307434082</v>
+        <v>21.414169311523441</v>
       </c>
       <c r="BF124" s="3">
-        <v>21.414169311523441</v>
+        <v>13.611440658569339</v>
       </c>
       <c r="BG124" s="3">
-        <v>13.611440658569339</v>
-      </c>
-      <c r="BH124" s="3">
         <v>40.94921875</v>
       </c>
     </row>
-    <row r="125" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
         <v>45471</v>
       </c>
@@ -23357,28 +22985,25 @@
         <v>10.61136054992676</v>
       </c>
       <c r="BB125" s="3">
-        <v>-1.518951296806335</v>
+        <v>7.9099998474121094</v>
       </c>
       <c r="BC125" s="3">
-        <v>7.9099998474121094</v>
+        <v>57.261276245117188</v>
       </c>
       <c r="BD125" s="3">
-        <v>57.261276245117188</v>
+        <v>19.0561408996582</v>
       </c>
       <c r="BE125" s="3">
-        <v>19.0561408996582</v>
+        <v>21.17597579956055</v>
       </c>
       <c r="BF125" s="3">
-        <v>21.17597579956055</v>
+        <v>13.51377105712891</v>
       </c>
       <c r="BG125" s="3">
-        <v>13.51377105712891</v>
-      </c>
-      <c r="BH125" s="3">
         <v>41.430397033691413</v>
       </c>
     </row>
-    <row r="126" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
         <v>45474</v>
       </c>
@@ -23539,28 +23164,25 @@
         <v>10.542263984680179</v>
       </c>
       <c r="BB126" s="3">
-        <v>-1.53521203994751</v>
+        <v>7.869999885559082</v>
       </c>
       <c r="BC126" s="3">
-        <v>7.869999885559082</v>
+        <v>58.107955932617188</v>
       </c>
       <c r="BD126" s="3">
-        <v>58.107955932617188</v>
+        <v>18.605550765991211</v>
       </c>
       <c r="BE126" s="3">
-        <v>18.605550765991211</v>
+        <v>21.432853698730469</v>
       </c>
       <c r="BF126" s="3">
-        <v>21.432853698730469</v>
+        <v>13.45161724090576</v>
       </c>
       <c r="BG126" s="3">
-        <v>13.45161724090576</v>
-      </c>
-      <c r="BH126" s="3">
         <v>41.275760650634773</v>
       </c>
     </row>
-    <row r="127" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
         <v>45475</v>
       </c>
@@ -23721,28 +23343,25 @@
         <v>10.57187652587891</v>
       </c>
       <c r="BB127" s="3">
-        <v>-1.5103427171707151</v>
+        <v>7.9699997901916504</v>
       </c>
       <c r="BC127" s="3">
-        <v>7.9699997901916504</v>
+        <v>57.914695739746087</v>
       </c>
       <c r="BD127" s="3">
-        <v>57.914695739746087</v>
+        <v>18.931962966918949</v>
       </c>
       <c r="BE127" s="3">
-        <v>18.931962966918949</v>
+        <v>21.241363525390621</v>
       </c>
       <c r="BF127" s="3">
-        <v>21.241363525390621</v>
+        <v>13.478255271911619</v>
       </c>
       <c r="BG127" s="3">
-        <v>13.478255271911619</v>
-      </c>
-      <c r="BH127" s="3">
         <v>41.334762573242188</v>
       </c>
     </row>
-    <row r="128" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
         <v>45476</v>
       </c>
@@ -23903,28 +23522,25 @@
         <v>10.89762115478516</v>
       </c>
       <c r="BB128" s="3">
-        <v>-1.4969513416290281</v>
+        <v>7.9899997711181641</v>
       </c>
       <c r="BC128" s="3">
-        <v>7.9899997711181641</v>
+        <v>59.065071105957031</v>
       </c>
       <c r="BD128" s="3">
-        <v>59.065071105957031</v>
+        <v>19.60344314575195</v>
       </c>
       <c r="BE128" s="3">
-        <v>19.60344314575195</v>
+        <v>21.250703811645511</v>
       </c>
       <c r="BF128" s="3">
-        <v>21.250703811645511</v>
+        <v>13.771261215209959</v>
       </c>
       <c r="BG128" s="3">
-        <v>13.771261215209959</v>
-      </c>
-      <c r="BH128" s="3">
         <v>41.413444519042969</v>
       </c>
     </row>
-    <row r="129" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
         <v>45477</v>
       </c>
@@ -24085,28 +23701,25 @@
         <v>11.70704555511475</v>
       </c>
       <c r="BB129" s="3">
-        <v>-1.51990795135498</v>
+        <v>8.1499996185302734</v>
       </c>
       <c r="BC129" s="3">
-        <v>8.1499996185302734</v>
+        <v>58.770572662353523</v>
       </c>
       <c r="BD129" s="3">
-        <v>58.770572662353523</v>
+        <v>20.041769027709961</v>
       </c>
       <c r="BE129" s="3">
-        <v>20.041769027709961</v>
+        <v>21.554286956787109</v>
       </c>
       <c r="BF129" s="3">
-        <v>21.554286956787109</v>
+        <v>14.05538845062256</v>
       </c>
       <c r="BG129" s="3">
-        <v>14.05538845062256</v>
-      </c>
-      <c r="BH129" s="3">
         <v>41.19708251953125</v>
       </c>
     </row>
-    <row r="130" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A130" s="2">
         <v>45478</v>
       </c>
@@ -24267,28 +23880,25 @@
         <v>11.95382118225098</v>
       </c>
       <c r="BB130" s="3">
-        <v>-1.5036469697952271</v>
+        <v>7.9899997711181641</v>
       </c>
       <c r="BC130" s="3">
-        <v>7.9899997711181641</v>
+        <v>58.531295776367188</v>
       </c>
       <c r="BD130" s="3">
-        <v>58.531295776367188</v>
+        <v>20.619985580444339</v>
       </c>
       <c r="BE130" s="3">
-        <v>20.619985580444339</v>
+        <v>21.680389404296879</v>
       </c>
       <c r="BF130" s="3">
-        <v>21.680389404296879</v>
+        <v>13.94884014129639</v>
       </c>
       <c r="BG130" s="3">
-        <v>13.94884014129639</v>
-      </c>
-      <c r="BH130" s="3">
         <v>41.492122650146477</v>
       </c>
     </row>
-    <row r="131" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A131" s="2">
         <v>45481</v>
       </c>
@@ -24449,28 +24059,25 @@
         <v>11.776143074035639</v>
       </c>
       <c r="BB131" s="3">
-        <v>-1.5218209028244021</v>
+        <v>7.869999885559082</v>
       </c>
       <c r="BC131" s="3">
-        <v>7.869999885559082</v>
+        <v>58.071140289306641</v>
       </c>
       <c r="BD131" s="3">
-        <v>58.071140289306641</v>
+        <v>20.536050796508789</v>
       </c>
       <c r="BE131" s="3">
-        <v>20.536050796508789</v>
+        <v>21.727096557617191</v>
       </c>
       <c r="BF131" s="3">
-        <v>21.727096557617191</v>
+        <v>13.80677604675293</v>
       </c>
       <c r="BG131" s="3">
-        <v>13.80677604675293</v>
-      </c>
-      <c r="BH131" s="3">
         <v>43.734409332275391</v>
       </c>
     </row>
-    <row r="132" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A132" s="2">
         <v>45482</v>
       </c>
@@ -24631,28 +24238,25 @@
         <v>11.76627159118652</v>
       </c>
       <c r="BB132" s="3">
-        <v>-1.515125155448914</v>
+        <v>8.0200004577636719</v>
       </c>
       <c r="BC132" s="3">
-        <v>8.0200004577636719</v>
+        <v>57.997520446777337</v>
       </c>
       <c r="BD132" s="3">
-        <v>57.997520446777337</v>
+        <v>20.703920364379879</v>
       </c>
       <c r="BE132" s="3">
-        <v>20.703920364379879</v>
+        <v>21.839187622070309</v>
       </c>
       <c r="BF132" s="3">
-        <v>21.839187622070309</v>
+        <v>14.073145866394039</v>
       </c>
       <c r="BG132" s="3">
-        <v>14.073145866394039</v>
-      </c>
-      <c r="BH132" s="3">
         <v>43.813083648681641</v>
       </c>
     </row>
-    <row r="133" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A133" s="2">
         <v>45483</v>
       </c>
@@ -24813,28 +24417,25 @@
         <v>12.200596809387211</v>
       </c>
       <c r="BB133" s="3">
-        <v>-1.5399948358535771</v>
+        <v>7.9200000762939453</v>
       </c>
       <c r="BC133" s="3">
-        <v>7.9200000762939453</v>
+        <v>57.215259552001953</v>
       </c>
       <c r="BD133" s="3">
-        <v>57.215259552001953</v>
+        <v>20.96505165100098</v>
       </c>
       <c r="BE133" s="3">
-        <v>20.96505165100098</v>
+        <v>22.16145133972168</v>
       </c>
       <c r="BF133" s="3">
-        <v>22.16145133972168</v>
+        <v>13.88668727874756</v>
       </c>
       <c r="BG133" s="3">
-        <v>13.88668727874756</v>
-      </c>
-      <c r="BH133" s="3">
         <v>43.321353912353523</v>
       </c>
     </row>
-    <row r="134" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A134" s="2">
         <v>45484</v>
       </c>
@@ -24995,28 +24596,25 @@
         <v>13.15808773040771</v>
       </c>
       <c r="BB134" s="3">
-        <v>-1.6031249761581421</v>
+        <v>8</v>
       </c>
       <c r="BC134" s="3">
-        <v>8</v>
+        <v>57.068012237548828</v>
       </c>
       <c r="BD134" s="3">
-        <v>57.068012237548828</v>
+        <v>21.450008392333981</v>
       </c>
       <c r="BE134" s="3">
-        <v>21.450008392333981</v>
+        <v>22.8853759765625</v>
       </c>
       <c r="BF134" s="3">
-        <v>22.8853759765625</v>
+        <v>13.984354972839361</v>
       </c>
       <c r="BG134" s="3">
-        <v>13.984354972839361</v>
-      </c>
-      <c r="BH134" s="3">
         <v>44.216297149658203</v>
       </c>
     </row>
-    <row r="135" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A135" s="2">
         <v>45485</v>
       </c>
@@ -25177,28 +24775,25 @@
         <v>12.57569599151611</v>
       </c>
       <c r="BB135" s="3">
-        <v>-1.621299028396606</v>
+        <v>8.0600004196166992</v>
       </c>
       <c r="BC135" s="3">
-        <v>8.0600004196166992</v>
+        <v>57.905487060546882</v>
       </c>
       <c r="BD135" s="3">
-        <v>57.905487060546882</v>
+        <v>21.216854095458981</v>
       </c>
       <c r="BE135" s="3">
-        <v>21.216854095458981</v>
+        <v>23.104887008666989</v>
       </c>
       <c r="BF135" s="3">
-        <v>23.104887008666989</v>
+        <v>13.88668727874756</v>
       </c>
       <c r="BG135" s="3">
-        <v>13.88668727874756</v>
-      </c>
-      <c r="BH135" s="3">
         <v>45.121086120605469</v>
       </c>
     </row>
-    <row r="136" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A136" s="2">
         <v>45488</v>
       </c>
@@ -25359,28 +24954,25 @@
         <v>12.842214584350589</v>
       </c>
       <c r="BB136" s="3">
-        <v>-1.6021684408187871</v>
+        <v>8.1700000762939453</v>
       </c>
       <c r="BC136" s="3">
-        <v>8.1700000762939453</v>
+        <v>57.969913482666023</v>
       </c>
       <c r="BD136" s="3">
-        <v>57.969913482666023</v>
+        <v>21.142246246337891</v>
       </c>
       <c r="BE136" s="3">
-        <v>21.142246246337891</v>
+        <v>22.86202239990234</v>
       </c>
       <c r="BF136" s="3">
-        <v>22.86202239990234</v>
+        <v>14.03763008117676</v>
       </c>
       <c r="BG136" s="3">
-        <v>14.03763008117676</v>
-      </c>
-      <c r="BH136" s="3">
         <v>45.74066162109375</v>
       </c>
     </row>
-    <row r="137" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A137" s="2">
         <v>45489</v>
       </c>
@@ -25541,28 +25133,25 @@
         <v>12.852086067199711</v>
       </c>
       <c r="BB137" s="3">
-        <v>-1.6050382852554319</v>
+        <v>8.1400003433227539</v>
       </c>
       <c r="BC137" s="3">
-        <v>8.1400003433227539</v>
+        <v>57.362514495849609</v>
       </c>
       <c r="BD137" s="3">
-        <v>57.362514495849609</v>
+        <v>21.291463851928711</v>
       </c>
       <c r="BE137" s="3">
-        <v>21.291463851928711</v>
+        <v>22.913394927978519</v>
       </c>
       <c r="BF137" s="3">
-        <v>22.913394927978519</v>
+        <v>13.97547626495361</v>
       </c>
       <c r="BG137" s="3">
-        <v>13.97547626495361</v>
-      </c>
-      <c r="BH137" s="3">
         <v>45.907848358154297</v>
       </c>
     </row>
-    <row r="138" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A138" s="2">
         <v>45490</v>
       </c>
@@ -25723,28 +25312,25 @@
         <v>12.773117065429689</v>
       </c>
       <c r="BB138" s="3">
-        <v>-1.629907608032227</v>
+        <v>8.5500001907348633</v>
       </c>
       <c r="BC138" s="3">
-        <v>8.5500001907348633</v>
+        <v>56.8287353515625</v>
       </c>
       <c r="BD138" s="3">
-        <v>56.8287353515625</v>
+        <v>21.739114761352539</v>
       </c>
       <c r="BE138" s="3">
-        <v>21.739114761352539</v>
+        <v>23.291706085205082</v>
       </c>
       <c r="BF138" s="3">
-        <v>23.291706085205082</v>
+        <v>14.65915679931641</v>
       </c>
       <c r="BG138" s="3">
-        <v>14.65915679931641</v>
-      </c>
-      <c r="BH138" s="3">
         <v>46.271728515625</v>
       </c>
     </row>
-    <row r="139" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A139" s="2">
         <v>45491</v>
       </c>
@@ -25905,28 +25491,25 @@
         <v>12.10188674926758</v>
       </c>
       <c r="BB139" s="3">
-        <v>-1.6021684408187871</v>
+        <v>8.3999996185302734</v>
       </c>
       <c r="BC139" s="3">
-        <v>8.3999996185302734</v>
+        <v>56.294956207275391</v>
       </c>
       <c r="BD139" s="3">
-        <v>56.294956207275391</v>
+        <v>21.505964279174801</v>
       </c>
       <c r="BE139" s="3">
-        <v>21.505964279174801</v>
+        <v>23.067523956298832</v>
       </c>
       <c r="BF139" s="3">
-        <v>23.067523956298832</v>
+        <v>14.277360916137701</v>
       </c>
       <c r="BG139" s="3">
-        <v>14.277360916137701</v>
-      </c>
-      <c r="BH139" s="3">
         <v>46.615943908691413</v>
       </c>
     </row>
-    <row r="140" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A140" s="2">
         <v>45492</v>
       </c>
@@ -26087,28 +25670,25 @@
         <v>12.23021030426025</v>
       </c>
       <c r="BB140" s="3">
-        <v>-1.604081511497498</v>
+        <v>8.5299997329711914</v>
       </c>
       <c r="BC140" s="3">
-        <v>8.5299997329711914</v>
+        <v>56.248943328857422</v>
       </c>
       <c r="BD140" s="3">
-        <v>56.248943328857422</v>
+        <v>21.533941268920898</v>
       </c>
       <c r="BE140" s="3">
-        <v>21.533941268920898</v>
+        <v>22.899387359619141</v>
       </c>
       <c r="BF140" s="3">
-        <v>22.899387359619141</v>
+        <v>14.57924652099609</v>
       </c>
       <c r="BG140" s="3">
-        <v>14.57924652099609</v>
-      </c>
-      <c r="BH140" s="3">
         <v>46.507762908935547</v>
       </c>
     </row>
-    <row r="141" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A141" s="2">
         <v>45495</v>
       </c>
@@ -26269,28 +25849,25 @@
         <v>12.328920364379879</v>
       </c>
       <c r="BB141" s="3">
-        <v>-1.61842930316925</v>
+        <v>8.5600004196166992</v>
       </c>
       <c r="BC141" s="3">
-        <v>8.5600004196166992</v>
+        <v>56.184520721435547</v>
       </c>
       <c r="BD141" s="3">
-        <v>56.184520721435547</v>
+        <v>21.711139678955082</v>
       </c>
       <c r="BE141" s="3">
-        <v>21.711139678955082</v>
+        <v>23.151594161987301</v>
       </c>
       <c r="BF141" s="3">
-        <v>23.151594161987301</v>
+        <v>15.21852874755859</v>
       </c>
       <c r="BG141" s="3">
-        <v>15.21852874755859</v>
-      </c>
-      <c r="BH141" s="3">
         <v>46.389739990234382</v>
       </c>
     </row>
-    <row r="142" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A142" s="2">
         <v>45496</v>
       </c>
@@ -26451,28 +26028,25 @@
         <v>12.46711540222168</v>
       </c>
       <c r="BB142" s="3">
-        <v>-1.5878206491470339</v>
+        <v>8.2899999618530273</v>
       </c>
       <c r="BC142" s="3">
-        <v>8.2899999618530273</v>
+        <v>55.429874420166023</v>
       </c>
       <c r="BD142" s="3">
-        <v>55.429874420166023</v>
+        <v>21.366071701049801</v>
       </c>
       <c r="BE142" s="3">
-        <v>21.366071701049801</v>
+        <v>22.684541702270511</v>
       </c>
       <c r="BF142" s="3">
-        <v>22.684541702270511</v>
+        <v>15.360593795776371</v>
       </c>
       <c r="BG142" s="3">
-        <v>15.360593795776371</v>
-      </c>
-      <c r="BH142" s="3">
         <v>46.271728515625</v>
       </c>
     </row>
-    <row r="143" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A143" s="2">
         <v>45497</v>
       </c>
@@ -26633,28 +26207,25 @@
         <v>12.56582546234131</v>
       </c>
       <c r="BB143" s="3">
-        <v>-1.5878206491470339</v>
+        <v>8.1099996566772461</v>
       </c>
       <c r="BC143" s="3">
-        <v>8.1099996566772461</v>
+        <v>55.7703857421875</v>
       </c>
       <c r="BD143" s="3">
-        <v>55.7703857421875</v>
+        <v>21.291463851928711</v>
       </c>
       <c r="BE143" s="3">
-        <v>21.291463851928711</v>
+        <v>22.927410125732418</v>
       </c>
       <c r="BF143" s="3">
-        <v>22.927410125732418</v>
+        <v>14.872251510620121</v>
       </c>
       <c r="BG143" s="3">
-        <v>14.872251510620121</v>
-      </c>
-      <c r="BH143" s="3">
         <v>45.878345489501953</v>
       </c>
     </row>
-    <row r="144" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A144" s="2">
         <v>45498</v>
       </c>
@@ -26815,28 +26386,25 @@
         <v>12.49672794342041</v>
       </c>
       <c r="BB144" s="3">
-        <v>-1.5677337646484379</v>
+        <v>8.2799997329711914</v>
       </c>
       <c r="BC144" s="3">
-        <v>8.2799997329711914</v>
+        <v>55.742774963378913</v>
       </c>
       <c r="BD144" s="3">
-        <v>55.742774963378913</v>
+        <v>21.207529067993161</v>
       </c>
       <c r="BE144" s="3">
-        <v>21.207529067993161</v>
+        <v>22.78729248046875</v>
       </c>
       <c r="BF144" s="3">
-        <v>22.78729248046875</v>
+        <v>15.103104591369631</v>
       </c>
       <c r="BG144" s="3">
-        <v>15.103104591369631</v>
-      </c>
-      <c r="BH144" s="3">
         <v>45.189929962158203</v>
       </c>
     </row>
-    <row r="145" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A145" s="2">
         <v>45499</v>
       </c>
@@ -26997,28 +26565,25 @@
         <v>12.68427848815918</v>
       </c>
       <c r="BB145" s="3">
-        <v>-1.557212114334106</v>
+        <v>6.3299999237060547</v>
       </c>
       <c r="BC145" s="3">
-        <v>6.3299999237060547</v>
+        <v>56.571048736572273</v>
       </c>
       <c r="BD145" s="3">
-        <v>56.571048736572273</v>
+        <v>21.673831939697269</v>
       </c>
       <c r="BE145" s="3">
-        <v>21.673831939697269</v>
+        <v>22.74526214599609</v>
       </c>
       <c r="BF145" s="3">
-        <v>22.74526214599609</v>
+        <v>15.049832344055179</v>
       </c>
       <c r="BG145" s="3">
-        <v>15.049832344055179</v>
-      </c>
-      <c r="BH145" s="3">
         <v>46.143878936767578</v>
       </c>
     </row>
-    <row r="146" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A146" s="2">
         <v>45502</v>
       </c>
@@ -27179,28 +26744,25 @@
         <v>12.516470909118651</v>
       </c>
       <c r="BB146" s="3">
-        <v>-1.540951251983643</v>
+        <v>6.0500001907348633</v>
       </c>
       <c r="BC146" s="3">
-        <v>6.0500001907348633</v>
+        <v>56.672283172607422</v>
       </c>
       <c r="BD146" s="3">
-        <v>56.672283172607422</v>
+        <v>21.543268203735352</v>
       </c>
       <c r="BE146" s="3">
-        <v>21.543268203735352</v>
+        <v>22.719657897949219</v>
       </c>
       <c r="BF146" s="3">
-        <v>22.719657897949219</v>
+        <v>14.765703201293951</v>
       </c>
       <c r="BG146" s="3">
-        <v>14.765703201293951</v>
-      </c>
-      <c r="BH146" s="3">
         <v>45.711158752441413</v>
       </c>
     </row>
-    <row r="147" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A147" s="2">
         <v>45503</v>
       </c>
@@ -27361,28 +26923,25 @@
         <v>12.398018836975099</v>
       </c>
       <c r="BB147" s="3">
-        <v>-1.565820693969727</v>
+        <v>6.3299999237060547</v>
       </c>
       <c r="BC147" s="3">
-        <v>6.3299999237060547</v>
+        <v>55.420673370361328</v>
       </c>
       <c r="BD147" s="3">
-        <v>55.420673370361328</v>
+        <v>21.627204895019531</v>
       </c>
       <c r="BE147" s="3">
-        <v>21.627204895019531</v>
+        <v>22.267620086669918</v>
       </c>
       <c r="BF147" s="3">
-        <v>22.267620086669918</v>
+        <v>14.978798866271971</v>
       </c>
       <c r="BG147" s="3">
-        <v>14.978798866271971</v>
-      </c>
-      <c r="BH147" s="3">
         <v>45.101409912109382</v>
       </c>
     </row>
-    <row r="148" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A148" s="2">
         <v>45504</v>
       </c>
@@ -27543,28 +27102,25 @@
         <v>12.90144062042236</v>
       </c>
       <c r="BB148" s="3">
-        <v>-1.672950863838196</v>
+        <v>6.2199997901916504</v>
       </c>
       <c r="BC148" s="3">
-        <v>6.2199997901916504</v>
+        <v>56.718299865722663</v>
       </c>
       <c r="BD148" s="3">
-        <v>56.718299865722663</v>
+        <v>21.599224090576168</v>
       </c>
       <c r="BE148" s="3">
-        <v>21.599224090576168</v>
+        <v>22.842081069946289</v>
       </c>
       <c r="BF148" s="3">
-        <v>22.842081069946289</v>
+        <v>15.236288070678709</v>
       </c>
       <c r="BG148" s="3">
-        <v>15.236288070678709</v>
-      </c>
-      <c r="BH148" s="3">
         <v>49.822013854980469</v>
       </c>
     </row>
-    <row r="149" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A149" s="2">
         <v>45505</v>
       </c>
@@ -27725,28 +27281,25 @@
         <v>12.852086067199711</v>
       </c>
       <c r="BB149" s="3">
-        <v>-1.6853858232498169</v>
+        <v>6.130000114440918</v>
       </c>
       <c r="BC149" s="3">
-        <v>6.130000114440918</v>
+        <v>55.448280334472663</v>
       </c>
       <c r="BD149" s="3">
-        <v>55.448280334472663</v>
+        <v>21.841701507568359</v>
       </c>
       <c r="BE149" s="3">
-        <v>21.841701507568359</v>
+        <v>23.82621002197266</v>
       </c>
       <c r="BF149" s="3">
-        <v>23.82621002197266</v>
+        <v>15.18301486968994</v>
       </c>
       <c r="BG149" s="3">
-        <v>15.18301486968994</v>
-      </c>
-      <c r="BH149" s="3">
         <v>51.965953826904297</v>
       </c>
     </row>
-    <row r="150" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A150" s="2">
         <v>45506</v>
       </c>
@@ -27907,28 +27460,25 @@
         <v>13.04950618743896</v>
       </c>
       <c r="BB150" s="3">
-        <v>-1.691124796867371</v>
+        <v>5.940000057220459</v>
       </c>
       <c r="BC150" s="3">
-        <v>5.940000057220459</v>
+        <v>54.675224304199219</v>
       </c>
       <c r="BD150" s="3">
-        <v>54.675224304199219</v>
+        <v>21.739114761352539</v>
       </c>
       <c r="BE150" s="3">
-        <v>21.739114761352539</v>
+        <v>23.581356048583981</v>
       </c>
       <c r="BF150" s="3">
-        <v>23.581356048583981</v>
+        <v>15.227407455444339</v>
       </c>
       <c r="BG150" s="3">
-        <v>15.227407455444339</v>
-      </c>
-      <c r="BH150" s="3">
         <v>48.99591064453125</v>
       </c>
     </row>
-    <row r="151" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A151" s="2">
         <v>45509</v>
       </c>
@@ -28089,28 +27639,25 @@
         <v>12.83234310150146</v>
       </c>
       <c r="BB151" s="3">
-        <v>-1.640429019927979</v>
+        <v>5.809999942779541</v>
       </c>
       <c r="BC151" s="3">
-        <v>5.809999942779541</v>
+        <v>54.392673492431641</v>
       </c>
       <c r="BD151" s="3">
-        <v>54.392673492431641</v>
+        <v>21.440679550170898</v>
       </c>
       <c r="BE151" s="3">
-        <v>21.440679550170898</v>
+        <v>23.025724411010739</v>
       </c>
       <c r="BF151" s="3">
-        <v>23.025724411010739</v>
+        <v>14.82785701751709</v>
       </c>
       <c r="BG151" s="3">
-        <v>14.82785701751709</v>
-      </c>
-      <c r="BH151" s="3">
         <v>48.233367919921882</v>
       </c>
     </row>
-    <row r="152" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A152" s="2">
         <v>45510</v>
       </c>
@@ -28271,28 +27818,25 @@
         <v>12.68427848815918</v>
       </c>
       <c r="BB152" s="3">
-        <v>-1.639472484588623</v>
+        <v>5.7699999809265137</v>
       </c>
       <c r="BC152" s="3">
-        <v>5.7699999809265137</v>
+        <v>54.6693115234375</v>
       </c>
       <c r="BD152" s="3">
-        <v>54.6693115234375</v>
+        <v>21.92563629150391</v>
       </c>
       <c r="BE152" s="3">
-        <v>21.92563629150391</v>
+        <v>23.044559478759769</v>
       </c>
       <c r="BF152" s="3">
-        <v>23.044559478759769</v>
+        <v>15.07646656036377</v>
       </c>
       <c r="BG152" s="3">
-        <v>15.07646656036377</v>
-      </c>
-      <c r="BH152" s="3">
         <v>48.341960906982422</v>
       </c>
     </row>
-    <row r="153" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A153" s="2">
         <v>45511</v>
       </c>
@@ -28453,28 +27997,25 @@
         <v>13.2271842956543</v>
       </c>
       <c r="BB153" s="3">
-        <v>-1.662429094314575</v>
+        <v>5.7300000190734863</v>
       </c>
       <c r="BC153" s="3">
-        <v>5.7300000190734863</v>
+        <v>54.564380645751953</v>
       </c>
       <c r="BD153" s="3">
-        <v>54.564380645751953</v>
+        <v>22.47587776184082</v>
       </c>
       <c r="BE153" s="3">
-        <v>22.47587776184082</v>
+        <v>23.402421951293949</v>
       </c>
       <c r="BF153" s="3">
-        <v>23.402421951293949</v>
+        <v>15.37835216522217</v>
       </c>
       <c r="BG153" s="3">
-        <v>15.37835216522217</v>
-      </c>
-      <c r="BH153" s="3">
         <v>47.700290679931641</v>
       </c>
     </row>
-    <row r="154" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A154" s="2">
         <v>45512</v>
       </c>
@@ -28635,28 +28176,25 @@
         <v>12.67440700531006</v>
       </c>
       <c r="BB154" s="3">
-        <v>-1.655733466148376</v>
+        <v>5.8299999237060547</v>
       </c>
       <c r="BC154" s="3">
-        <v>5.8299999237060547</v>
+        <v>54.230503082275391</v>
       </c>
       <c r="BD154" s="3">
-        <v>54.230503082275391</v>
+        <v>22.48520469665527</v>
       </c>
       <c r="BE154" s="3">
-        <v>22.48520469665527</v>
+        <v>23.7744140625</v>
       </c>
       <c r="BF154" s="3">
-        <v>23.7744140625</v>
+        <v>17.083110809326168</v>
       </c>
       <c r="BG154" s="3">
-        <v>17.083110809326168</v>
-      </c>
-      <c r="BH154" s="3">
         <v>49.052722930908203</v>
       </c>
     </row>
-    <row r="155" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A155" s="2">
         <v>45513</v>
       </c>
@@ -28817,28 +28355,25 @@
         <v>13.01989269256592</v>
       </c>
       <c r="BB155" s="3">
-        <v>-1.6853858232498169</v>
+        <v>5.9499998092651367</v>
       </c>
       <c r="BC155" s="3">
-        <v>5.9499998092651367</v>
+        <v>54.430828094482422</v>
       </c>
       <c r="BD155" s="3">
-        <v>54.430828094482422</v>
+        <v>23.082073211669918</v>
       </c>
       <c r="BE155" s="3">
-        <v>23.082073211669918</v>
+        <v>23.901548385620121</v>
       </c>
       <c r="BF155" s="3">
-        <v>23.901548385620121</v>
+        <v>17.615848541259769</v>
       </c>
       <c r="BG155" s="3">
-        <v>17.615848541259769</v>
-      </c>
-      <c r="BH155" s="3">
         <v>49.062595367431641</v>
       </c>
     </row>
-    <row r="156" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A156" s="2">
         <v>45516</v>
       </c>
@@ -28999,28 +28534,25 @@
         <v>12.694149017333981</v>
       </c>
       <c r="BB156" s="3">
-        <v>-1.691124796867371</v>
+        <v>6.059999942779541</v>
       </c>
       <c r="BC156" s="3">
-        <v>6.059999942779541</v>
+        <v>54.154193878173828</v>
       </c>
       <c r="BD156" s="3">
-        <v>54.154193878173828</v>
+        <v>22.830268859863281</v>
       </c>
       <c r="BE156" s="3">
-        <v>22.830268859863281</v>
+        <v>23.845046997070309</v>
       </c>
       <c r="BF156" s="3">
-        <v>23.845046997070309</v>
+        <v>18.460319519042969</v>
       </c>
       <c r="BG156" s="3">
-        <v>18.460319519042969</v>
-      </c>
-      <c r="BH156" s="3">
         <v>49.931312561035163</v>
       </c>
     </row>
-    <row r="157" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A157" s="2">
         <v>45517</v>
       </c>
@@ -29181,28 +28713,25 @@
         <v>12.911312103271481</v>
       </c>
       <c r="BB157" s="3">
-        <v>-1.707385659217834</v>
+        <v>6.25</v>
       </c>
       <c r="BC157" s="3">
-        <v>6.25</v>
+        <v>53.915714263916023</v>
       </c>
       <c r="BD157" s="3">
-        <v>53.915714263916023</v>
+        <v>23.59500694274902</v>
       </c>
       <c r="BE157" s="3">
-        <v>23.59500694274902</v>
+        <v>24.023977279663089</v>
       </c>
       <c r="BF157" s="3">
-        <v>24.023977279663089</v>
+        <v>18.20606803894043</v>
       </c>
       <c r="BG157" s="3">
-        <v>18.20606803894043</v>
-      </c>
-      <c r="BH157" s="3">
         <v>50.474254608154297</v>
       </c>
     </row>
-    <row r="158" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A158" s="2">
         <v>45518</v>
       </c>
@@ -29363,28 +28892,25 @@
         <v>13.01989269256592</v>
       </c>
       <c r="BB158" s="3">
-        <v>-1.731298565864563</v>
+        <v>6.0900001525878906</v>
       </c>
       <c r="BC158" s="3">
-        <v>6.0900001525878906</v>
+        <v>53.419670104980469</v>
       </c>
       <c r="BD158" s="3">
-        <v>53.419670104980469</v>
+        <v>23.5390510559082</v>
       </c>
       <c r="BE158" s="3">
-        <v>23.5390510559082</v>
+        <v>24.306497573852539</v>
       </c>
       <c r="BF158" s="3">
-        <v>24.306497573852539</v>
+        <v>18.914335250854489</v>
       </c>
       <c r="BG158" s="3">
-        <v>18.914335250854489</v>
-      </c>
-      <c r="BH158" s="3">
         <v>50.878997802734382</v>
       </c>
     </row>
-    <row r="159" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A159" s="2">
         <v>45519</v>
       </c>
@@ -29545,28 +29071,25 @@
         <v>13.4443473815918</v>
       </c>
       <c r="BB159" s="3">
-        <v>-1.719820022583008</v>
+        <v>6.179999828338623</v>
       </c>
       <c r="BC159" s="3">
-        <v>6.179999828338623</v>
+        <v>53.639072418212891</v>
       </c>
       <c r="BD159" s="3">
-        <v>53.639072418212891</v>
+        <v>24.079963684082031</v>
       </c>
       <c r="BE159" s="3">
-        <v>24.079963684082031</v>
+        <v>23.981599807739261</v>
       </c>
       <c r="BF159" s="3">
-        <v>23.981599807739261</v>
+        <v>18.769050598144531</v>
       </c>
       <c r="BG159" s="3">
-        <v>18.769050598144531</v>
-      </c>
-      <c r="BH159" s="3">
         <v>52.024120330810547</v>
       </c>
     </row>
-    <row r="160" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A160" s="2">
         <v>45520</v>
       </c>
@@ -29727,28 +29250,25 @@
         <v>13.10873222351074</v>
       </c>
       <c r="BB160" s="3">
-        <v>-1.749472379684448</v>
+        <v>6.0799999237060547</v>
       </c>
       <c r="BC160" s="3">
-        <v>6.0799999237060547</v>
+        <v>53.495986938476563</v>
       </c>
       <c r="BD160" s="3">
-        <v>53.495986938476563</v>
+        <v>24.275812149047852</v>
       </c>
       <c r="BE160" s="3">
-        <v>24.275812149047852</v>
+        <v>24.579607009887699</v>
       </c>
       <c r="BF160" s="3">
-        <v>24.579607009887699</v>
+        <v>19.27754974365234</v>
       </c>
       <c r="BG160" s="3">
-        <v>19.27754974365234</v>
-      </c>
-      <c r="BH160" s="3">
         <v>52.567066192626953</v>
       </c>
     </row>
-    <row r="161" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A161" s="2">
         <v>45523</v>
       </c>
@@ -29909,28 +29429,25 @@
         <v>13.473959922790529</v>
       </c>
       <c r="BB161" s="3">
-        <v>-1.747559189796448</v>
+        <v>6.5</v>
       </c>
       <c r="BC161" s="3">
-        <v>6.5</v>
+        <v>54.354515075683587</v>
       </c>
       <c r="BD161" s="3">
-        <v>54.354515075683587</v>
+        <v>24.480985641479489</v>
       </c>
       <c r="BE161" s="3">
-        <v>24.480985641479489</v>
+        <v>24.541936874389648</v>
       </c>
       <c r="BF161" s="3">
-        <v>24.541936874389648</v>
+        <v>19.386514663696289</v>
       </c>
       <c r="BG161" s="3">
-        <v>19.386514663696289</v>
-      </c>
-      <c r="BH161" s="3">
         <v>51.12579345703125</v>
       </c>
     </row>
-    <row r="162" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A162" s="2">
         <v>45524</v>
       </c>
@@ -30091,28 +29608,25 @@
         <v>13.70099449157715</v>
       </c>
       <c r="BB162" s="3">
-        <v>-1.752341747283936</v>
+        <v>6.4499998092651367</v>
       </c>
       <c r="BC162" s="3">
-        <v>6.4499998092651367</v>
+        <v>54.564380645751953</v>
       </c>
       <c r="BD162" s="3">
-        <v>54.564380645751953</v>
+        <v>24.369071960449219</v>
       </c>
       <c r="BE162" s="3">
-        <v>24.369071960449219</v>
+        <v>24.687908172607418</v>
       </c>
       <c r="BF162" s="3">
-        <v>24.687908172607418</v>
+        <v>19.976736068725589</v>
       </c>
       <c r="BG162" s="3">
-        <v>19.976736068725589</v>
-      </c>
-      <c r="BH162" s="3">
         <v>52.428859710693359</v>
       </c>
     </row>
-    <row r="163" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A163" s="2">
         <v>45525</v>
       </c>
@@ -30273,28 +29787,25 @@
         <v>13.740478515625</v>
       </c>
       <c r="BB163" s="3">
-        <v>-1.745646476745605</v>
+        <v>6.6399998664855957</v>
       </c>
       <c r="BC163" s="3">
-        <v>6.6399998664855957</v>
+        <v>55.613693237304688</v>
       </c>
       <c r="BD163" s="3">
-        <v>55.613693237304688</v>
+        <v>24.322443008422852</v>
       </c>
       <c r="BE163" s="3">
-        <v>24.322443008422852</v>
+        <v>24.758537292480469</v>
       </c>
       <c r="BF163" s="3">
-        <v>24.758537292480469</v>
+        <v>19.677083969116211</v>
       </c>
       <c r="BG163" s="3">
-        <v>19.677083969116211</v>
-      </c>
-      <c r="BH163" s="3">
         <v>52.744758605957031</v>
       </c>
     </row>
-    <row r="164" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A164" s="2">
         <v>45526</v>
       </c>
@@ -30455,28 +29966,25 @@
         <v>13.069248199462891</v>
       </c>
       <c r="BB164" s="3">
-        <v>-1.711211681365967</v>
+        <v>6.4099998474121094</v>
       </c>
       <c r="BC164" s="3">
-        <v>6.4099998474121094</v>
+        <v>55.690006256103523</v>
       </c>
       <c r="BD164" s="3">
-        <v>55.690006256103523</v>
+        <v>23.483095169067379</v>
       </c>
       <c r="BE164" s="3">
-        <v>23.483095169067379</v>
+        <v>24.466594696044918</v>
       </c>
       <c r="BF164" s="3">
-        <v>24.466594696044918</v>
+        <v>19.559040069580082</v>
       </c>
       <c r="BG164" s="3">
-        <v>19.559040069580082</v>
-      </c>
-      <c r="BH164" s="3">
         <v>53.5048828125</v>
       </c>
     </row>
-    <row r="165" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A165" s="2">
         <v>45527</v>
       </c>
@@ -30637,28 +30145,25 @@
         <v>13.839189529418951</v>
       </c>
       <c r="BB165" s="3">
-        <v>-1.735124468803406</v>
+        <v>6.5799999237060547</v>
       </c>
       <c r="BC165" s="3">
-        <v>6.5799999237060547</v>
+        <v>54.755165100097663</v>
       </c>
       <c r="BD165" s="3">
-        <v>54.755165100097663</v>
+        <v>23.73489952087402</v>
       </c>
       <c r="BE165" s="3">
-        <v>23.73489952087402</v>
+        <v>25.03635406494141</v>
       </c>
       <c r="BF165" s="3">
-        <v>25.03635406494141</v>
+        <v>20.131101608276371</v>
       </c>
       <c r="BG165" s="3">
-        <v>20.131101608276371</v>
-      </c>
-      <c r="BH165" s="3">
         <v>53.119880676269531</v>
       </c>
     </row>
-    <row r="166" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A166" s="2">
         <v>45530</v>
       </c>
@@ -30819,28 +30324,25 @@
         <v>13.67138195037842</v>
       </c>
       <c r="BB166" s="3">
-        <v>-1.718863725662231</v>
+        <v>6.5999999046325684</v>
       </c>
       <c r="BC166" s="3">
-        <v>6.5999999046325684</v>
+        <v>55.375209808349609</v>
       </c>
       <c r="BD166" s="3">
-        <v>55.375209808349609</v>
+        <v>23.846811294555661</v>
       </c>
       <c r="BE166" s="3">
-        <v>23.846811294555661</v>
+        <v>24.669073104858398</v>
       </c>
       <c r="BF166" s="3">
-        <v>24.669073104858398</v>
+        <v>20.430751800537109</v>
       </c>
       <c r="BG166" s="3">
-        <v>20.430751800537109</v>
-      </c>
-      <c r="BH166" s="3">
         <v>53.386425018310547</v>
       </c>
     </row>
-    <row r="167" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A167" s="2">
         <v>45531</v>
       </c>
@@ -31001,28 +30503,25 @@
         <v>13.77996253967285</v>
       </c>
       <c r="BB167" s="3">
-        <v>-1.707385659217834</v>
+        <v>6.4600000381469727</v>
       </c>
       <c r="BC167" s="3">
-        <v>6.4600000381469727</v>
+        <v>57.044574737548828</v>
       </c>
       <c r="BD167" s="3">
-        <v>57.044574737548828</v>
+        <v>23.856138229370121</v>
       </c>
       <c r="BE167" s="3">
-        <v>23.856138229370121</v>
+        <v>24.571695327758789</v>
       </c>
       <c r="BF167" s="3">
-        <v>24.571695327758789</v>
+        <v>19.749727249145511</v>
       </c>
       <c r="BG167" s="3">
-        <v>19.749727249145511</v>
-      </c>
-      <c r="BH167" s="3">
         <v>53.307445526123047</v>
       </c>
     </row>
-    <row r="168" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A168" s="2">
         <v>45532</v>
       </c>
@@ -31183,28 +30682,25 @@
         <v>13.622026443481451</v>
       </c>
       <c r="BB168" s="3">
-        <v>-1.7322549819946289</v>
+        <v>6.2399997711181641</v>
       </c>
       <c r="BC168" s="3">
-        <v>6.2399997711181641</v>
+        <v>56.634387969970703</v>
       </c>
       <c r="BD168" s="3">
-        <v>56.634387969970703</v>
+        <v>24.070636749267582</v>
       </c>
       <c r="BE168" s="3">
-        <v>24.070636749267582</v>
+        <v>24.600078582763668</v>
       </c>
       <c r="BF168" s="3">
-        <v>24.600078582763668</v>
+        <v>20.812124252319339</v>
       </c>
       <c r="BG168" s="3">
-        <v>20.812124252319339</v>
-      </c>
-      <c r="BH168" s="3">
         <v>53.307445526123047</v>
       </c>
     </row>
-    <row r="169" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A169" s="2">
         <v>45533</v>
       </c>
@@ -31365,28 +30861,25 @@
         <v>13.098861694335939</v>
       </c>
       <c r="BB169" s="3">
-        <v>-1.715994119644165</v>
+        <v>6.2300000190734863</v>
       </c>
       <c r="BC169" s="3">
-        <v>6.2300000190734863</v>
+        <v>56.567615509033203</v>
       </c>
       <c r="BD169" s="3">
-        <v>56.567615509033203</v>
+        <v>23.86546516418457</v>
       </c>
       <c r="BE169" s="3">
-        <v>23.86546516418457</v>
+        <v>24.514925003051761</v>
       </c>
       <c r="BF169" s="3">
-        <v>24.514925003051761</v>
+        <v>20.71224212646484</v>
       </c>
       <c r="BG169" s="3">
-        <v>20.71224212646484</v>
-      </c>
-      <c r="BH169" s="3">
         <v>52.853347778320313</v>
       </c>
     </row>
-    <row r="170" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A170" s="2">
         <v>45534</v>
       </c>
@@ -31547,28 +31040,25 @@
         <v>13.2271842956543</v>
       </c>
       <c r="BB170" s="3">
-        <v>-1.7083419561386111</v>
+        <v>6.2300000190734863</v>
       </c>
       <c r="BC170" s="3">
-        <v>6.2300000190734863</v>
+        <v>56.834716796875</v>
       </c>
       <c r="BD170" s="3">
-        <v>56.834716796875</v>
+        <v>23.986703872680661</v>
       </c>
       <c r="BE170" s="3">
-        <v>23.986703872680661</v>
+        <v>24.519659042358398</v>
       </c>
       <c r="BF170" s="3">
-        <v>24.519659042358398</v>
+        <v>20.657758712768551</v>
       </c>
       <c r="BG170" s="3">
-        <v>20.657758712768551</v>
-      </c>
-      <c r="BH170" s="3">
         <v>53.455524444580078</v>
       </c>
     </row>
-    <row r="171" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A171" s="2">
         <v>45537</v>
       </c>
@@ -31729,28 +31219,25 @@
         <v>13.10873222351074</v>
       </c>
       <c r="BB171" s="3">
-        <v>-1.702602863311768</v>
+        <v>6.1599998474121094</v>
       </c>
       <c r="BC171" s="3">
-        <v>6.1599998474121094</v>
+        <v>56.033420562744141</v>
       </c>
       <c r="BD171" s="3">
-        <v>56.033420562744141</v>
+        <v>23.68826866149902</v>
       </c>
       <c r="BE171" s="3">
-        <v>23.68826866149902</v>
+        <v>24.704158782958981</v>
       </c>
       <c r="BF171" s="3">
-        <v>24.704158782958981</v>
+        <v>20.566957473754879</v>
       </c>
       <c r="BG171" s="3">
-        <v>20.566957473754879</v>
-      </c>
-      <c r="BH171" s="3">
         <v>51.678607940673828</v>
       </c>
     </row>
-    <row r="172" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A172" s="2">
         <v>45538</v>
       </c>
@@ -31911,28 +31398,25 @@
         <v>12.83234310150146</v>
       </c>
       <c r="BB172" s="3">
-        <v>-1.7255592346191411</v>
+        <v>5.9600000381469727</v>
       </c>
       <c r="BC172" s="3">
-        <v>5.9600000381469727</v>
+        <v>53.944328308105469</v>
       </c>
       <c r="BD172" s="3">
-        <v>53.944328308105469</v>
+        <v>23.986703872680661</v>
       </c>
       <c r="BE172" s="3">
-        <v>23.986703872680661</v>
+        <v>25.172504425048832</v>
       </c>
       <c r="BF172" s="3">
-        <v>25.172504425048832</v>
+        <v>20.51247406005859</v>
       </c>
       <c r="BG172" s="3">
-        <v>20.51247406005859</v>
-      </c>
-      <c r="BH172" s="3">
         <v>52.122840881347663</v>
       </c>
     </row>
-    <row r="173" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A173" s="2">
         <v>45539</v>
       </c>
@@ -32093,28 +31577,25 @@
         <v>13.207443237304689</v>
       </c>
       <c r="BB173" s="3">
-        <v>-1.752341747283936</v>
+        <v>6.0799999237060547</v>
       </c>
       <c r="BC173" s="3">
-        <v>6.0799999237060547</v>
+        <v>54.364055633544922</v>
       </c>
       <c r="BD173" s="3">
-        <v>54.364055633544922</v>
+        <v>24.331768035888668</v>
       </c>
       <c r="BE173" s="3">
-        <v>24.331768035888668</v>
+        <v>25.787504196166989</v>
       </c>
       <c r="BF173" s="3">
-        <v>25.787504196166989</v>
+        <v>21.102695465087891</v>
       </c>
       <c r="BG173" s="3">
-        <v>21.102695465087891</v>
-      </c>
-      <c r="BH173" s="3">
         <v>52.705272674560547</v>
       </c>
     </row>
-    <row r="174" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A174" s="2">
         <v>45540</v>
       </c>
@@ -32275,28 +31756,25 @@
         <v>13.33576679229736</v>
       </c>
       <c r="BB174" s="3">
-        <v>-1.7819938659667971</v>
+        <v>6.0799999237060547</v>
       </c>
       <c r="BC174" s="3">
-        <v>6.0799999237060547</v>
+        <v>54.755165100097663</v>
       </c>
       <c r="BD174" s="3">
-        <v>54.755165100097663</v>
+        <v>24.714138031005859</v>
       </c>
       <c r="BE174" s="3">
-        <v>24.714138031005859</v>
+        <v>26.07608795166016</v>
       </c>
       <c r="BF174" s="3">
-        <v>26.07608795166016</v>
+        <v>21.03005218505859</v>
       </c>
       <c r="BG174" s="3">
-        <v>21.03005218505859</v>
-      </c>
-      <c r="BH174" s="3">
         <v>53.297576904296882</v>
       </c>
     </row>
-    <row r="175" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A175" s="2">
         <v>45541</v>
       </c>
@@ -32457,28 +31935,25 @@
         <v>13.01989269256592</v>
       </c>
       <c r="BB175" s="3">
-        <v>-1.760950446128845</v>
+        <v>5.9899997711181641</v>
       </c>
       <c r="BC175" s="3">
-        <v>5.9899997711181641</v>
+        <v>54.068340301513672</v>
       </c>
       <c r="BD175" s="3">
-        <v>54.068340301513672</v>
+        <v>24.163900375366211</v>
       </c>
       <c r="BE175" s="3">
-        <v>24.163900375366211</v>
+        <v>26.000392913818359</v>
       </c>
       <c r="BF175" s="3">
-        <v>26.000392913818359</v>
+        <v>20.784883499145511</v>
       </c>
       <c r="BG175" s="3">
-        <v>20.784883499145511</v>
-      </c>
-      <c r="BH175" s="3">
         <v>52.201812744140618</v>
       </c>
     </row>
-    <row r="176" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A176" s="2">
         <v>45544</v>
       </c>
@@ -32639,28 +32114,25 @@
         <v>12.83234310150146</v>
       </c>
       <c r="BB176" s="3">
-        <v>-1.7341679334640501</v>
+        <v>5.8400001525878906</v>
       </c>
       <c r="BC176" s="3">
-        <v>5.8400001525878906</v>
+        <v>54.068340301513672</v>
       </c>
       <c r="BD176" s="3">
-        <v>54.068340301513672</v>
+        <v>24.294464111328121</v>
       </c>
       <c r="BE176" s="3">
-        <v>24.294464111328121</v>
+        <v>25.63612174987793</v>
       </c>
       <c r="BF176" s="3">
-        <v>25.63612174987793</v>
+        <v>20.612360000610352</v>
       </c>
       <c r="BG176" s="3">
-        <v>20.612360000610352</v>
-      </c>
-      <c r="BH176" s="3">
         <v>51.777328491210938</v>
       </c>
     </row>
-    <row r="177" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A177" s="2">
         <v>45545</v>
       </c>
@@ -32821,28 +32293,25 @@
         <v>12.79285907745361</v>
       </c>
       <c r="BB177" s="3">
-        <v>-1.74277663230896</v>
+        <v>5.7699999809265137</v>
       </c>
       <c r="BC177" s="3">
-        <v>5.7699999809265137</v>
+        <v>53.419670104980469</v>
       </c>
       <c r="BD177" s="3">
-        <v>53.419670104980469</v>
+        <v>24.107944488525391</v>
       </c>
       <c r="BE177" s="3">
-        <v>24.107944488525391</v>
+        <v>25.72127723693848</v>
       </c>
       <c r="BF177" s="3">
-        <v>25.72127723693848</v>
+        <v>20.83936882019043</v>
       </c>
       <c r="BG177" s="3">
-        <v>20.83936882019043</v>
-      </c>
-      <c r="BH177" s="3">
         <v>52.211685180664063</v>
       </c>
     </row>
-    <row r="178" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A178" s="2">
         <v>45546</v>
       </c>
@@ -33003,28 +32472,25 @@
         <v>12.78298854827881</v>
       </c>
       <c r="BB178" s="3">
-        <v>-1.758080840110779</v>
+        <v>5.9099998474121094</v>
       </c>
       <c r="BC178" s="3">
-        <v>5.9099998474121094</v>
+        <v>54.936408996582031</v>
       </c>
       <c r="BD178" s="3">
-        <v>54.936408996582031</v>
+        <v>24.033334732055661</v>
       </c>
       <c r="BE178" s="3">
-        <v>24.033334732055661</v>
+        <v>25.849008560180661</v>
       </c>
       <c r="BF178" s="3">
-        <v>25.849008560180661</v>
+        <v>21.42958831787109</v>
       </c>
       <c r="BG178" s="3">
-        <v>21.42958831787109</v>
-      </c>
-      <c r="BH178" s="3">
         <v>52.813858032226563</v>
       </c>
     </row>
-    <row r="179" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A179" s="2">
         <v>45547</v>
       </c>
@@ -33185,28 +32651,25 @@
         <v>12.68427848815918</v>
       </c>
       <c r="BB179" s="3">
-        <v>-1.740863561630249</v>
+        <v>5.9099998474121094</v>
       </c>
       <c r="BC179" s="3">
-        <v>5.9099998474121094</v>
+        <v>55.432445526123047</v>
       </c>
       <c r="BD179" s="3">
-        <v>55.432445526123047</v>
+        <v>23.95872688293457</v>
       </c>
       <c r="BE179" s="3">
-        <v>23.95872688293457</v>
+        <v>25.830083847045898</v>
       </c>
       <c r="BF179" s="3">
-        <v>25.830083847045898</v>
+        <v>20.51247406005859</v>
       </c>
       <c r="BG179" s="3">
-        <v>20.51247406005859</v>
-      </c>
-      <c r="BH179" s="3">
         <v>52.626293182373047</v>
       </c>
     </row>
-    <row r="180" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A180" s="2">
         <v>45548</v>
       </c>
@@ -33367,28 +32830,25 @@
         <v>13.404863357543951</v>
       </c>
       <c r="BB180" s="3">
-        <v>-1.7599940299987791</v>
+        <v>6.1700000762939453</v>
       </c>
       <c r="BC180" s="3">
-        <v>6.1700000762939453</v>
+        <v>55.804477691650391</v>
       </c>
       <c r="BD180" s="3">
-        <v>55.804477691650391</v>
+        <v>23.576356887817379</v>
       </c>
       <c r="BE180" s="3">
-        <v>23.576356887817379</v>
+        <v>25.948354721069339</v>
       </c>
       <c r="BF180" s="3">
-        <v>25.948354721069339</v>
+        <v>22.0107307434082</v>
       </c>
       <c r="BG180" s="3">
-        <v>22.0107307434082</v>
-      </c>
-      <c r="BH180" s="3">
         <v>52.932315826416023</v>
       </c>
     </row>
-    <row r="181" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A181" s="2">
         <v>45551</v>
       </c>
@@ -33549,28 +33009,25 @@
         <v>14.303127288818359</v>
       </c>
       <c r="BB181" s="3">
-        <v>-1.7848635911941531</v>
+        <v>6.0500001907348633</v>
       </c>
       <c r="BC181" s="3">
-        <v>6.0500001907348633</v>
+        <v>55.804477691650391</v>
       </c>
       <c r="BD181" s="3">
-        <v>55.804477691650391</v>
+        <v>23.072746276855469</v>
       </c>
       <c r="BE181" s="3">
-        <v>23.072746276855469</v>
+        <v>26.39777755737305</v>
       </c>
       <c r="BF181" s="3">
-        <v>26.39777755737305</v>
+        <v>21.765560150146481</v>
       </c>
       <c r="BG181" s="3">
-        <v>21.765560150146481</v>
-      </c>
-      <c r="BH181" s="3">
         <v>52.320270538330078</v>
       </c>
     </row>
-    <row r="182" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A182" s="2">
         <v>45552</v>
       </c>
@@ -33731,28 +33188,25 @@
         <v>14.39196681976318</v>
       </c>
       <c r="BB182" s="3">
-        <v>-1.7829505205154419</v>
+        <v>6.0900001525878906</v>
       </c>
       <c r="BC182" s="3">
-        <v>6.0900001525878906</v>
+        <v>55.537380218505859</v>
       </c>
       <c r="BD182" s="3">
-        <v>55.537380218505859</v>
+        <v>23.259267807006839</v>
       </c>
       <c r="BE182" s="3">
-        <v>23.259267807006839</v>
+        <v>26.331546783447269</v>
       </c>
       <c r="BF182" s="3">
-        <v>26.331546783447269</v>
+        <v>21.711078643798832</v>
       </c>
       <c r="BG182" s="3">
-        <v>21.711078643798832</v>
-      </c>
-      <c r="BH182" s="3">
         <v>52.636165618896477</v>
       </c>
     </row>
-    <row r="183" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A183" s="2">
         <v>45553</v>
       </c>
@@ -33913,28 +33367,25 @@
         <v>14.382095336914061</v>
       </c>
       <c r="BB183" s="3">
-        <v>-1.794428825378418</v>
+        <v>6.2600002288818359</v>
       </c>
       <c r="BC183" s="3">
-        <v>6.2600002288818359</v>
+        <v>54.888713836669922</v>
       </c>
       <c r="BD183" s="3">
-        <v>54.888713836669922</v>
+        <v>22.998138427734379</v>
       </c>
       <c r="BE183" s="3">
-        <v>22.998138427734379</v>
+        <v>26.402509689331051</v>
       </c>
       <c r="BF183" s="3">
-        <v>26.402509689331051</v>
+        <v>21.647518157958981</v>
       </c>
       <c r="BG183" s="3">
-        <v>21.647518157958981</v>
-      </c>
-      <c r="BH183" s="3">
         <v>52.912578582763672</v>
       </c>
     </row>
-    <row r="184" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A184" s="2">
         <v>45554</v>
       </c>
@@ -34095,28 +33546,25 @@
         <v>14.016867637634279</v>
       </c>
       <c r="BB184" s="3">
-        <v>-1.768602609634399</v>
+        <v>6.2300000190734863</v>
       </c>
       <c r="BC184" s="3">
-        <v>6.2300000190734863</v>
+        <v>55.546916961669922</v>
       </c>
       <c r="BD184" s="3">
-        <v>55.546916961669922</v>
+        <v>22.848920822143551</v>
       </c>
       <c r="BE184" s="3">
-        <v>22.848920822143551</v>
+        <v>26.113933563232418</v>
       </c>
       <c r="BF184" s="3">
-        <v>26.113933563232418</v>
+        <v>21.011892318725589</v>
       </c>
       <c r="BG184" s="3">
-        <v>21.011892318725589</v>
-      </c>
-      <c r="BH184" s="3">
         <v>52.576938629150391</v>
       </c>
     </row>
-    <row r="185" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A185" s="2">
         <v>45555</v>
       </c>
@@ -34277,28 +33725,25 @@
         <v>13.12847423553467</v>
       </c>
       <c r="BB185" s="3">
-        <v>-1.791559219360352</v>
+        <v>5.880000114440918</v>
       </c>
       <c r="BC185" s="3">
-        <v>5.880000114440918</v>
+        <v>54.707466125488281</v>
       </c>
       <c r="BD185" s="3">
-        <v>54.707466125488281</v>
+        <v>23.110052108764648</v>
       </c>
       <c r="BE185" s="3">
-        <v>23.110052108764648</v>
+        <v>26.151777267456051</v>
       </c>
       <c r="BF185" s="3">
-        <v>26.151777267456051</v>
+        <v>21.338785171508789</v>
       </c>
       <c r="BG185" s="3">
-        <v>21.338785171508789</v>
-      </c>
-      <c r="BH185" s="3">
         <v>51.846427917480469</v>
       </c>
     </row>
-    <row r="186" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A186" s="2">
         <v>45558</v>
       </c>
@@ -34459,28 +33904,25 @@
         <v>12.595438957214361</v>
       </c>
       <c r="BB186" s="3">
-        <v>-1.791559219360352</v>
+        <v>5.5999999046325684</v>
       </c>
       <c r="BC186" s="3">
-        <v>5.5999999046325684</v>
+        <v>54.879169464111328</v>
       </c>
       <c r="BD186" s="3">
-        <v>54.879169464111328</v>
+        <v>22.17744255065918</v>
       </c>
       <c r="BE186" s="3">
-        <v>22.17744255065918</v>
+        <v>25.986198425292969</v>
       </c>
       <c r="BF186" s="3">
-        <v>25.986198425292969</v>
+        <v>20.775802612304691</v>
       </c>
       <c r="BG186" s="3">
-        <v>20.775802612304691</v>
-      </c>
-      <c r="BH186" s="3">
         <v>53.623340606689453</v>
       </c>
     </row>
-    <row r="187" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A187" s="2">
         <v>45559</v>
       </c>
@@ -34641,28 +34083,25 @@
         <v>12.694149017333981</v>
       </c>
       <c r="BB187" s="3">
-        <v>-5.3135318756103516</v>
+        <v>6.0300002098083496</v>
       </c>
       <c r="BC187" s="3">
-        <v>6.0300002098083496</v>
+        <v>57.559696197509773</v>
       </c>
       <c r="BD187" s="3">
-        <v>57.559696197509773</v>
+        <v>22.794389724731449</v>
       </c>
       <c r="BE187" s="3">
-        <v>22.794389724731449</v>
+        <v>26.151777267456051</v>
       </c>
       <c r="BF187" s="3">
-        <v>26.151777267456051</v>
+        <v>20.557876586914059</v>
       </c>
       <c r="BG187" s="3">
-        <v>20.557876586914059</v>
-      </c>
-      <c r="BH187" s="3">
         <v>54.67962646484375</v>
       </c>
     </row>
-    <row r="188" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A188" s="2">
         <v>45560</v>
       </c>
@@ -34823,28 +34262,25 @@
         <v>12.368404388427731</v>
       </c>
       <c r="BB188" s="3">
-        <v>-5.2993922233581543</v>
+        <v>6.0399999618530273</v>
       </c>
       <c r="BC188" s="3">
-        <v>6.0399999618530273</v>
+        <v>57.817256927490227</v>
       </c>
       <c r="BD188" s="3">
-        <v>57.817256927490227</v>
+        <v>22.615425109863281</v>
       </c>
       <c r="BE188" s="3">
-        <v>22.615425109863281</v>
+        <v>26.255859375</v>
       </c>
       <c r="BF188" s="3">
-        <v>26.255859375</v>
+        <v>20.358110427856449</v>
       </c>
       <c r="BG188" s="3">
-        <v>20.358110427856449</v>
-      </c>
-      <c r="BH188" s="3">
         <v>54.965900421142578</v>
       </c>
     </row>
-    <row r="189" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A189" s="2">
         <v>45561</v>
       </c>
@@ -35005,28 +34441,25 @@
         <v>12.34866333007812</v>
       </c>
       <c r="BB189" s="3">
-        <v>-5.2795977592468262</v>
+        <v>6.380000114440918</v>
       </c>
       <c r="BC189" s="3">
-        <v>6.380000114440918</v>
+        <v>61.289531707763672</v>
       </c>
       <c r="BD189" s="3">
-        <v>61.289531707763672</v>
+        <v>22.700197219848629</v>
       </c>
       <c r="BE189" s="3">
-        <v>22.700197219848629</v>
+        <v>26.04770469665527</v>
       </c>
       <c r="BF189" s="3">
-        <v>26.04770469665527</v>
+        <v>20.04029655456543</v>
       </c>
       <c r="BG189" s="3">
-        <v>20.04029655456543</v>
-      </c>
-      <c r="BH189" s="3">
         <v>55.331153869628913</v>
       </c>
     </row>
-    <row r="190" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A190" s="2">
         <v>45562</v>
       </c>
@@ -35187,28 +34620,25 @@
         <v>12.24008083343506</v>
       </c>
       <c r="BB190" s="3">
-        <v>-5.2909083366394043</v>
+        <v>6.2399997711181641</v>
       </c>
       <c r="BC190" s="3">
-        <v>6.2399997711181641</v>
+        <v>61.012897491455078</v>
       </c>
       <c r="BD190" s="3">
-        <v>61.012897491455078</v>
+        <v>22.248079299926761</v>
       </c>
       <c r="BE190" s="3">
-        <v>22.248079299926761</v>
+        <v>26.303163528442379</v>
       </c>
       <c r="BF190" s="3">
-        <v>26.303163528442379</v>
+        <v>20.875688552856449</v>
       </c>
       <c r="BG190" s="3">
-        <v>20.875688552856449</v>
-      </c>
-      <c r="BH190" s="3">
         <v>55.311408996582031</v>
       </c>
     </row>
-    <row r="191" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A191" s="2">
         <v>45565</v>
       </c>
@@ -35369,28 +34799,25 @@
         <v>12.26969528198242</v>
       </c>
       <c r="BB191" s="3">
-        <v>-5.2965645790100098</v>
+        <v>6.2399997711181641</v>
       </c>
       <c r="BC191" s="3">
-        <v>6.2399997711181641</v>
+        <v>60.583625793457031</v>
       </c>
       <c r="BD191" s="3">
-        <v>60.583625793457031</v>
+        <v>22.040853500366211</v>
       </c>
       <c r="BE191" s="3">
-        <v>22.040853500366211</v>
+        <v>26.40723991394043</v>
       </c>
       <c r="BF191" s="3">
-        <v>26.40723991394043</v>
+        <v>20.612360000610352</v>
       </c>
       <c r="BG191" s="3">
-        <v>20.612360000610352</v>
-      </c>
-      <c r="BH191" s="3">
         <v>53.759666442871087</v>
       </c>
     </row>
-    <row r="192" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A192" s="2">
         <v>45566</v>
       </c>
@@ -35551,28 +34978,25 @@
         <v>12.763246536254879</v>
       </c>
       <c r="BB192" s="3">
-        <v>-5.2598023414611816</v>
+        <v>6.2399997711181641</v>
       </c>
       <c r="BC192" s="3">
-        <v>6.2399997711181641</v>
+        <v>60.879344940185547</v>
       </c>
       <c r="BD192" s="3">
-        <v>60.879344940185547</v>
+        <v>21.927825927734379</v>
       </c>
       <c r="BE192" s="3">
-        <v>21.927825927734379</v>
+        <v>26.288967132568359</v>
       </c>
       <c r="BF192" s="3">
-        <v>26.288967132568359</v>
+        <v>20.45799446105957</v>
       </c>
       <c r="BG192" s="3">
-        <v>20.45799446105957</v>
-      </c>
-      <c r="BH192" s="3">
         <v>55.232398986816413</v>
       </c>
     </row>
-    <row r="193" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A193" s="2">
         <v>45567</v>
       </c>
@@ -35733,28 +35157,25 @@
         <v>13.58254241943359</v>
       </c>
       <c r="BB193" s="3">
-        <v>-5.302220344543457</v>
+        <v>6.309999942779541</v>
       </c>
       <c r="BC193" s="3">
-        <v>6.309999942779541</v>
+        <v>61.213218688964837</v>
       </c>
       <c r="BD193" s="3">
-        <v>61.213218688964837</v>
+        <v>22.031435012817379</v>
       </c>
       <c r="BE193" s="3">
-        <v>22.031435012817379</v>
+        <v>26.534971237182621</v>
       </c>
       <c r="BF193" s="3">
-        <v>26.534971237182621</v>
+        <v>21.665678024291989</v>
       </c>
       <c r="BG193" s="3">
-        <v>21.665678024291989</v>
-      </c>
-      <c r="BH193" s="3">
         <v>54.708538055419922</v>
       </c>
     </row>
-    <row r="194" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A194" s="2">
         <v>45568</v>
       </c>
@@ -35915,28 +35336,25 @@
         <v>13.27653980255127</v>
       </c>
       <c r="BB194" s="3">
-        <v>-5.109926700592041</v>
+        <v>6.1100001335144043</v>
       </c>
       <c r="BC194" s="3">
-        <v>6.1100001335144043</v>
+        <v>60.039894104003913</v>
       </c>
       <c r="BD194" s="3">
-        <v>60.039894104003913</v>
+        <v>21.61699295043945</v>
       </c>
       <c r="BE194" s="3">
-        <v>21.61699295043945</v>
+        <v>25.872661590576168</v>
       </c>
       <c r="BF194" s="3">
-        <v>25.872661590576168</v>
+        <v>21.002811431884769</v>
       </c>
       <c r="BG194" s="3">
-        <v>21.002811431884769</v>
-      </c>
-      <c r="BH194" s="3">
         <v>53.967231750488281</v>
       </c>
     </row>
-    <row r="195" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A195" s="2">
         <v>45569</v>
       </c>
@@ -36097,28 +35515,25 @@
         <v>13.167959213256839</v>
       </c>
       <c r="BB195" s="3">
-        <v>-5.019434928894043</v>
+        <v>6.2100000381469727</v>
       </c>
       <c r="BC195" s="3">
-        <v>6.2100000381469727</v>
+        <v>59.601089477539063</v>
       </c>
       <c r="BD195" s="3">
-        <v>59.601089477539063</v>
+        <v>21.748861312866211</v>
       </c>
       <c r="BE195" s="3">
-        <v>21.748861312866211</v>
+        <v>25.839546203613281</v>
       </c>
       <c r="BF195" s="3">
-        <v>25.839546203613281</v>
+        <v>21.057296752929691</v>
       </c>
       <c r="BG195" s="3">
-        <v>21.057296752929691</v>
-      </c>
-      <c r="BH195" s="3">
         <v>53.868389129638672</v>
       </c>
     </row>
-    <row r="196" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A196" s="2">
         <v>45572</v>
       </c>
@@ -36279,28 +35694,25 @@
         <v>13.513443946838381</v>
       </c>
       <c r="BB196" s="3">
-        <v>-4.9459114074707031</v>
+        <v>6.2800002098083496</v>
       </c>
       <c r="BC196" s="3">
-        <v>6.2800002098083496</v>
+        <v>60.125743865966797</v>
       </c>
       <c r="BD196" s="3">
-        <v>60.125743865966797</v>
+        <v>21.84305381774902</v>
       </c>
       <c r="BE196" s="3">
-        <v>21.84305381774902</v>
+        <v>25.47054481506348</v>
       </c>
       <c r="BF196" s="3">
-        <v>25.47054481506348</v>
+        <v>20.585115432739261</v>
       </c>
       <c r="BG196" s="3">
-        <v>20.585115432739261</v>
-      </c>
-      <c r="BH196" s="3">
         <v>52.781139373779297</v>
       </c>
     </row>
-    <row r="197" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A197" s="2">
         <v>45573</v>
       </c>
@@ -36461,28 +35873,25 @@
         <v>13.67138195037842</v>
       </c>
       <c r="BB197" s="3">
-        <v>-4.9543943405151367</v>
+        <v>6.0199999809265137</v>
       </c>
       <c r="BC197" s="3">
-        <v>6.0199999809265137</v>
+        <v>58.303752899169922</v>
       </c>
       <c r="BD197" s="3">
-        <v>58.303752899169922</v>
+        <v>21.927825927734379</v>
       </c>
       <c r="BE197" s="3">
-        <v>21.927825927734379</v>
+        <v>25.60774040222168</v>
       </c>
       <c r="BF197" s="3">
-        <v>25.60774040222168</v>
+        <v>20.11293983459473</v>
       </c>
       <c r="BG197" s="3">
-        <v>20.11293983459473</v>
-      </c>
-      <c r="BH197" s="3">
         <v>53.680591583251953</v>
       </c>
     </row>
-    <row r="198" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A198" s="2">
         <v>45574</v>
       </c>
@@ -36643,28 +36052,25 @@
         <v>13.48383140563965</v>
       </c>
       <c r="BB198" s="3">
-        <v>-4.892181396484375</v>
+        <v>6.2899999618530273</v>
       </c>
       <c r="BC198" s="3">
-        <v>6.2899999618530273</v>
+        <v>58.151126861572273</v>
       </c>
       <c r="BD198" s="3">
-        <v>58.151126861572273</v>
+        <v>21.522800445556641</v>
       </c>
       <c r="BE198" s="3">
-        <v>21.522800445556641</v>
+        <v>25.494197845458981</v>
       </c>
       <c r="BF198" s="3">
-        <v>25.494197845458981</v>
+        <v>20.51247406005859</v>
       </c>
       <c r="BG198" s="3">
-        <v>20.51247406005859</v>
-      </c>
-      <c r="BH198" s="3">
         <v>53.374183654785163</v>
       </c>
     </row>
-    <row r="199" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A199" s="2">
         <v>45575</v>
       </c>
@@ -36825,28 +36231,25 @@
         <v>13.286411285400391</v>
       </c>
       <c r="BB199" s="3">
-        <v>-4.8639035224914551</v>
+        <v>6.2300000190734863</v>
       </c>
       <c r="BC199" s="3">
-        <v>6.2300000190734863</v>
+        <v>58.427764892578118</v>
       </c>
       <c r="BD199" s="3">
-        <v>58.427764892578118</v>
+        <v>21.438028335571289</v>
       </c>
       <c r="BE199" s="3">
-        <v>21.438028335571289</v>
+        <v>25.45162391662598</v>
       </c>
       <c r="BF199" s="3">
-        <v>25.45162391662598</v>
+        <v>20.294546127319339</v>
       </c>
       <c r="BG199" s="3">
-        <v>20.294546127319339</v>
-      </c>
-      <c r="BH199" s="3">
         <v>53.552097320556641</v>
       </c>
     </row>
-    <row r="200" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A200" s="2">
         <v>45576</v>
       </c>
@@ -37007,28 +36410,25 @@
         <v>13.23705577850342</v>
       </c>
       <c r="BB200" s="3">
-        <v>-4.8016901016235352</v>
+        <v>6.25</v>
       </c>
       <c r="BC200" s="3">
-        <v>6.25</v>
+        <v>59.267219543457031</v>
       </c>
       <c r="BD200" s="3">
-        <v>59.267219543457031</v>
+        <v>21.54163932800293</v>
       </c>
       <c r="BE200" s="3">
-        <v>21.54163932800293</v>
+        <v>24.917043685913089</v>
       </c>
       <c r="BF200" s="3">
-        <v>24.917043685913089</v>
+        <v>19.332033157348629</v>
       </c>
       <c r="BG200" s="3">
-        <v>19.332033157348629</v>
-      </c>
-      <c r="BH200" s="3">
         <v>53.542213439941413</v>
       </c>
     </row>
-    <row r="201" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A201" s="2">
         <v>45579</v>
       </c>
@@ -37189,28 +36589,25 @@
         <v>13.404863357543951</v>
       </c>
       <c r="BB201" s="3">
-        <v>-4.7790675163269043</v>
+        <v>6.2699999809265137</v>
       </c>
       <c r="BC201" s="3">
-        <v>6.2699999809265137</v>
+        <v>59.076431274414063</v>
       </c>
       <c r="BD201" s="3">
-        <v>59.076431274414063</v>
+        <v>21.56989669799805</v>
       </c>
       <c r="BE201" s="3">
-        <v>21.56989669799805</v>
+        <v>25.163045883178711</v>
       </c>
       <c r="BF201" s="3">
-        <v>25.163045883178711</v>
+        <v>18.705490112304691</v>
       </c>
       <c r="BG201" s="3">
-        <v>18.705490112304691</v>
-      </c>
-      <c r="BH201" s="3">
         <v>54.402137756347663</v>
       </c>
     </row>
-    <row r="202" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A202" s="2">
         <v>45580</v>
       </c>
@@ -37371,28 +36768,25 @@
         <v>13.48383140563965</v>
       </c>
       <c r="BB202" s="3">
-        <v>-4.8865261077880859</v>
+        <v>6.119999885559082</v>
       </c>
       <c r="BC202" s="3">
-        <v>6.119999885559082</v>
+        <v>58.351448059082031</v>
       </c>
       <c r="BD202" s="3">
-        <v>58.351448059082031</v>
+        <v>21.91840744018555</v>
       </c>
       <c r="BE202" s="3">
-        <v>21.91840744018555</v>
+        <v>25.144123077392582</v>
       </c>
       <c r="BF202" s="3">
-        <v>25.144123077392582</v>
+        <v>18.896175384521481</v>
       </c>
       <c r="BG202" s="3">
-        <v>18.896175384521481</v>
-      </c>
-      <c r="BH202" s="3">
         <v>55.874866485595703</v>
       </c>
     </row>
-    <row r="203" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A203" s="2">
         <v>45581</v>
       </c>
@@ -37553,28 +36947,25 @@
         <v>13.730607032775881</v>
       </c>
       <c r="BB203" s="3">
-        <v>-4.9911561012268066</v>
+        <v>6.1700000762939453</v>
       </c>
       <c r="BC203" s="3">
-        <v>6.1700000762939453</v>
+        <v>59.467540740966797</v>
       </c>
       <c r="BD203" s="3">
-        <v>59.467540740966797</v>
+        <v>21.758279800415039</v>
       </c>
       <c r="BE203" s="3">
-        <v>21.758279800415039</v>
+        <v>25.688161849975589</v>
       </c>
       <c r="BF203" s="3">
-        <v>25.688161849975589</v>
+        <v>20.948331832885739</v>
       </c>
       <c r="BG203" s="3">
-        <v>20.948331832885739</v>
-      </c>
-      <c r="BH203" s="3">
         <v>56.527217864990227</v>
       </c>
     </row>
-    <row r="204" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A204" s="2">
         <v>45582</v>
       </c>
@@ -37735,28 +37126,25 @@
         <v>13.720736503601071</v>
       </c>
       <c r="BB204" s="3">
-        <v>-4.9628782272338867</v>
+        <v>6.070000171661377</v>
       </c>
       <c r="BC204" s="3">
-        <v>6.070000171661377</v>
+        <v>57.960342407226563</v>
       </c>
       <c r="BD204" s="3">
-        <v>57.960342407226563</v>
+        <v>21.32499885559082</v>
       </c>
       <c r="BE204" s="3">
-        <v>21.32499885559082</v>
+        <v>25.782777786254879</v>
       </c>
       <c r="BF204" s="3">
-        <v>25.782777786254879</v>
+        <v>20.648679733276371</v>
       </c>
       <c r="BG204" s="3">
-        <v>20.648679733276371</v>
-      </c>
-      <c r="BH204" s="3">
         <v>55.568458557128913</v>
       </c>
     </row>
-    <row r="205" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A205" s="2">
         <v>45583</v>
       </c>
@@ -37917,28 +37305,25 @@
         <v>13.967512130737299</v>
       </c>
       <c r="BB205" s="3">
-        <v>-4.9883284568786621</v>
+        <v>6.119999885559082</v>
       </c>
       <c r="BC205" s="3">
-        <v>6.119999885559082</v>
+        <v>57.760021209716797</v>
       </c>
       <c r="BD205" s="3">
-        <v>57.760021209716797</v>
+        <v>21.2967414855957</v>
       </c>
       <c r="BE205" s="3">
-        <v>21.2967414855957</v>
+        <v>25.9294319152832</v>
       </c>
       <c r="BF205" s="3">
-        <v>25.9294319152832</v>
+        <v>20.594196319580082</v>
       </c>
       <c r="BG205" s="3">
-        <v>20.594196319580082</v>
-      </c>
-      <c r="BH205" s="3">
         <v>54.580047607421882</v>
       </c>
     </row>
-    <row r="206" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A206" s="2">
         <v>45586</v>
       </c>
@@ -38099,28 +37484,25 @@
         <v>14.26364326477051</v>
       </c>
       <c r="BB206" s="3">
-        <v>-4.9232878684997559</v>
+        <v>6.2699999809265137</v>
       </c>
       <c r="BC206" s="3">
-        <v>6.2699999809265137</v>
+        <v>57.550159454345703</v>
       </c>
       <c r="BD206" s="3">
-        <v>57.550159454345703</v>
+        <v>21.372097015380859</v>
       </c>
       <c r="BE206" s="3">
-        <v>21.372097015380859</v>
+        <v>25.759120941162109</v>
       </c>
       <c r="BF206" s="3">
-        <v>25.759120941162109</v>
+        <v>20.530637741088871</v>
       </c>
       <c r="BG206" s="3">
-        <v>20.530637741088871</v>
-      </c>
-      <c r="BH206" s="3">
         <v>54.402137756347663</v>
       </c>
     </row>
-    <row r="207" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A207" s="2">
         <v>45587</v>
       </c>
@@ -38281,28 +37663,25 @@
         <v>14.076093673706049</v>
       </c>
       <c r="BB207" s="3">
-        <v>-4.8667311668395996</v>
+        <v>6.1500000953674316</v>
       </c>
       <c r="BC207" s="3">
-        <v>6.1500000953674316</v>
+        <v>57.626468658447273</v>
       </c>
       <c r="BD207" s="3">
-        <v>57.626468658447273</v>
+        <v>20.938812255859379</v>
       </c>
       <c r="BE207" s="3">
-        <v>20.938812255859379</v>
+        <v>25.361736297607418</v>
       </c>
       <c r="BF207" s="3">
-        <v>25.361736297607418</v>
+        <v>20.566957473754879</v>
       </c>
       <c r="BG207" s="3">
-        <v>20.566957473754879</v>
-      </c>
-      <c r="BH207" s="3">
         <v>55.301589965820313</v>
       </c>
     </row>
-    <row r="208" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A208" s="2">
         <v>45588</v>
       </c>
@@ -38463,28 +37842,25 @@
         <v>14.14519119262695</v>
       </c>
       <c r="BB208" s="3">
-        <v>-4.8723874092102051</v>
+        <v>6.2699999809265137</v>
       </c>
       <c r="BC208" s="3">
-        <v>6.2699999809265137</v>
+        <v>56.615310668945313</v>
       </c>
       <c r="BD208" s="3">
-        <v>56.615310668945313</v>
+        <v>20.901138305664059</v>
       </c>
       <c r="BE208" s="3">
-        <v>20.901138305664059</v>
+        <v>25.390121459960941</v>
       </c>
       <c r="BF208" s="3">
-        <v>25.390121459960941</v>
+        <v>21.075454711914059</v>
       </c>
       <c r="BG208" s="3">
-        <v>21.075454711914059</v>
-      </c>
-      <c r="BH208" s="3">
         <v>55.548694610595703</v>
       </c>
     </row>
-    <row r="209" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A209" s="2">
         <v>45589</v>
       </c>
@@ -38645,28 +38021,25 @@
         <v>14.31299877166748</v>
       </c>
       <c r="BB209" s="3">
-        <v>-4.8808708190917969</v>
+        <v>6.369999885559082</v>
       </c>
       <c r="BC209" s="3">
-        <v>6.369999885559082</v>
+        <v>56.949184417724609</v>
       </c>
       <c r="BD209" s="3">
-        <v>56.949184417724609</v>
+        <v>20.882297515869141</v>
       </c>
       <c r="BE209" s="3">
-        <v>20.882297515869141</v>
+        <v>25.43742752075195</v>
       </c>
       <c r="BF209" s="3">
-        <v>25.43742752075195</v>
+        <v>21.11177825927734</v>
       </c>
       <c r="BG209" s="3">
-        <v>21.11177825927734</v>
-      </c>
-      <c r="BH209" s="3">
         <v>55.617877960205078</v>
       </c>
     </row>
-    <row r="210" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A210" s="2">
         <v>45590</v>
       </c>
@@ -38827,28 +38200,25 @@
         <v>14.32286930084229</v>
       </c>
       <c r="BB210" s="3">
-        <v>-4.7932076454162598</v>
+        <v>6.6399998664855957</v>
       </c>
       <c r="BC210" s="3">
-        <v>6.6399998664855957</v>
+        <v>58.885646820068359</v>
       </c>
       <c r="BD210" s="3">
-        <v>58.885646820068359</v>
+        <v>20.637399673461911</v>
       </c>
       <c r="BE210" s="3">
-        <v>20.637399673461911</v>
+        <v>25.276584625244141</v>
       </c>
       <c r="BF210" s="3">
-        <v>25.276584625244141</v>
+        <v>20.766725540161129</v>
       </c>
       <c r="BG210" s="3">
-        <v>20.766725540161129</v>
-      </c>
-      <c r="BH210" s="3">
         <v>54.8271484375</v>
       </c>
     </row>
-    <row r="211" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A211" s="2">
         <v>45593</v>
       </c>
@@ -39009,28 +38379,25 @@
         <v>14.28338527679443</v>
       </c>
       <c r="BB211" s="3">
-        <v>-4.8610758781433114</v>
+        <v>6.630000114440918</v>
       </c>
       <c r="BC211" s="3">
-        <v>6.630000114440918</v>
+        <v>59.982658386230469</v>
       </c>
       <c r="BD211" s="3">
-        <v>59.982658386230469</v>
+        <v>21.033004760742191</v>
       </c>
       <c r="BE211" s="3">
-        <v>21.033004760742191</v>
+        <v>25.480009078979489</v>
       </c>
       <c r="BF211" s="3">
-        <v>25.480009078979489</v>
+        <v>21.075454711914059</v>
       </c>
       <c r="BG211" s="3">
-        <v>21.075454711914059</v>
-      </c>
-      <c r="BH211" s="3">
         <v>55.607990264892578</v>
       </c>
     </row>
-    <row r="212" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A212" s="2">
         <v>45594</v>
       </c>
@@ -39191,28 +38558,25 @@
         <v>14.54990291595459</v>
       </c>
       <c r="BB212" s="3">
-        <v>-4.6207079887390137</v>
+        <v>6.429999828338623</v>
       </c>
       <c r="BC212" s="3">
-        <v>6.429999828338623</v>
+        <v>59.772796630859382</v>
       </c>
       <c r="BD212" s="3">
-        <v>59.772796630859382</v>
+        <v>20.910554885864261</v>
       </c>
       <c r="BE212" s="3">
-        <v>20.910554885864261</v>
+        <v>24.557502746582031</v>
       </c>
       <c r="BF212" s="3">
-        <v>24.557502746582031</v>
+        <v>20.721323013305661</v>
       </c>
       <c r="BG212" s="3">
-        <v>20.721323013305661</v>
-      </c>
-      <c r="BH212" s="3">
         <v>56.280113220214837</v>
       </c>
     </row>
-    <row r="213" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A213" s="2">
         <v>45595</v>
       </c>
@@ -39373,28 +38737,25 @@
         <v>14.86577701568604</v>
       </c>
       <c r="BB213" s="3">
-        <v>-4.7027153968811044</v>
+        <v>6.570000171661377</v>
       </c>
       <c r="BC213" s="3">
-        <v>6.570000171661377</v>
+        <v>59.591552734375</v>
       </c>
       <c r="BD213" s="3">
-        <v>59.591552734375</v>
+        <v>21.014163970947269</v>
       </c>
       <c r="BE213" s="3">
-        <v>21.014163970947269</v>
+        <v>24.921773910522461</v>
       </c>
       <c r="BF213" s="3">
-        <v>24.921773910522461</v>
+        <v>21.465909957885739</v>
       </c>
       <c r="BG213" s="3">
-        <v>21.465909957885739</v>
-      </c>
-      <c r="BH213" s="3">
         <v>53.374183654785163</v>
       </c>
     </row>
-    <row r="214" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A214" s="2">
         <v>45596</v>
       </c>
@@ -39555,28 +38916,25 @@
         <v>14.816421508789061</v>
       </c>
       <c r="BB214" s="3">
-        <v>-4.6885766983032227</v>
+        <v>6.6100001335144043</v>
       </c>
       <c r="BC214" s="3">
-        <v>6.6100001335144043</v>
+        <v>59.200443267822273</v>
       </c>
       <c r="BD214" s="3">
-        <v>59.200443267822273</v>
+        <v>21.014163970947269</v>
       </c>
       <c r="BE214" s="3">
-        <v>21.014163970947269</v>
+        <v>24.902847290039059</v>
       </c>
       <c r="BF214" s="3">
-        <v>24.902847290039059</v>
+        <v>21.765560150146481</v>
       </c>
       <c r="BG214" s="3">
-        <v>21.765560150146481</v>
-      </c>
-      <c r="BH214" s="3">
         <v>53.482913970947273</v>
       </c>
     </row>
-    <row r="215" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A215" s="2">
         <v>45597</v>
       </c>
@@ -39737,28 +39095,25 @@
         <v>14.678226470947269</v>
       </c>
       <c r="BB215" s="3">
-        <v>-4.6716094017028809</v>
+        <v>6.320000171661377</v>
       </c>
       <c r="BC215" s="3">
-        <v>6.320000171661377</v>
+        <v>59.171825408935547</v>
       </c>
       <c r="BD215" s="3">
-        <v>59.171825408935547</v>
+        <v>20.835201263427731</v>
       </c>
       <c r="BE215" s="3">
-        <v>20.835201263427731</v>
+        <v>24.784580230712891</v>
       </c>
       <c r="BF215" s="3">
-        <v>24.784580230712891</v>
+        <v>21.175336837768551</v>
       </c>
       <c r="BG215" s="3">
-        <v>21.175336837768551</v>
-      </c>
-      <c r="BH215" s="3">
         <v>54.066078186035163</v>
       </c>
     </row>
-    <row r="216" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A216" s="2">
         <v>45600</v>
       </c>
@@ -39919,28 +39274,25 @@
         <v>15.408682823181151</v>
       </c>
       <c r="BB216" s="3">
-        <v>-4.7479615211486816</v>
+        <v>6.559999942779541</v>
       </c>
       <c r="BC216" s="3">
-        <v>6.559999942779541</v>
+        <v>59.782333374023438</v>
       </c>
       <c r="BD216" s="3">
-        <v>59.782333374023438</v>
+        <v>21.306159973144531</v>
       </c>
       <c r="BE216" s="3">
-        <v>21.306159973144531</v>
+        <v>25.257659912109379</v>
       </c>
       <c r="BF216" s="3">
-        <v>25.257659912109379</v>
+        <v>22.065212249755859</v>
       </c>
       <c r="BG216" s="3">
-        <v>22.065212249755859</v>
-      </c>
-      <c r="BH216" s="3">
         <v>55.538803100585938</v>
       </c>
     </row>
-    <row r="217" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A217" s="2">
         <v>45601</v>
       </c>
@@ -40101,28 +39453,25 @@
         <v>15.398812294006349</v>
       </c>
       <c r="BB217" s="3">
-        <v>-4.5613226890563956</v>
+        <v>6.6599998474121094</v>
       </c>
       <c r="BC217" s="3">
-        <v>6.6599998474121094</v>
+        <v>59.257678985595703</v>
       </c>
       <c r="BD217" s="3">
-        <v>59.257678985595703</v>
+        <v>21.485122680664059</v>
       </c>
       <c r="BE217" s="3">
-        <v>21.485122680664059</v>
+        <v>25.08261871337891</v>
       </c>
       <c r="BF217" s="3">
-        <v>25.08261871337891</v>
+        <v>23.472663879394531</v>
       </c>
       <c r="BG217" s="3">
-        <v>23.472663879394531</v>
-      </c>
-      <c r="BH217" s="3">
         <v>55.360893249511719</v>
       </c>
     </row>
-    <row r="218" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A218" s="2">
         <v>45602</v>
       </c>
@@ -40283,28 +39632,25 @@
         <v>15.63571739196777</v>
       </c>
       <c r="BB218" s="3">
-        <v>-4.5584959983825684</v>
+        <v>6.619999885559082</v>
       </c>
       <c r="BC218" s="3">
-        <v>6.619999885559082</v>
+        <v>58.589927673339837</v>
       </c>
       <c r="BD218" s="3">
-        <v>58.589927673339837</v>
+        <v>21.937246322631839</v>
       </c>
       <c r="BE218" s="3">
-        <v>21.937246322631839</v>
+        <v>25.030584335327148</v>
       </c>
       <c r="BF218" s="3">
-        <v>25.030584335327148</v>
+        <v>23.990242004394531</v>
       </c>
       <c r="BG218" s="3">
-        <v>23.990242004394531</v>
-      </c>
-      <c r="BH218" s="3">
         <v>55.439964294433587</v>
       </c>
     </row>
-    <row r="219" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A219" s="2">
         <v>45603</v>
       </c>
@@ -40465,28 +39811,25 @@
         <v>16.277334213256839</v>
       </c>
       <c r="BB219" s="3">
-        <v>-4.5471839904785156</v>
+        <v>6.6500000953674316</v>
       </c>
       <c r="BC219" s="3">
-        <v>6.6500000953674316</v>
+        <v>60.631324768066413</v>
       </c>
       <c r="BD219" s="3">
-        <v>60.631324768066413</v>
+        <v>21.108358383178711</v>
       </c>
       <c r="BE219" s="3">
-        <v>21.108358383178711</v>
+        <v>25.234004974365231</v>
       </c>
       <c r="BF219" s="3">
-        <v>25.234004974365231</v>
+        <v>21.720159530639648</v>
       </c>
       <c r="BG219" s="3">
-        <v>21.720159530639648</v>
-      </c>
-      <c r="BH219" s="3">
         <v>55.123672485351563</v>
       </c>
     </row>
-    <row r="220" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A220" s="2">
         <v>45604</v>
       </c>
@@ -40647,28 +39990,25 @@
         <v>16.099655151367191</v>
       </c>
       <c r="BB220" s="3">
-        <v>-4.4991106986999512</v>
+        <v>6.25</v>
       </c>
       <c r="BC220" s="3">
-        <v>6.25</v>
+        <v>57.836334228515618</v>
       </c>
       <c r="BD220" s="3">
-        <v>57.836334228515618</v>
+        <v>21.14603424072266</v>
       </c>
       <c r="BE220" s="3">
-        <v>21.14603424072266</v>
+        <v>24.600078582763668</v>
       </c>
       <c r="BF220" s="3">
-        <v>24.600078582763668</v>
+        <v>23.530946731567379</v>
       </c>
       <c r="BG220" s="3">
-        <v>23.530946731567379</v>
-      </c>
-      <c r="BH220" s="3">
         <v>54.451549530029297</v>
       </c>
     </row>
-    <row r="221" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A221" s="2">
         <v>45607</v>
       </c>
@@ -40829,28 +40169,25 @@
         <v>17.382890701293949</v>
       </c>
       <c r="BB221" s="3">
-        <v>-4.6970605850219727</v>
+        <v>6.0900001525878906</v>
       </c>
       <c r="BC221" s="3">
-        <v>6.0900001525878906</v>
+        <v>55.947566986083977</v>
       </c>
       <c r="BD221" s="3">
-        <v>55.947566986083977</v>
+        <v>21.230808258056641</v>
       </c>
       <c r="BE221" s="3">
-        <v>21.230808258056641</v>
+        <v>25.073160171508789</v>
       </c>
       <c r="BF221" s="3">
-        <v>25.073160171508789</v>
+        <v>24.16240119934082</v>
       </c>
       <c r="BG221" s="3">
-        <v>24.16240119934082</v>
-      </c>
-      <c r="BH221" s="3">
         <v>54.846920013427727</v>
       </c>
     </row>
-    <row r="222" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A222" s="2">
         <v>45608</v>
       </c>
@@ -41011,28 +40348,25 @@
         <v>17.136114120483398</v>
       </c>
       <c r="BB222" s="3">
-        <v>-4.6772656440734863</v>
+        <v>6</v>
       </c>
       <c r="BC222" s="3">
-        <v>6</v>
+        <v>54.678848266601563</v>
       </c>
       <c r="BD222" s="3">
-        <v>54.678848266601563</v>
+        <v>21.127195358276371</v>
       </c>
       <c r="BE222" s="3">
-        <v>21.127195358276371</v>
+        <v>24.718349456787109</v>
       </c>
       <c r="BF222" s="3">
-        <v>24.718349456787109</v>
+        <v>22.908779144287109</v>
       </c>
       <c r="BG222" s="3">
-        <v>22.908779144287109</v>
-      </c>
-      <c r="BH222" s="3">
         <v>54.777729034423828</v>
       </c>
     </row>
-    <row r="223" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A223" s="2">
         <v>45609</v>
       </c>
@@ -41193,28 +40527,25 @@
         <v>16.761014938354489</v>
       </c>
       <c r="BB223" s="3">
-        <v>-4.6291918754577637</v>
+        <v>6.0900001525878906</v>
       </c>
       <c r="BC223" s="3">
-        <v>6.0900001525878906</v>
+        <v>54.526218414306641</v>
       </c>
       <c r="BD223" s="3">
-        <v>54.526218414306641</v>
+        <v>21.02358436584473</v>
       </c>
       <c r="BE223" s="3">
-        <v>21.02358436584473</v>
+        <v>24.62846755981445</v>
       </c>
       <c r="BF223" s="3">
-        <v>24.62846755981445</v>
+        <v>23.261650085449219</v>
       </c>
       <c r="BG223" s="3">
-        <v>23.261650085449219</v>
-      </c>
-      <c r="BH223" s="3">
         <v>54.066078186035163</v>
       </c>
     </row>
-    <row r="224" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A224" s="2">
         <v>45610</v>
       </c>
@@ -41375,28 +40706,25 @@
         <v>16.060171127319339</v>
       </c>
       <c r="BB224" s="3">
-        <v>-4.6602978706359863</v>
+        <v>6.0999999046325684</v>
       </c>
       <c r="BC224" s="3">
-        <v>6.0999999046325684</v>
+        <v>54.220962524414063</v>
       </c>
       <c r="BD224" s="3">
-        <v>54.220962524414063</v>
+        <v>20.919973373413089</v>
       </c>
       <c r="BE224" s="3">
-        <v>20.919973373413089</v>
+        <v>24.410844802856449</v>
       </c>
       <c r="BF224" s="3">
-        <v>24.410844802856449</v>
+        <v>22.760202407836911</v>
       </c>
       <c r="BG224" s="3">
-        <v>22.760202407836911</v>
-      </c>
-      <c r="BH224" s="3">
         <v>53.720127105712891</v>
       </c>
     </row>
-    <row r="225" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A225" s="2">
         <v>45614</v>
       </c>
@@ -41557,28 +40885,25 @@
         <v>16.11939811706543</v>
       </c>
       <c r="BB225" s="3">
-        <v>-4.6602978706359863</v>
+        <v>6.1999998092651367</v>
       </c>
       <c r="BC225" s="3">
-        <v>6.1999998092651367</v>
+        <v>54.898250579833977</v>
       </c>
       <c r="BD225" s="3">
-        <v>54.898250579833977</v>
+        <v>20.53378868103027</v>
       </c>
       <c r="BE225" s="3">
-        <v>20.53378868103027</v>
+        <v>24.406118392944339</v>
       </c>
       <c r="BF225" s="3">
-        <v>24.406118392944339</v>
+        <v>23.122358322143551</v>
       </c>
       <c r="BG225" s="3">
-        <v>23.122358322143551</v>
-      </c>
-      <c r="BH225" s="3">
         <v>53.374183654785163</v>
       </c>
     </row>
-    <row r="226" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A226" s="2">
         <v>45615</v>
       </c>
@@ -41739,28 +41064,25 @@
         <v>16.3365592956543</v>
       </c>
       <c r="BB226" s="3">
-        <v>-4.6263642311096191</v>
+        <v>6.2100000381469727</v>
       </c>
       <c r="BC226" s="3">
-        <v>6.2100000381469727</v>
+        <v>55.022258758544922</v>
       </c>
       <c r="BD226" s="3">
-        <v>55.022258758544922</v>
+        <v>20.53378868103027</v>
       </c>
       <c r="BE226" s="3">
-        <v>20.53378868103027</v>
+        <v>24.66158294677734</v>
       </c>
       <c r="BF226" s="3">
-        <v>24.66158294677734</v>
+        <v>22.658054351806641</v>
       </c>
       <c r="BG226" s="3">
-        <v>22.658054351806641</v>
-      </c>
-      <c r="BH226" s="3">
         <v>53.502677917480469</v>
       </c>
     </row>
-    <row r="227" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A227" s="2">
         <v>45617</v>
       </c>
@@ -41921,28 +41243,25 @@
         <v>16.000944137573239</v>
       </c>
       <c r="BB227" s="3">
-        <v>-4.4877996444702148</v>
+        <v>6.0500001907348633</v>
       </c>
       <c r="BC227" s="3">
-        <v>6.0500001907348633</v>
+        <v>54.96502685546875</v>
       </c>
       <c r="BD227" s="3">
-        <v>54.96502685546875</v>
+        <v>20.251213073730469</v>
       </c>
       <c r="BE227" s="3">
-        <v>20.251213073730469</v>
+        <v>23.914117813110352</v>
       </c>
       <c r="BF227" s="3">
-        <v>23.914117813110352</v>
+        <v>22.490903854370121</v>
       </c>
       <c r="BG227" s="3">
-        <v>22.490903854370121</v>
-      </c>
-      <c r="BH227" s="3">
         <v>53.107315063476563</v>
       </c>
     </row>
-    <row r="228" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A228" s="2">
         <v>45618</v>
       </c>
@@ -42103,28 +41422,25 @@
         <v>16.198366165161129</v>
       </c>
       <c r="BB228" s="3">
-        <v>-4.5839462280273438</v>
+        <v>6.179999828338623</v>
       </c>
       <c r="BC228" s="3">
-        <v>6.179999828338623</v>
+        <v>55.499221801757813</v>
       </c>
       <c r="BD228" s="3">
-        <v>55.499221801757813</v>
+        <v>20.562046051025391</v>
       </c>
       <c r="BE228" s="3">
-        <v>20.562046051025391</v>
+        <v>24.12700080871582</v>
       </c>
       <c r="BF228" s="3">
-        <v>24.12700080871582</v>
+        <v>22.983066558837891</v>
       </c>
       <c r="BG228" s="3">
-        <v>22.983066558837891</v>
-      </c>
-      <c r="BH228" s="3">
         <v>53.384067535400391</v>
       </c>
     </row>
-    <row r="229" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A229" s="2">
         <v>45621</v>
       </c>
@@ -42285,28 +41601,25 @@
         <v>16.139139175415039</v>
       </c>
       <c r="BB229" s="3">
-        <v>-4.6122245788574219</v>
+        <v>6.25</v>
       </c>
       <c r="BC229" s="3">
-        <v>6.25</v>
+        <v>55.489681243896477</v>
       </c>
       <c r="BD229" s="3">
-        <v>55.489681243896477</v>
+        <v>20.53378868103027</v>
       </c>
       <c r="BE229" s="3">
-        <v>20.53378868103027</v>
+        <v>24.145925521850589</v>
       </c>
       <c r="BF229" s="3">
-        <v>24.145925521850589</v>
+        <v>22.97377967834473</v>
       </c>
       <c r="BG229" s="3">
-        <v>22.97377967834473</v>
-      </c>
-      <c r="BH229" s="3">
         <v>51.545627593994141</v>
       </c>
     </row>
-    <row r="230" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A230" s="2">
         <v>45622</v>
       </c>
@@ -42467,28 +41780,25 @@
         <v>16.287204742431641</v>
       </c>
       <c r="BB230" s="3">
-        <v>-4.6150522232055664</v>
+        <v>6.2399997711181641</v>
       </c>
       <c r="BC230" s="3">
-        <v>6.2399997711181641</v>
+        <v>54.783779144287109</v>
       </c>
       <c r="BD230" s="3">
-        <v>54.783779144287109</v>
+        <v>20.769266128540039</v>
       </c>
       <c r="BE230" s="3">
-        <v>20.769266128540039</v>
+        <v>24.54331016540527</v>
       </c>
       <c r="BF230" s="3">
-        <v>24.54331016540527</v>
+        <v>23.187360763549801</v>
       </c>
       <c r="BG230" s="3">
-        <v>23.187360763549801</v>
-      </c>
-      <c r="BH230" s="3">
         <v>52.168323516845703</v>
       </c>
     </row>
-    <row r="231" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A231" s="2">
         <v>45623</v>
       </c>
@@ -42649,28 +41959,25 @@
         <v>15.38894081115723</v>
       </c>
       <c r="BB231" s="3">
-        <v>-4.5782904624938956</v>
+        <v>6.3600001335144043</v>
       </c>
       <c r="BC231" s="3">
-        <v>6.3600001335144043</v>
+        <v>55.451526641845703</v>
       </c>
       <c r="BD231" s="3">
-        <v>55.451526641845703</v>
+        <v>20.166440963745121</v>
       </c>
       <c r="BE231" s="3">
-        <v>20.166440963745121</v>
+        <v>24.06550407409668</v>
       </c>
       <c r="BF231" s="3">
-        <v>24.06550407409668</v>
+        <v>22.992353439331051</v>
       </c>
       <c r="BG231" s="3">
-        <v>22.992353439331051</v>
-      </c>
-      <c r="BH231" s="3">
         <v>51.506092071533203</v>
       </c>
     </row>
-    <row r="232" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A232" s="2">
         <v>45624</v>
       </c>
@@ -42831,28 +42138,25 @@
         <v>13.760220527648929</v>
       </c>
       <c r="BB232" s="3">
-        <v>-4.3973078727722168</v>
+        <v>6.059999942779541</v>
       </c>
       <c r="BC232" s="3">
-        <v>6.059999942779541</v>
+        <v>54.879169464111328</v>
       </c>
       <c r="BD232" s="3">
-        <v>54.879169464111328</v>
+        <v>19.17742919921875</v>
       </c>
       <c r="BE232" s="3">
-        <v>19.17742919921875</v>
+        <v>23.341691970825199</v>
       </c>
       <c r="BF232" s="3">
-        <v>23.341691970825199</v>
+        <v>22.22160720825195</v>
       </c>
       <c r="BG232" s="3">
-        <v>22.22160720825195</v>
-      </c>
-      <c r="BH232" s="3">
         <v>52.296817779541023</v>
       </c>
     </row>
-    <row r="233" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A233" s="2">
         <v>45625</v>
       </c>
@@ -43013,28 +42317,25 @@
         <v>13.829318046569821</v>
       </c>
       <c r="BB233" s="3">
-        <v>-4.4793157577514648</v>
+        <v>6.1399998664855957</v>
       </c>
       <c r="BC233" s="3">
-        <v>6.1399998664855957</v>
+        <v>56.071575164794922</v>
       </c>
       <c r="BD233" s="3">
-        <v>56.071575164794922</v>
+        <v>19.431745529174801</v>
       </c>
       <c r="BE233" s="3">
-        <v>19.431745529174801</v>
+        <v>23.426849365234379</v>
       </c>
       <c r="BF233" s="3">
-        <v>23.426849365234379</v>
+        <v>22.806631088256839</v>
       </c>
       <c r="BG233" s="3">
-        <v>22.806631088256839</v>
-      </c>
-      <c r="BH233" s="3">
         <v>53.31488037109375</v>
       </c>
     </row>
-    <row r="234" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A234" s="2">
         <v>45628</v>
       </c>
@@ -43195,28 +42496,25 @@
         <v>13.355507850646971</v>
       </c>
       <c r="BB234" s="3">
-        <v>-4.4199309349060059</v>
+        <v>6.1700000762939453</v>
       </c>
       <c r="BC234" s="3">
-        <v>6.1700000762939453</v>
+        <v>56.205123901367188</v>
       </c>
       <c r="BD234" s="3">
-        <v>56.205123901367188</v>
+        <v>19.2716178894043</v>
       </c>
       <c r="BE234" s="3">
-        <v>19.2716178894043</v>
+        <v>23.441036224365231</v>
       </c>
       <c r="BF234" s="3">
-        <v>23.441036224365231</v>
+        <v>22.379470825195309</v>
       </c>
       <c r="BG234" s="3">
-        <v>22.379470825195309</v>
-      </c>
-      <c r="BH234" s="3">
         <v>53.225921630859382</v>
       </c>
     </row>
-    <row r="235" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A235" s="2">
         <v>45629</v>
       </c>
@@ -43377,28 +42675,25 @@
         <v>13.15808773040771</v>
       </c>
       <c r="BB235" s="3">
-        <v>-4.4962825775146484</v>
+        <v>6.0799999237060547</v>
       </c>
       <c r="BC235" s="3">
-        <v>6.0799999237060547</v>
+        <v>55.775859832763672</v>
       </c>
       <c r="BD235" s="3">
-        <v>55.775859832763672</v>
+        <v>19.215105056762699</v>
       </c>
       <c r="BE235" s="3">
-        <v>19.215105056762699</v>
+        <v>24.264194488525391</v>
       </c>
       <c r="BF235" s="3">
-        <v>24.264194488525391</v>
+        <v>22.203035354614261</v>
       </c>
       <c r="BG235" s="3">
-        <v>22.203035354614261</v>
-      </c>
-      <c r="BH235" s="3">
         <v>53.967231750488281</v>
       </c>
     </row>
-    <row r="236" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A236" s="2">
         <v>45630</v>
       </c>
@@ -43559,28 +42854,25 @@
         <v>13.246927261352541</v>
       </c>
       <c r="BB236" s="3">
-        <v>-4.5217337608337402</v>
+        <v>6.070000171661377</v>
       </c>
       <c r="BC236" s="3">
-        <v>6.070000171661377</v>
+        <v>54.688388824462891</v>
       </c>
       <c r="BD236" s="3">
-        <v>54.688388824462891</v>
+        <v>19.17742919921875</v>
       </c>
       <c r="BE236" s="3">
-        <v>19.17742919921875</v>
+        <v>24.150653839111332</v>
       </c>
       <c r="BF236" s="3">
-        <v>24.150653839111332</v>
+        <v>22.138034820556641</v>
       </c>
       <c r="BG236" s="3">
-        <v>22.138034820556641</v>
-      </c>
-      <c r="BH236" s="3">
         <v>54.362594604492188</v>
       </c>
     </row>
-    <row r="237" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A237" s="2">
         <v>45631</v>
       </c>
@@ -43741,28 +43033,25 @@
         <v>13.25679779052734</v>
       </c>
       <c r="BB237" s="3">
-        <v>-4.5613226890563956</v>
+        <v>6.1599998474121094</v>
       </c>
       <c r="BC237" s="3">
-        <v>6.1599998474121094</v>
+        <v>55.136730194091797</v>
       </c>
       <c r="BD237" s="3">
-        <v>55.136730194091797</v>
+        <v>19.46942138671875</v>
       </c>
       <c r="BE237" s="3">
-        <v>19.46942138671875</v>
+        <v>24.562234878540039</v>
       </c>
       <c r="BF237" s="3">
-        <v>24.562234878540039</v>
+        <v>22.611623764038089</v>
       </c>
       <c r="BG237" s="3">
-        <v>22.611623764038089</v>
-      </c>
-      <c r="BH237" s="3">
         <v>54.293407440185547</v>
       </c>
     </row>
-    <row r="238" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A238" s="2">
         <v>45632</v>
       </c>
@@ -43923,28 +43212,25 @@
         <v>13.05937671661377</v>
       </c>
       <c r="BB238" s="3">
-        <v>-4.5556678771972656</v>
+        <v>5.9800000190734863</v>
       </c>
       <c r="BC238" s="3">
-        <v>5.9800000190734863</v>
+        <v>54.192348480224609</v>
       </c>
       <c r="BD238" s="3">
-        <v>54.192348480224609</v>
+        <v>19.017303466796879</v>
       </c>
       <c r="BE238" s="3">
-        <v>19.017303466796879</v>
+        <v>24.43923377990723</v>
       </c>
       <c r="BF238" s="3">
-        <v>24.43923377990723</v>
+        <v>22.48161697387695</v>
       </c>
       <c r="BG238" s="3">
-        <v>22.48161697387695</v>
-      </c>
-      <c r="BH238" s="3">
         <v>54.955642700195313</v>
       </c>
     </row>
-    <row r="239" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A239" s="2">
         <v>45635</v>
       </c>
@@ -44105,28 +43391,25 @@
         <v>12.86999988555908</v>
       </c>
       <c r="BB239" s="3">
-        <v>-4.4114475250244141</v>
+        <v>6.119999885559082</v>
       </c>
       <c r="BC239" s="3">
-        <v>6.119999885559082</v>
+        <v>57.073196411132813</v>
       </c>
       <c r="BD239" s="3">
-        <v>57.073196411132813</v>
+        <v>19.111494064331051</v>
       </c>
       <c r="BE239" s="3">
-        <v>19.111494064331051</v>
+        <v>24.16011810302734</v>
       </c>
       <c r="BF239" s="3">
-        <v>24.16011810302734</v>
+        <v>22.88092041015625</v>
       </c>
       <c r="BG239" s="3">
-        <v>22.88092041015625</v>
-      </c>
-      <c r="BH239" s="3">
         <v>55.103904724121087</v>
       </c>
     </row>
-    <row r="240" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A240" s="2">
         <v>45636</v>
       </c>
@@ -44287,28 +43570,25 @@
         <v>13.27000045776367</v>
       </c>
       <c r="BB240" s="3">
-        <v>-4.4708318710327148</v>
+        <v>6.119999885559082</v>
       </c>
       <c r="BC240" s="3">
-        <v>6.119999885559082</v>
+        <v>57.015960693359382</v>
       </c>
       <c r="BD240" s="3">
-        <v>57.015960693359382</v>
+        <v>19.450582504272461</v>
       </c>
       <c r="BE240" s="3">
-        <v>19.450582504272461</v>
+        <v>24.33515739440918</v>
       </c>
       <c r="BF240" s="3">
-        <v>24.33515739440918</v>
+        <v>23.196645736694339</v>
       </c>
       <c r="BG240" s="3">
-        <v>23.196645736694339</v>
-      </c>
-      <c r="BH240" s="3">
         <v>56.220809936523438</v>
       </c>
     </row>
-    <row r="241" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A241" s="2">
         <v>45637</v>
       </c>
@@ -44469,28 +43749,25 @@
         <v>13.739999771118161</v>
       </c>
       <c r="BB241" s="3">
-        <v>-4.5132498741149902</v>
+        <v>6.130000114440918</v>
       </c>
       <c r="BC241" s="3">
-        <v>6.130000114440918</v>
+        <v>56.128810882568359</v>
       </c>
       <c r="BD241" s="3">
-        <v>56.128810882568359</v>
+        <v>19.780254364013668</v>
       </c>
       <c r="BE241" s="3">
-        <v>19.780254364013668</v>
+        <v>24.718349456787109</v>
       </c>
       <c r="BF241" s="3">
-        <v>24.718349456787109</v>
+        <v>23.168788909912109</v>
       </c>
       <c r="BG241" s="3">
-        <v>23.168788909912109</v>
-      </c>
-      <c r="BH241" s="3">
         <v>57.871456146240227</v>
       </c>
     </row>
-    <row r="242" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A242" s="2">
         <v>45638</v>
       </c>
@@ -44651,28 +43928,25 @@
         <v>12.85000038146973</v>
       </c>
       <c r="BB242" s="3">
-        <v>-4.3322668075561523</v>
+        <v>5.9600000381469727</v>
       </c>
       <c r="BC242" s="3">
-        <v>5.9600000381469727</v>
+        <v>54.579795837402337</v>
       </c>
       <c r="BD242" s="3">
-        <v>54.579795837402337</v>
+        <v>19.168010711669918</v>
       </c>
       <c r="BE242" s="3">
-        <v>19.168010711669918</v>
+        <v>23.540384292602539</v>
       </c>
       <c r="BF242" s="3">
-        <v>23.540384292602539</v>
+        <v>22.723056793212891</v>
       </c>
       <c r="BG242" s="3">
-        <v>22.723056793212891</v>
-      </c>
-      <c r="BH242" s="3">
         <v>57.130142211914063</v>
       </c>
     </row>
-    <row r="243" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A243" s="2">
         <v>45639</v>
       </c>
@@ -44833,28 +44107,25 @@
         <v>12.47999954223633</v>
       </c>
       <c r="BB243" s="3">
-        <v>-4.3181281089782706</v>
+        <v>5.8600001335144043</v>
       </c>
       <c r="BC243" s="3">
-        <v>5.8600001335144043</v>
+        <v>53.761726379394531</v>
       </c>
       <c r="BD243" s="3">
-        <v>53.761726379394531</v>
+        <v>18.92310905456543</v>
       </c>
       <c r="BE243" s="3">
-        <v>18.92310905456543</v>
+        <v>23.379535675048832</v>
       </c>
       <c r="BF243" s="3">
-        <v>23.379535675048832</v>
+        <v>22.75091552734375</v>
       </c>
       <c r="BG243" s="3">
-        <v>22.75091552734375</v>
-      </c>
-      <c r="BH243" s="3">
         <v>56.991771697998047</v>
       </c>
     </row>
-    <row r="244" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A244" s="2">
         <v>45642</v>
       </c>
@@ -45015,28 +44286,25 @@
         <v>12.539999961853029</v>
       </c>
       <c r="BB244" s="3">
-        <v>-4.2983331680297852</v>
+        <v>5.8299999237060547</v>
       </c>
       <c r="BC244" s="3">
-        <v>5.8299999237060547</v>
+        <v>53.732852935791023</v>
       </c>
       <c r="BD244" s="3">
-        <v>53.732852935791023</v>
+        <v>18.0377082824707</v>
       </c>
       <c r="BE244" s="3">
-        <v>18.0377082824707</v>
+        <v>23.275459289550781</v>
       </c>
       <c r="BF244" s="3">
-        <v>23.275459289550781</v>
+        <v>22.119461059570309</v>
       </c>
       <c r="BG244" s="3">
-        <v>22.119461059570309</v>
-      </c>
-      <c r="BH244" s="3">
         <v>56.448143005371087</v>
       </c>
     </row>
-    <row r="245" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A245" s="2">
         <v>45643</v>
       </c>
@@ -45197,28 +44465,25 @@
         <v>13.44999980926514</v>
       </c>
       <c r="BB245" s="3">
-        <v>-4.2672266960144043</v>
+        <v>5.7800002098083496</v>
       </c>
       <c r="BC245" s="3">
-        <v>5.7800002098083496</v>
+        <v>54.002334594726563</v>
       </c>
       <c r="BD245" s="3">
-        <v>54.002334594726563</v>
+        <v>18.131900787353519</v>
       </c>
       <c r="BE245" s="3">
-        <v>18.131900787353519</v>
+        <v>23.299114227294918</v>
       </c>
       <c r="BF245" s="3">
-        <v>23.299114227294918</v>
+        <v>22.295896530151371</v>
       </c>
       <c r="BG245" s="3">
-        <v>22.295896530151371</v>
-      </c>
-      <c r="BH245" s="3">
         <v>57.228988647460938</v>
       </c>
     </row>
-    <row r="246" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A246" s="2">
         <v>45644</v>
       </c>
@@ -45379,28 +44644,25 @@
         <v>12.47000026702881</v>
       </c>
       <c r="BB246" s="3">
-        <v>-4.2134976387023926</v>
+        <v>5.5500001907348633</v>
       </c>
       <c r="BC246" s="3">
-        <v>5.5500001907348633</v>
+        <v>52.751167297363281</v>
       </c>
       <c r="BD246" s="3">
-        <v>52.751167297363281</v>
+        <v>17.0486946105957</v>
       </c>
       <c r="BE246" s="3">
-        <v>17.0486946105957</v>
+        <v>23.019998550415039</v>
       </c>
       <c r="BF246" s="3">
-        <v>23.019998550415039</v>
+        <v>20.791549682617191</v>
       </c>
       <c r="BG246" s="3">
-        <v>20.791549682617191</v>
-      </c>
-      <c r="BH246" s="3">
         <v>56.388835906982422</v>
       </c>
     </row>
-    <row r="247" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A247" s="2">
         <v>45645</v>
       </c>
@@ -45561,28 +44823,25 @@
         <v>13.060000419616699</v>
       </c>
       <c r="BB247" s="3">
-        <v>-4.2050142288208008</v>
+        <v>5.5199999809265137</v>
       </c>
       <c r="BC247" s="3">
-        <v>5.5199999809265137</v>
+        <v>51.750232696533203</v>
       </c>
       <c r="BD247" s="3">
-        <v>51.750232696533203</v>
+        <v>17.284175872802731</v>
       </c>
       <c r="BE247" s="3">
-        <v>17.284175872802731</v>
+        <v>23.256536483764648</v>
       </c>
       <c r="BF247" s="3">
-        <v>23.256536483764648</v>
+        <v>21.980171203613281</v>
       </c>
       <c r="BG247" s="3">
-        <v>21.980171203613281</v>
-      </c>
-      <c r="BH247" s="3">
         <v>55.805675506591797</v>
       </c>
     </row>
-    <row r="248" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A248" s="2">
         <v>45646</v>
       </c>
@@ -45743,28 +45002,25 @@
         <v>13.289999961853029</v>
       </c>
       <c r="BB248" s="3">
-        <v>-4.2417759895324707</v>
+        <v>5.429999828338623</v>
       </c>
       <c r="BC248" s="3">
-        <v>5.429999828338623</v>
+        <v>52.568302154541023</v>
       </c>
       <c r="BD248" s="3">
-        <v>52.568302154541023</v>
+        <v>17.67036056518555</v>
       </c>
       <c r="BE248" s="3">
-        <v>17.67036056518555</v>
+        <v>23.488346099853519</v>
       </c>
       <c r="BF248" s="3">
-        <v>23.488346099853519</v>
+        <v>21.905881881713871</v>
       </c>
       <c r="BG248" s="3">
-        <v>21.905881881713871</v>
-      </c>
-      <c r="BH248" s="3">
         <v>54.896343231201172</v>
       </c>
     </row>
-    <row r="249" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A249" s="2">
         <v>45649</v>
       </c>
@@ -45925,28 +45181,25 @@
         <v>12.590000152587891</v>
       </c>
       <c r="BB249" s="3">
-        <v>-4.2134976387023926</v>
+        <v>5.2399997711181641</v>
       </c>
       <c r="BC249" s="3">
-        <v>5.2399997711181641</v>
+        <v>52.789661407470703</v>
       </c>
       <c r="BD249" s="3">
-        <v>52.789661407470703</v>
+        <v>17.434881210327148</v>
       </c>
       <c r="BE249" s="3">
-        <v>17.434881210327148</v>
+        <v>22.726690292358398</v>
       </c>
       <c r="BF249" s="3">
-        <v>22.726690292358398</v>
+        <v>20.95223236083984</v>
       </c>
       <c r="BG249" s="3">
-        <v>20.95223236083984</v>
-      </c>
-      <c r="BH249" s="3">
         <v>53.688510894775391</v>
       </c>
     </row>
-    <row r="250" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A250" s="2">
         <v>45652</v>
       </c>
@@ -46107,28 +45360,25 @@
         <v>12.30000019073486</v>
       </c>
       <c r="BB250" s="3">
-        <v>5.0620574951171884</v>
+        <v>5.2899999618530273</v>
       </c>
       <c r="BC250" s="3">
-        <v>5.2899999618530273</v>
+        <v>52.943653106689453</v>
       </c>
       <c r="BD250" s="3">
-        <v>52.943653106689453</v>
+        <v>17.322135925292969</v>
       </c>
       <c r="BE250" s="3">
-        <v>17.322135925292969</v>
+        <v>22.90645790100098</v>
       </c>
       <c r="BF250" s="3">
-        <v>22.90645790100098</v>
+        <v>21.26076507568359</v>
       </c>
       <c r="BG250" s="3">
-        <v>21.26076507568359</v>
-      </c>
-      <c r="BH250" s="3">
         <v>54.104240417480469</v>
       </c>
     </row>
-    <row r="251" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A251" s="2">
         <v>45653</v>
       </c>
@@ -46289,29 +45539,26 @@
         <v>12.30000019073486</v>
       </c>
       <c r="BB251" s="3">
-        <v>5.0761580467224121</v>
+        <v>5.2899999618530273</v>
       </c>
       <c r="BC251" s="3">
-        <v>5.2899999618530273</v>
+        <v>52.683799743652337</v>
       </c>
       <c r="BD251" s="3">
-        <v>52.683799743652337</v>
+        <v>17.102384567260739</v>
       </c>
       <c r="BE251" s="3">
-        <v>17.102384567260739</v>
+        <v>22.655548095703121</v>
       </c>
       <c r="BF251" s="3">
-        <v>22.655548095703121</v>
+        <v>21.429056167602539</v>
       </c>
       <c r="BG251" s="3">
-        <v>21.429056167602539</v>
-      </c>
-      <c r="BH251" s="3">
         <v>53.134204864501953</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH251" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:BG251" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
